--- a/manuals/feedback_figures/figures.xlsx
+++ b/manuals/feedback_figures/figures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.213\local\koike\proj\e7awg_sw\manuals\feedback_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F659DF2-8724-4F8E-8660-B81C8F15DE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5866FDA9-9345-442E-9459-46E45754BF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20925" tabRatio="675" firstSheet="1" activeTab="5" xr2:uid="{B803739A-C1C9-4218-A586-EC4A5DED1E9C}"/>
+    <workbookView xWindow="4605" yWindow="570" windowWidth="20925" windowHeight="19845" tabRatio="794" activeTab="5" xr2:uid="{B803739A-C1C9-4218-A586-EC4A5DED1E9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="626">
   <si>
     <t>AWG スタートコマンド</t>
     <phoneticPr fontId="1"/>
@@ -4096,6 +4096,36 @@
     </rPh>
     <rPh sb="9" eb="10">
       <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件付きフィードバックコマンド</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウケンツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタート時刻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2 bits</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了待ちフラグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィードバックフラグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件付きフィードバックコマンドエラー</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウケンツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5480,7 +5510,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="374">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6246,6 +6276,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6288,12 +6324,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6319,6 +6349,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6570,17 +6609,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="80" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="98" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="81" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16584,13 +16635,13 @@
       <xdr:col>19</xdr:col>
       <xdr:colOff>438148</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>190501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>380999</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -16605,8 +16656,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13468348" y="1171575"/>
-          <a:ext cx="1314451" cy="561975"/>
+          <a:off x="13425766" y="1131795"/>
+          <a:ext cx="1309968" cy="582146"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18748,6 +18799,1308 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>679636</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>515471</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D83533-5F2B-4517-8C5A-B83D50173661}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11616577" y="5186642"/>
+          <a:ext cx="4620747" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>100851</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>670111</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="正方形/長方形 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5413CCC-44D6-43C8-B5B0-1E2B5FBF2B86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11037792" y="5008469"/>
+          <a:ext cx="569260" cy="349623"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>AWG</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>679636</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>549088</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直線コネクタ 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB1C41A-2F6F-428F-9ED5-B6C2E0ABB2A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11616577" y="5892613"/>
+          <a:ext cx="4654364" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="31750">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>483534</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>674034</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="正方形/長方形 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D65CBF8-5972-4133-8785-D1C0B7E33CF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10053358" y="5723964"/>
+          <a:ext cx="1557617" cy="349624"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>キャプチャユニット</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>558052</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41056</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>558052</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>222030</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="直線コネクタ 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0861C5F6-7C03-4D84-B0DB-FAD1D6D16461}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12178552" y="4982850"/>
+          <a:ext cx="0" cy="416298"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>5601</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>434227</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>64995</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="896" name="正方形/長方形 895">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC7752C3-0468-45E2-9294-ED0FFB0EAB85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11626101" y="4415117"/>
+          <a:ext cx="1112185" cy="591672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>波形出力開始</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(1 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>回目</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>177052</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>44011</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>177052</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>215462</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="898" name="直線コネクタ 897">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72EB547F-0292-4D7A-89AD-326F754EE8B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12481111" y="5691776"/>
+          <a:ext cx="0" cy="406774"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>243726</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="899" name="正方形/長方形 898">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{112BBEDD-8590-443E-B438-6818D46180B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11864226" y="6156511"/>
+          <a:ext cx="1224244" cy="368675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>キャプチャ開始</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>344586</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>39741</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>344586</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="900" name="直線コネクタ 899">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139675E5-2B08-4530-A88F-459483235A23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15382880" y="5687506"/>
+          <a:ext cx="0" cy="405132"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>373161</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>325536</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="901" name="正方形/長方形 900">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634C5F46-D2DA-44C1-B9B6-925F15A5FB5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14727896" y="6156511"/>
+          <a:ext cx="1319493" cy="368675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>四値化結果出力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>668433</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>32149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>668433</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>211481</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="902" name="直線コネクタ 901">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C5DE907-599A-47FF-9C38-2B5CD7A419B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14339609" y="4973943"/>
+          <a:ext cx="0" cy="414656"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>32500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>188819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>658909</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>64995</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="903" name="正方形/長方形 902">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E072DCEC-AE4C-425C-A2B2-2EE7F26EA4D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13703676" y="4424643"/>
+          <a:ext cx="1309968" cy="582146"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>波形パラメータ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>設定開始</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>647706</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41056</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>647706</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>222030</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="904" name="直線コネクタ 903">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{957EDDB2-83CB-4B79-91E7-E9BEE0521377}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15686000" y="4982850"/>
+          <a:ext cx="0" cy="416298"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>97496</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>523881</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="907" name="正方形/長方形 906">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E89F0F1A-4BEC-4EF9-86FB-97FB3A4684DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15135790" y="4426323"/>
+          <a:ext cx="1109944" cy="591672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>波形出力開始</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>回目</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>577102</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>138952</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>200024</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="922" name="直線コネクタ 921">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEDC4DDD-F9DC-48F2-A1DD-FE169F235596}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12197602" y="5205692"/>
+          <a:ext cx="245409" cy="642097"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>344586</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>611286</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="926" name="直線コネクタ 925">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D37FA256-A85F-4856-806C-ADE3896A5BDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="15382880" y="5253317"/>
+          <a:ext cx="266700" cy="648821"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>290795</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>176496</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="927" name="正方形/長方形 926">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C84ECA-4C58-4625-86C8-51A6AC696FDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16012648" y="5948082"/>
+          <a:ext cx="569260" cy="349623"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>時間</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>460562</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>145675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>205630</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>82923</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="928" name="正方形/長方形 927">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE84BF9C-EB91-4DB8-BF1B-822233073BD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12764621" y="4616822"/>
+          <a:ext cx="1112185" cy="407895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>波形出力完了</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>329455</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>36574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>329455</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>217548</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="931" name="直線コネクタ 930">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69F6E21-B7EC-48A6-9DCA-42FAAC242852}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13317073" y="4978368"/>
+          <a:ext cx="0" cy="416298"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -31104,6 +32457,11 @@
     <mergeCell ref="CP32:CU32"/>
     <mergeCell ref="CP29:CU29"/>
     <mergeCell ref="CP28:CU28"/>
+    <mergeCell ref="BL27:BQ27"/>
+    <mergeCell ref="BR27:BW27"/>
+    <mergeCell ref="BX27:CC27"/>
+    <mergeCell ref="CD27:CI27"/>
+    <mergeCell ref="CJ27:CO27"/>
     <mergeCell ref="CP63:CU63"/>
     <mergeCell ref="CV63:DA63"/>
     <mergeCell ref="DB63:DG63"/>
@@ -31173,11 +32531,6 @@
     <mergeCell ref="BX29:CC29"/>
     <mergeCell ref="CD29:CI29"/>
     <mergeCell ref="CJ29:CO29"/>
-    <mergeCell ref="BL27:BQ27"/>
-    <mergeCell ref="BR27:BW27"/>
-    <mergeCell ref="BX27:CC27"/>
-    <mergeCell ref="CD27:CI27"/>
-    <mergeCell ref="CJ27:CO27"/>
     <mergeCell ref="DI25:DO25"/>
     <mergeCell ref="CV26:DA26"/>
     <mergeCell ref="DB26:DG26"/>
@@ -33504,13 +34857,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD61CAE-C273-4175-8812-B19C7AB731B2}">
-  <dimension ref="C2:NO11"/>
+  <dimension ref="C2:OT11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="386" width="3.625" customWidth="1"/>
+    <col min="1" max="572" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="2" spans="3:410" x14ac:dyDescent="0.4">
       <c r="AQ2" s="2"/>
       <c r="AR2" s="8">
         <v>15</v>
@@ -33518,31 +34871,31 @@
       <c r="AS2" s="6">
         <v>14</v>
       </c>
-      <c r="AT2" s="262" t="s">
+      <c r="AT2" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="AU2" s="263"/>
-      <c r="AV2" s="263"/>
-      <c r="AW2" s="263"/>
-      <c r="AX2" s="263"/>
-      <c r="AY2" s="263"/>
-      <c r="AZ2" s="263"/>
-      <c r="BA2" s="263"/>
-      <c r="BB2" s="263"/>
-      <c r="BC2" s="263"/>
-      <c r="BD2" s="264"/>
+      <c r="AU2" s="265"/>
+      <c r="AV2" s="265"/>
+      <c r="AW2" s="265"/>
+      <c r="AX2" s="265"/>
+      <c r="AY2" s="265"/>
+      <c r="AZ2" s="265"/>
+      <c r="BA2" s="265"/>
+      <c r="BB2" s="265"/>
+      <c r="BC2" s="265"/>
+      <c r="BD2" s="266"/>
       <c r="BE2" s="6">
         <v>1</v>
       </c>
       <c r="BF2" s="7">
         <v>0</v>
       </c>
-      <c r="BG2" s="255" t="s">
+      <c r="BG2" s="257" t="s">
         <v>12</v>
       </c>
       <c r="BH2" s="40"/>
     </row>
-    <row r="3" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:410" x14ac:dyDescent="0.4">
       <c r="C3" s="241" t="s">
         <v>0</v>
       </c>
@@ -33568,186 +34921,186 @@
       <c r="W3" s="242"/>
       <c r="X3" s="242"/>
       <c r="Y3" s="243"/>
-      <c r="AC3" s="268" t="s">
+      <c r="AC3" s="270" t="s">
         <v>9</v>
       </c>
-      <c r="AD3" s="268"/>
-      <c r="AE3" s="268"/>
-      <c r="AF3" s="268"/>
-      <c r="AG3" s="268"/>
-      <c r="AH3" s="268"/>
-      <c r="AI3" s="268"/>
-      <c r="AJ3" s="268"/>
-      <c r="AK3" s="268"/>
-      <c r="AL3" s="268"/>
-      <c r="AM3" s="268"/>
-      <c r="AN3" s="268"/>
+      <c r="AD3" s="270"/>
+      <c r="AE3" s="270"/>
+      <c r="AF3" s="270"/>
+      <c r="AG3" s="270"/>
+      <c r="AH3" s="270"/>
+      <c r="AI3" s="270"/>
+      <c r="AJ3" s="270"/>
+      <c r="AK3" s="270"/>
+      <c r="AL3" s="270"/>
+      <c r="AM3" s="270"/>
+      <c r="AN3" s="270"/>
       <c r="AQ3" s="2"/>
       <c r="AR3" s="243" t="s">
         <v>387</v>
       </c>
-      <c r="AS3" s="268"/>
-      <c r="AT3" s="268"/>
-      <c r="AU3" s="268"/>
-      <c r="AV3" s="268"/>
-      <c r="AW3" s="268"/>
-      <c r="AX3" s="268"/>
-      <c r="AY3" s="268"/>
-      <c r="AZ3" s="268"/>
-      <c r="BA3" s="268"/>
-      <c r="BB3" s="268"/>
-      <c r="BC3" s="268"/>
-      <c r="BD3" s="268"/>
-      <c r="BE3" s="268"/>
-      <c r="BF3" s="268"/>
-      <c r="BK3" s="268" t="s">
+      <c r="AS3" s="270"/>
+      <c r="AT3" s="270"/>
+      <c r="AU3" s="270"/>
+      <c r="AV3" s="270"/>
+      <c r="AW3" s="270"/>
+      <c r="AX3" s="270"/>
+      <c r="AY3" s="270"/>
+      <c r="AZ3" s="270"/>
+      <c r="BA3" s="270"/>
+      <c r="BB3" s="270"/>
+      <c r="BC3" s="270"/>
+      <c r="BD3" s="270"/>
+      <c r="BE3" s="270"/>
+      <c r="BF3" s="270"/>
+      <c r="BK3" s="270" t="s">
         <v>22</v>
       </c>
-      <c r="BL3" s="268"/>
-      <c r="BM3" s="268"/>
-      <c r="BN3" s="268"/>
-      <c r="BO3" s="268"/>
-      <c r="BP3" s="268"/>
-      <c r="BQ3" s="268"/>
-      <c r="BR3" s="268"/>
-      <c r="BS3" s="268"/>
-      <c r="BT3" s="268"/>
-      <c r="BU3" s="268"/>
-      <c r="BV3" s="268"/>
-      <c r="BW3" s="268"/>
-      <c r="BX3" s="268"/>
-      <c r="BY3" s="268"/>
-      <c r="BZ3" s="268"/>
-      <c r="CA3" s="268"/>
-      <c r="CB3" s="268"/>
-      <c r="CC3" s="268"/>
-      <c r="CD3" s="268"/>
-      <c r="CE3" s="268"/>
-      <c r="CF3" s="268"/>
-      <c r="CG3" s="268"/>
-      <c r="CH3" s="268"/>
-      <c r="CI3" s="268"/>
-      <c r="CJ3" s="268"/>
-      <c r="CK3" s="268"/>
-      <c r="CL3" s="268"/>
-      <c r="CM3" s="268"/>
-      <c r="CN3" s="268"/>
-      <c r="CO3" s="268"/>
-      <c r="CP3" s="268"/>
-      <c r="CQ3" s="268"/>
-      <c r="CU3" s="268" t="s">
+      <c r="BL3" s="270"/>
+      <c r="BM3" s="270"/>
+      <c r="BN3" s="270"/>
+      <c r="BO3" s="270"/>
+      <c r="BP3" s="270"/>
+      <c r="BQ3" s="270"/>
+      <c r="BR3" s="270"/>
+      <c r="BS3" s="270"/>
+      <c r="BT3" s="270"/>
+      <c r="BU3" s="270"/>
+      <c r="BV3" s="270"/>
+      <c r="BW3" s="270"/>
+      <c r="BX3" s="270"/>
+      <c r="BY3" s="270"/>
+      <c r="BZ3" s="270"/>
+      <c r="CA3" s="270"/>
+      <c r="CB3" s="270"/>
+      <c r="CC3" s="270"/>
+      <c r="CD3" s="270"/>
+      <c r="CE3" s="270"/>
+      <c r="CF3" s="270"/>
+      <c r="CG3" s="270"/>
+      <c r="CH3" s="270"/>
+      <c r="CI3" s="270"/>
+      <c r="CJ3" s="270"/>
+      <c r="CK3" s="270"/>
+      <c r="CL3" s="270"/>
+      <c r="CM3" s="270"/>
+      <c r="CN3" s="270"/>
+      <c r="CO3" s="270"/>
+      <c r="CP3" s="270"/>
+      <c r="CQ3" s="270"/>
+      <c r="CU3" s="270" t="s">
         <v>614</v>
       </c>
-      <c r="CV3" s="268"/>
-      <c r="CW3" s="268"/>
-      <c r="CX3" s="268"/>
-      <c r="CY3" s="268"/>
-      <c r="CZ3" s="268"/>
-      <c r="DA3" s="268"/>
-      <c r="DB3" s="268"/>
-      <c r="DC3" s="268"/>
-      <c r="DD3" s="268"/>
-      <c r="DE3" s="268"/>
-      <c r="DF3" s="268"/>
-      <c r="DG3" s="268"/>
-      <c r="DH3" s="268"/>
-      <c r="DI3" s="268"/>
-      <c r="DJ3" s="268"/>
-      <c r="DK3" s="268"/>
-      <c r="DL3" s="268"/>
-      <c r="DM3" s="268"/>
-      <c r="DN3" s="268"/>
-      <c r="DO3" s="268"/>
-      <c r="DP3" s="268"/>
-      <c r="DQ3" s="268"/>
-      <c r="DR3" s="268"/>
-      <c r="DS3" s="268"/>
-      <c r="DT3" s="268"/>
-      <c r="DU3" s="268"/>
-      <c r="DV3" s="268"/>
-      <c r="DW3" s="268"/>
-      <c r="DX3" s="268"/>
-      <c r="DY3" s="268"/>
-      <c r="DZ3" s="268"/>
-      <c r="EA3" s="268"/>
-      <c r="EB3" s="268"/>
-      <c r="EC3" s="268"/>
-      <c r="ED3" s="268"/>
-      <c r="EH3" s="268" t="s">
+      <c r="CV3" s="270"/>
+      <c r="CW3" s="270"/>
+      <c r="CX3" s="270"/>
+      <c r="CY3" s="270"/>
+      <c r="CZ3" s="270"/>
+      <c r="DA3" s="270"/>
+      <c r="DB3" s="270"/>
+      <c r="DC3" s="270"/>
+      <c r="DD3" s="270"/>
+      <c r="DE3" s="270"/>
+      <c r="DF3" s="270"/>
+      <c r="DG3" s="270"/>
+      <c r="DH3" s="270"/>
+      <c r="DI3" s="270"/>
+      <c r="DJ3" s="270"/>
+      <c r="DK3" s="270"/>
+      <c r="DL3" s="270"/>
+      <c r="DM3" s="270"/>
+      <c r="DN3" s="270"/>
+      <c r="DO3" s="270"/>
+      <c r="DP3" s="270"/>
+      <c r="DQ3" s="270"/>
+      <c r="DR3" s="270"/>
+      <c r="DS3" s="270"/>
+      <c r="DT3" s="270"/>
+      <c r="DU3" s="270"/>
+      <c r="DV3" s="270"/>
+      <c r="DW3" s="270"/>
+      <c r="DX3" s="270"/>
+      <c r="DY3" s="270"/>
+      <c r="DZ3" s="270"/>
+      <c r="EA3" s="270"/>
+      <c r="EB3" s="270"/>
+      <c r="EC3" s="270"/>
+      <c r="ED3" s="270"/>
+      <c r="EH3" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="EI3" s="268"/>
-      <c r="EJ3" s="268"/>
-      <c r="EK3" s="268"/>
-      <c r="EL3" s="268"/>
-      <c r="EM3" s="268"/>
-      <c r="EN3" s="268"/>
-      <c r="EO3" s="268"/>
-      <c r="EP3" s="268"/>
-      <c r="EQ3" s="268"/>
-      <c r="ER3" s="268"/>
-      <c r="ES3" s="268"/>
-      <c r="ET3" s="268"/>
-      <c r="EU3" s="268"/>
-      <c r="EV3" s="268"/>
-      <c r="EW3" s="268"/>
-      <c r="EX3" s="268"/>
-      <c r="EY3" s="268"/>
-      <c r="EZ3" s="268"/>
-      <c r="FA3" s="268"/>
-      <c r="FB3" s="268"/>
-      <c r="FC3" s="268"/>
-      <c r="FD3" s="268"/>
-      <c r="FE3" s="268"/>
-      <c r="FF3" s="268"/>
-      <c r="FG3" s="268"/>
-      <c r="FH3" s="268"/>
-      <c r="FI3" s="268"/>
-      <c r="FJ3" s="268"/>
-      <c r="FK3" s="268"/>
-      <c r="FL3" s="268"/>
-      <c r="FM3" s="268"/>
-      <c r="FN3" s="268"/>
-      <c r="FO3" s="268"/>
-      <c r="FP3" s="268"/>
-      <c r="FQ3" s="268"/>
-      <c r="FR3" s="268"/>
-      <c r="FS3" s="268"/>
-      <c r="FT3" s="268"/>
-      <c r="FU3" s="268"/>
-      <c r="FV3" s="268"/>
-      <c r="FW3" s="268"/>
-      <c r="FX3" s="268"/>
-      <c r="FY3" s="268"/>
-      <c r="FZ3" s="268"/>
-      <c r="GA3" s="268"/>
-      <c r="GB3" s="268"/>
-      <c r="GF3" s="268" t="s">
+      <c r="EI3" s="270"/>
+      <c r="EJ3" s="270"/>
+      <c r="EK3" s="270"/>
+      <c r="EL3" s="270"/>
+      <c r="EM3" s="270"/>
+      <c r="EN3" s="270"/>
+      <c r="EO3" s="270"/>
+      <c r="EP3" s="270"/>
+      <c r="EQ3" s="270"/>
+      <c r="ER3" s="270"/>
+      <c r="ES3" s="270"/>
+      <c r="ET3" s="270"/>
+      <c r="EU3" s="270"/>
+      <c r="EV3" s="270"/>
+      <c r="EW3" s="270"/>
+      <c r="EX3" s="270"/>
+      <c r="EY3" s="270"/>
+      <c r="EZ3" s="270"/>
+      <c r="FA3" s="270"/>
+      <c r="FB3" s="270"/>
+      <c r="FC3" s="270"/>
+      <c r="FD3" s="270"/>
+      <c r="FE3" s="270"/>
+      <c r="FF3" s="270"/>
+      <c r="FG3" s="270"/>
+      <c r="FH3" s="270"/>
+      <c r="FI3" s="270"/>
+      <c r="FJ3" s="270"/>
+      <c r="FK3" s="270"/>
+      <c r="FL3" s="270"/>
+      <c r="FM3" s="270"/>
+      <c r="FN3" s="270"/>
+      <c r="FO3" s="270"/>
+      <c r="FP3" s="270"/>
+      <c r="FQ3" s="270"/>
+      <c r="FR3" s="270"/>
+      <c r="FS3" s="270"/>
+      <c r="FT3" s="270"/>
+      <c r="FU3" s="270"/>
+      <c r="FV3" s="270"/>
+      <c r="FW3" s="270"/>
+      <c r="FX3" s="270"/>
+      <c r="FY3" s="270"/>
+      <c r="FZ3" s="270"/>
+      <c r="GA3" s="270"/>
+      <c r="GB3" s="270"/>
+      <c r="GF3" s="270" t="s">
         <v>37</v>
       </c>
-      <c r="GG3" s="268"/>
-      <c r="GH3" s="268"/>
-      <c r="GI3" s="268"/>
-      <c r="GJ3" s="268"/>
-      <c r="GK3" s="268"/>
-      <c r="GL3" s="268"/>
-      <c r="GM3" s="268"/>
-      <c r="GN3" s="268"/>
-      <c r="GO3" s="268"/>
-      <c r="GP3" s="268"/>
-      <c r="GQ3" s="268"/>
-      <c r="GR3" s="268"/>
-      <c r="GS3" s="268"/>
-      <c r="GT3" s="268"/>
-      <c r="GU3" s="268"/>
-      <c r="GV3" s="268"/>
-      <c r="GW3" s="268"/>
-      <c r="GX3" s="268"/>
-      <c r="GY3" s="268"/>
-      <c r="GZ3" s="268"/>
-      <c r="HA3" s="268"/>
-      <c r="HB3" s="268"/>
-      <c r="HC3" s="268"/>
+      <c r="GG3" s="270"/>
+      <c r="GH3" s="270"/>
+      <c r="GI3" s="270"/>
+      <c r="GJ3" s="270"/>
+      <c r="GK3" s="270"/>
+      <c r="GL3" s="270"/>
+      <c r="GM3" s="270"/>
+      <c r="GN3" s="270"/>
+      <c r="GO3" s="270"/>
+      <c r="GP3" s="270"/>
+      <c r="GQ3" s="270"/>
+      <c r="GR3" s="270"/>
+      <c r="GS3" s="270"/>
+      <c r="GT3" s="270"/>
+      <c r="GU3" s="270"/>
+      <c r="GV3" s="270"/>
+      <c r="GW3" s="270"/>
+      <c r="GX3" s="270"/>
+      <c r="GY3" s="270"/>
+      <c r="GZ3" s="270"/>
+      <c r="HA3" s="270"/>
+      <c r="HB3" s="270"/>
+      <c r="HC3" s="270"/>
       <c r="HF3" s="241" t="s">
         <v>38</v>
       </c>
@@ -33807,47 +35160,47 @@
       <c r="JI3" s="242"/>
       <c r="JJ3" s="242"/>
       <c r="JK3" s="243"/>
-      <c r="JO3" s="268" t="s">
+      <c r="JO3" s="270" t="s">
         <v>564</v>
       </c>
-      <c r="JP3" s="268"/>
-      <c r="JQ3" s="268"/>
-      <c r="JR3" s="268"/>
-      <c r="JS3" s="268"/>
-      <c r="JT3" s="268"/>
-      <c r="JU3" s="268"/>
-      <c r="JV3" s="268"/>
-      <c r="JW3" s="268"/>
-      <c r="JX3" s="268"/>
-      <c r="JY3" s="268"/>
-      <c r="JZ3" s="268"/>
-      <c r="KA3" s="268"/>
-      <c r="KB3" s="268"/>
-      <c r="KC3" s="268"/>
-      <c r="KD3" s="268"/>
-      <c r="KE3" s="268"/>
-      <c r="KF3" s="268"/>
-      <c r="KG3" s="268"/>
-      <c r="KH3" s="268"/>
-      <c r="KI3" s="268"/>
-      <c r="KJ3" s="268"/>
-      <c r="KK3" s="268"/>
-      <c r="KL3" s="268"/>
-      <c r="KM3" s="268"/>
-      <c r="KN3" s="268"/>
-      <c r="KO3" s="268"/>
-      <c r="KP3" s="268"/>
-      <c r="KQ3" s="268"/>
-      <c r="KR3" s="268"/>
-      <c r="KS3" s="268"/>
-      <c r="KT3" s="268"/>
-      <c r="KU3" s="268"/>
-      <c r="KV3" s="268"/>
-      <c r="KW3" s="268"/>
-      <c r="KX3" s="268"/>
-      <c r="KY3" s="268"/>
-      <c r="KZ3" s="268"/>
-      <c r="LA3" s="268"/>
+      <c r="JP3" s="270"/>
+      <c r="JQ3" s="270"/>
+      <c r="JR3" s="270"/>
+      <c r="JS3" s="270"/>
+      <c r="JT3" s="270"/>
+      <c r="JU3" s="270"/>
+      <c r="JV3" s="270"/>
+      <c r="JW3" s="270"/>
+      <c r="JX3" s="270"/>
+      <c r="JY3" s="270"/>
+      <c r="JZ3" s="270"/>
+      <c r="KA3" s="270"/>
+      <c r="KB3" s="270"/>
+      <c r="KC3" s="270"/>
+      <c r="KD3" s="270"/>
+      <c r="KE3" s="270"/>
+      <c r="KF3" s="270"/>
+      <c r="KG3" s="270"/>
+      <c r="KH3" s="270"/>
+      <c r="KI3" s="270"/>
+      <c r="KJ3" s="270"/>
+      <c r="KK3" s="270"/>
+      <c r="KL3" s="270"/>
+      <c r="KM3" s="270"/>
+      <c r="KN3" s="270"/>
+      <c r="KO3" s="270"/>
+      <c r="KP3" s="270"/>
+      <c r="KQ3" s="270"/>
+      <c r="KR3" s="270"/>
+      <c r="KS3" s="270"/>
+      <c r="KT3" s="270"/>
+      <c r="KU3" s="270"/>
+      <c r="KV3" s="270"/>
+      <c r="KW3" s="270"/>
+      <c r="KX3" s="270"/>
+      <c r="KY3" s="270"/>
+      <c r="KZ3" s="270"/>
+      <c r="LA3" s="270"/>
       <c r="LE3" s="241" t="s">
         <v>566</v>
       </c>
@@ -33913,8 +35266,39 @@
       <c r="NM3" s="242"/>
       <c r="NN3" s="242"/>
       <c r="NO3" s="243"/>
+      <c r="NR3" s="270" t="s">
+        <v>620</v>
+      </c>
+      <c r="NS3" s="270"/>
+      <c r="NT3" s="270"/>
+      <c r="NU3" s="270"/>
+      <c r="NV3" s="270"/>
+      <c r="NW3" s="270"/>
+      <c r="NX3" s="270"/>
+      <c r="NY3" s="270"/>
+      <c r="NZ3" s="270"/>
+      <c r="OA3" s="270"/>
+      <c r="OB3" s="270"/>
+      <c r="OC3" s="270"/>
+      <c r="OD3" s="270"/>
+      <c r="OE3" s="270"/>
+      <c r="OF3" s="270"/>
+      <c r="OG3" s="270"/>
+      <c r="OH3" s="270"/>
+      <c r="OI3" s="270"/>
+      <c r="OJ3" s="270"/>
+      <c r="OK3" s="270"/>
+      <c r="OL3" s="270"/>
+      <c r="OM3" s="270"/>
+      <c r="ON3" s="270"/>
+      <c r="OO3" s="270"/>
+      <c r="OP3" s="270"/>
+      <c r="OQ3" s="270"/>
+      <c r="OR3" s="270"/>
+      <c r="OS3" s="270"/>
+      <c r="OT3" s="270"/>
     </row>
-    <row r="4" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:410" x14ac:dyDescent="0.4">
       <c r="C4" s="39" t="s">
         <v>1</v>
       </c>
@@ -34152,23 +35536,23 @@
       <c r="FZ4" s="247"/>
       <c r="GA4" s="247"/>
       <c r="GB4" s="248"/>
-      <c r="GF4" s="269" t="s">
+      <c r="GF4" s="255" t="s">
         <v>1</v>
       </c>
-      <c r="GG4" s="269"/>
-      <c r="GH4" s="269"/>
-      <c r="GI4" s="270" t="s">
+      <c r="GG4" s="255"/>
+      <c r="GH4" s="255"/>
+      <c r="GI4" s="256" t="s">
         <v>35</v>
       </c>
-      <c r="GJ4" s="270"/>
-      <c r="GK4" s="270"/>
-      <c r="GL4" s="270"/>
-      <c r="GM4" s="270"/>
-      <c r="GN4" s="269" t="s">
+      <c r="GJ4" s="256"/>
+      <c r="GK4" s="256"/>
+      <c r="GL4" s="256"/>
+      <c r="GM4" s="256"/>
+      <c r="GN4" s="255" t="s">
         <v>1</v>
       </c>
-      <c r="GO4" s="269"/>
-      <c r="GP4" s="269"/>
+      <c r="GO4" s="255"/>
+      <c r="GP4" s="255"/>
       <c r="GQ4" s="274" t="s">
         <v>21</v>
       </c>
@@ -34407,8 +35791,49 @@
       <c r="NM4" s="247"/>
       <c r="NN4" s="247"/>
       <c r="NO4" s="248"/>
+      <c r="NR4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="NS4" s="39"/>
+      <c r="NT4" s="39"/>
+      <c r="NU4" s="245" t="s">
+        <v>624</v>
+      </c>
+      <c r="NV4" s="245"/>
+      <c r="NW4" s="245"/>
+      <c r="NX4" s="245"/>
+      <c r="NY4" s="245"/>
+      <c r="NZ4" s="245"/>
+      <c r="OA4" s="371" t="s">
+        <v>623</v>
+      </c>
+      <c r="OB4" s="372"/>
+      <c r="OC4" s="372"/>
+      <c r="OD4" s="372"/>
+      <c r="OE4" s="373"/>
+      <c r="OF4" s="244" t="s">
+        <v>621</v>
+      </c>
+      <c r="OG4" s="244"/>
+      <c r="OH4" s="244"/>
+      <c r="OI4" s="244"/>
+      <c r="OJ4" s="244"/>
+      <c r="OK4" s="245" t="s">
+        <v>2</v>
+      </c>
+      <c r="OL4" s="245"/>
+      <c r="OM4" s="245"/>
+      <c r="ON4" s="245"/>
+      <c r="OO4" s="245"/>
+      <c r="OP4" s="246" t="s">
+        <v>9</v>
+      </c>
+      <c r="OQ4" s="247"/>
+      <c r="OR4" s="247"/>
+      <c r="OS4" s="247"/>
+      <c r="OT4" s="248"/>
     </row>
-    <row r="5" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:410" x14ac:dyDescent="0.4">
       <c r="C5" s="39" t="str">
         <f>MD5</f>
         <v>88 bits</v>
@@ -34907,74 +36332,130 @@
       <c r="NM5" s="253"/>
       <c r="NN5" s="253"/>
       <c r="NO5" s="254"/>
+      <c r="NR5" s="219" t="str">
+        <f>128-24-16-64-1-2 &amp; " bits"</f>
+        <v>21 bits</v>
+      </c>
+      <c r="NS5" s="219"/>
+      <c r="NT5" s="219"/>
+      <c r="NU5" s="312" t="s">
+        <v>622</v>
+      </c>
+      <c r="NV5" s="312"/>
+      <c r="NW5" s="312"/>
+      <c r="NX5" s="312"/>
+      <c r="NY5" s="312"/>
+      <c r="NZ5" s="312"/>
+      <c r="OA5" s="240" t="s">
+        <v>26</v>
+      </c>
+      <c r="OB5" s="51"/>
+      <c r="OC5" s="51"/>
+      <c r="OD5" s="51"/>
+      <c r="OE5" s="52"/>
+      <c r="OF5" s="366" t="s">
+        <v>5</v>
+      </c>
+      <c r="OG5" s="367"/>
+      <c r="OH5" s="367"/>
+      <c r="OI5" s="367"/>
+      <c r="OJ5" s="367"/>
+      <c r="OK5" s="368" t="s">
+        <v>6</v>
+      </c>
+      <c r="OL5" s="369"/>
+      <c r="OM5" s="369"/>
+      <c r="ON5" s="369"/>
+      <c r="OO5" s="370"/>
+      <c r="OP5" s="252" t="s">
+        <v>10</v>
+      </c>
+      <c r="OQ5" s="253"/>
+      <c r="OR5" s="253"/>
+      <c r="OS5" s="253"/>
+      <c r="OT5" s="254"/>
     </row>
-    <row r="6" spans="3:379" x14ac:dyDescent="0.4">
-      <c r="C6" s="267"/>
-      <c r="D6" s="267"/>
-      <c r="AC6" s="267"/>
-      <c r="AD6" s="267"/>
+    <row r="6" spans="3:410" x14ac:dyDescent="0.4">
+      <c r="C6" s="269"/>
+      <c r="D6" s="269"/>
+      <c r="AC6" s="269"/>
+      <c r="AD6" s="269"/>
       <c r="AN6" s="1"/>
-      <c r="AR6" s="267"/>
-      <c r="AS6" s="267"/>
-      <c r="AT6" s="257" t="s">
+      <c r="AR6" s="269"/>
+      <c r="AS6" s="269"/>
+      <c r="AT6" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="AU6" s="258"/>
-      <c r="AV6" s="259" t="s">
+      <c r="AU6" s="260"/>
+      <c r="AV6" s="261" t="s">
         <v>16</v>
       </c>
-      <c r="AW6" s="258"/>
-      <c r="AX6" s="265" t="s">
+      <c r="AW6" s="260"/>
+      <c r="AX6" s="267" t="s">
         <v>14</v>
       </c>
-      <c r="AY6" s="259"/>
-      <c r="AZ6" s="258"/>
-      <c r="BA6" s="259">
+      <c r="AY6" s="261"/>
+      <c r="AZ6" s="260"/>
+      <c r="BA6" s="261">
         <v>1</v>
       </c>
-      <c r="BB6" s="258"/>
-      <c r="BC6" s="259">
+      <c r="BB6" s="260"/>
+      <c r="BC6" s="261">
         <v>0</v>
       </c>
-      <c r="BD6" s="260"/>
+      <c r="BD6" s="262"/>
       <c r="BE6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="BF6" s="1"/>
-      <c r="JO6" s="267"/>
-      <c r="JP6" s="267"/>
-      <c r="JQ6" s="267"/>
-      <c r="JR6" s="267"/>
-      <c r="JS6" s="267"/>
-      <c r="JT6" s="267"/>
-      <c r="JU6" s="267"/>
+      <c r="JO6" s="269"/>
+      <c r="JP6" s="269"/>
+      <c r="JQ6" s="269"/>
+      <c r="JR6" s="269"/>
+      <c r="JS6" s="269"/>
+      <c r="JT6" s="269"/>
+      <c r="JU6" s="269"/>
     </row>
-    <row r="7" spans="3:379" x14ac:dyDescent="0.4">
-      <c r="AT7" s="255" t="s">
+    <row r="7" spans="3:410" x14ac:dyDescent="0.4">
+      <c r="AT7" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="AU7" s="261"/>
+      <c r="AU7" s="263"/>
       <c r="AW7" s="5"/>
-      <c r="AX7" s="266"/>
+      <c r="AX7" s="268"/>
       <c r="AY7" s="40"/>
-      <c r="AZ7" s="261"/>
+      <c r="AZ7" s="263"/>
       <c r="BB7" s="5"/>
       <c r="BC7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="BD7" s="256"/>
+      <c r="BD7" s="258"/>
     </row>
-    <row r="9" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:410" x14ac:dyDescent="0.4">
       <c r="AQ9" s="4"/>
     </row>
-    <row r="10" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:410" x14ac:dyDescent="0.4">
       <c r="AQ10" s="4"/>
     </row>
-    <row r="11" spans="3:379" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:410" x14ac:dyDescent="0.4">
       <c r="AQ11" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="178">
+  <mergeCells count="191">
+    <mergeCell ref="NR5:NT5"/>
+    <mergeCell ref="NU5:NZ5"/>
+    <mergeCell ref="OA5:OE5"/>
+    <mergeCell ref="OF5:OJ5"/>
+    <mergeCell ref="OK5:OO5"/>
+    <mergeCell ref="OP4:OT4"/>
+    <mergeCell ref="OP5:OT5"/>
+    <mergeCell ref="NR4:NT4"/>
+    <mergeCell ref="NU4:NZ4"/>
+    <mergeCell ref="OA4:OE4"/>
+    <mergeCell ref="OF4:OJ4"/>
+    <mergeCell ref="OK4:OO4"/>
+    <mergeCell ref="NR3:OT3"/>
+    <mergeCell ref="KM5:KQ5"/>
     <mergeCell ref="JO6:JU6"/>
     <mergeCell ref="JW4:JZ4"/>
     <mergeCell ref="KA4:KD4"/>
@@ -34984,12 +36465,6 @@
     <mergeCell ref="KA5:KD5"/>
     <mergeCell ref="KE5:KH5"/>
     <mergeCell ref="KI5:KL5"/>
-    <mergeCell ref="JO3:LA3"/>
-    <mergeCell ref="GQ4:GX4"/>
-    <mergeCell ref="GF5:GH5"/>
-    <mergeCell ref="GI5:GM5"/>
-    <mergeCell ref="GN5:GP5"/>
-    <mergeCell ref="KM4:KQ4"/>
     <mergeCell ref="IK3:JK3"/>
     <mergeCell ref="IC4:IG4"/>
     <mergeCell ref="IC5:IG5"/>
@@ -35029,7 +36504,8 @@
     <mergeCell ref="LM5:LQ5"/>
     <mergeCell ref="LR5:LV5"/>
     <mergeCell ref="LW5:MA5"/>
-    <mergeCell ref="KM5:KQ5"/>
+    <mergeCell ref="JO3:LA3"/>
+    <mergeCell ref="KM4:KQ4"/>
     <mergeCell ref="GQ5:GX5"/>
     <mergeCell ref="FX5:GB5"/>
     <mergeCell ref="FN4:FP4"/>
@@ -35040,6 +36516,11 @@
     <mergeCell ref="EK4:EN4"/>
     <mergeCell ref="DJ4:DM4"/>
     <mergeCell ref="DN4:DT4"/>
+    <mergeCell ref="FD4:FF4"/>
+    <mergeCell ref="GQ4:GX4"/>
+    <mergeCell ref="GF5:GH5"/>
+    <mergeCell ref="GI5:GM5"/>
+    <mergeCell ref="GN5:GP5"/>
     <mergeCell ref="IK4:IM4"/>
     <mergeCell ref="IN4:IR4"/>
     <mergeCell ref="IS4:IW4"/>
@@ -35052,8 +36533,6 @@
     <mergeCell ref="IX5:JA5"/>
     <mergeCell ref="JB5:JF5"/>
     <mergeCell ref="JG5:JK5"/>
-    <mergeCell ref="FD4:FF4"/>
-    <mergeCell ref="EH3:GB3"/>
     <mergeCell ref="FX4:GB4"/>
     <mergeCell ref="DU5:DY5"/>
     <mergeCell ref="DZ5:ED5"/>
@@ -35092,6 +36571,7 @@
     <mergeCell ref="DB5:DE5"/>
     <mergeCell ref="CX4:DA4"/>
     <mergeCell ref="DB4:DE4"/>
+    <mergeCell ref="CU4:CW4"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="U4:Y4"/>
     <mergeCell ref="U5:Y5"/>
@@ -35129,7 +36609,6 @@
     <mergeCell ref="AT7:AU7"/>
     <mergeCell ref="AT2:BD2"/>
     <mergeCell ref="AX6:AZ7"/>
-    <mergeCell ref="CU4:CW4"/>
     <mergeCell ref="CU5:CW5"/>
     <mergeCell ref="JT4:JV4"/>
     <mergeCell ref="JT5:JV5"/>
@@ -35153,6 +36632,7 @@
     <mergeCell ref="GN4:GP4"/>
     <mergeCell ref="FQ5:FW5"/>
     <mergeCell ref="FA4:FC4"/>
+    <mergeCell ref="EH3:GB3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35161,44 +36641,44 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1C6584-A140-46FB-9B22-984E9B48BC21}">
-  <dimension ref="C2:IN7"/>
+  <dimension ref="C2:JK7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="468" width="3.625" customWidth="1"/>
+    <col min="1" max="491" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:248" x14ac:dyDescent="0.4">
-      <c r="HX2" s="8">
+    <row r="2" spans="3:271" x14ac:dyDescent="0.4">
+      <c r="IU2" s="8">
         <v>15</v>
       </c>
-      <c r="HY2" s="6">
+      <c r="IV2" s="6">
         <v>14</v>
       </c>
-      <c r="HZ2" s="262" t="s">
+      <c r="IW2" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="IA2" s="263"/>
-      <c r="IB2" s="263"/>
-      <c r="IC2" s="263"/>
-      <c r="ID2" s="263"/>
-      <c r="IE2" s="263"/>
-      <c r="IF2" s="263"/>
-      <c r="IG2" s="263"/>
-      <c r="IH2" s="263"/>
-      <c r="II2" s="263"/>
-      <c r="IJ2" s="264"/>
-      <c r="IK2" s="6">
+      <c r="IX2" s="265"/>
+      <c r="IY2" s="265"/>
+      <c r="IZ2" s="265"/>
+      <c r="JA2" s="265"/>
+      <c r="JB2" s="265"/>
+      <c r="JC2" s="265"/>
+      <c r="JD2" s="265"/>
+      <c r="JE2" s="265"/>
+      <c r="JF2" s="265"/>
+      <c r="JG2" s="266"/>
+      <c r="JH2" s="6">
         <v>1</v>
       </c>
-      <c r="IL2" s="7">
+      <c r="JI2" s="7">
         <v>0</v>
       </c>
-      <c r="IM2" s="255" t="s">
+      <c r="JJ2" s="257" t="s">
         <v>12</v>
       </c>
-      <c r="IN2" s="40"/>
+      <c r="JK2" s="40"/>
     </row>
-    <row r="3" spans="3:248" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:271" x14ac:dyDescent="0.4">
       <c r="C3" s="279" t="s">
         <v>9</v>
       </c>
@@ -35402,35 +36882,35 @@
       <c r="GT3" s="278"/>
       <c r="GU3" s="9"/>
       <c r="GV3" s="9"/>
-      <c r="GW3" s="363" t="s">
+      <c r="GW3" s="280" t="s">
         <v>619</v>
       </c>
-      <c r="GX3" s="364"/>
-      <c r="GY3" s="364"/>
-      <c r="GZ3" s="364"/>
-      <c r="HA3" s="364"/>
-      <c r="HB3" s="364"/>
-      <c r="HC3" s="364"/>
-      <c r="HD3" s="364"/>
-      <c r="HE3" s="364"/>
-      <c r="HF3" s="364"/>
-      <c r="HG3" s="364"/>
-      <c r="HH3" s="364"/>
-      <c r="HI3" s="364"/>
-      <c r="HJ3" s="364"/>
-      <c r="HK3" s="364"/>
-      <c r="HL3" s="364"/>
-      <c r="HM3" s="364"/>
-      <c r="HN3" s="364"/>
-      <c r="HO3" s="364"/>
-      <c r="HP3" s="364"/>
-      <c r="HQ3" s="364"/>
-      <c r="HR3" s="364"/>
-      <c r="HS3" s="364"/>
-      <c r="HT3" s="364"/>
-      <c r="HU3" s="365"/>
+      <c r="GX3" s="281"/>
+      <c r="GY3" s="281"/>
+      <c r="GZ3" s="281"/>
+      <c r="HA3" s="281"/>
+      <c r="HB3" s="281"/>
+      <c r="HC3" s="281"/>
+      <c r="HD3" s="281"/>
+      <c r="HE3" s="281"/>
+      <c r="HF3" s="281"/>
+      <c r="HG3" s="281"/>
+      <c r="HH3" s="281"/>
+      <c r="HI3" s="281"/>
+      <c r="HJ3" s="281"/>
+      <c r="HK3" s="281"/>
+      <c r="HL3" s="281"/>
+      <c r="HM3" s="281"/>
+      <c r="HN3" s="281"/>
+      <c r="HO3" s="281"/>
+      <c r="HP3" s="281"/>
+      <c r="HQ3" s="281"/>
+      <c r="HR3" s="281"/>
+      <c r="HS3" s="281"/>
+      <c r="HT3" s="281"/>
+      <c r="HU3" s="282"/>
       <c r="HX3" s="278" t="s">
-        <v>386</v>
+        <v>625</v>
       </c>
       <c r="HY3" s="278"/>
       <c r="HZ3" s="278"/>
@@ -35446,8 +36926,31 @@
       <c r="IJ3" s="278"/>
       <c r="IK3" s="278"/>
       <c r="IL3" s="278"/>
+      <c r="IM3" s="278"/>
+      <c r="IN3" s="278"/>
+      <c r="IO3" s="278"/>
+      <c r="IP3" s="278"/>
+      <c r="IQ3" s="278"/>
+      <c r="IR3" s="278"/>
+      <c r="IU3" s="278" t="s">
+        <v>386</v>
+      </c>
+      <c r="IV3" s="278"/>
+      <c r="IW3" s="278"/>
+      <c r="IX3" s="278"/>
+      <c r="IY3" s="278"/>
+      <c r="IZ3" s="278"/>
+      <c r="JA3" s="278"/>
+      <c r="JB3" s="278"/>
+      <c r="JC3" s="278"/>
+      <c r="JD3" s="278"/>
+      <c r="JE3" s="278"/>
+      <c r="JF3" s="278"/>
+      <c r="JG3" s="278"/>
+      <c r="JH3" s="278"/>
+      <c r="JI3" s="278"/>
     </row>
-    <row r="4" spans="3:248" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:271" x14ac:dyDescent="0.4">
       <c r="C4" s="35" t="s">
         <v>42</v>
       </c>
@@ -35748,25 +37251,56 @@
       <c r="HS4" s="38"/>
       <c r="HT4" s="38"/>
       <c r="HU4" s="37"/>
-      <c r="HX4" s="36"/>
-      <c r="HY4" s="37"/>
-      <c r="HZ4" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="IA4" s="35"/>
+      <c r="HX4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="HY4" s="39"/>
+      <c r="HZ4" s="39"/>
+      <c r="IA4" s="35" t="s">
+        <v>45</v>
+      </c>
       <c r="IB4" s="35"/>
       <c r="IC4" s="35"/>
       <c r="ID4" s="35"/>
-      <c r="IE4" s="35"/>
+      <c r="IE4" s="35" t="s">
+        <v>46</v>
+      </c>
       <c r="IF4" s="35"/>
       <c r="IG4" s="35"/>
       <c r="IH4" s="35"/>
-      <c r="II4" s="35"/>
+      <c r="II4" s="35" t="s">
+        <v>2</v>
+      </c>
       <c r="IJ4" s="35"/>
-      <c r="IK4" s="36"/>
-      <c r="IL4" s="37"/>
+      <c r="IK4" s="35"/>
+      <c r="IL4" s="35"/>
+      <c r="IM4" s="35"/>
+      <c r="IN4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="IO4" s="35"/>
+      <c r="IP4" s="35"/>
+      <c r="IQ4" s="35"/>
+      <c r="IR4" s="35"/>
+      <c r="IU4" s="36"/>
+      <c r="IV4" s="37"/>
+      <c r="IW4" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="IX4" s="35"/>
+      <c r="IY4" s="35"/>
+      <c r="IZ4" s="35"/>
+      <c r="JA4" s="35"/>
+      <c r="JB4" s="35"/>
+      <c r="JC4" s="35"/>
+      <c r="JD4" s="35"/>
+      <c r="JE4" s="35"/>
+      <c r="JF4" s="35"/>
+      <c r="JG4" s="35"/>
+      <c r="JH4" s="36"/>
+      <c r="JI4" s="37"/>
     </row>
-    <row r="5" spans="3:248" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:271" x14ac:dyDescent="0.4">
       <c r="C5" s="35" t="s">
         <v>6</v>
       </c>
@@ -36078,76 +37612,118 @@
       <c r="HS5" s="38"/>
       <c r="HT5" s="38"/>
       <c r="HU5" s="37"/>
-      <c r="HX5" s="36"/>
-      <c r="HY5" s="37"/>
-      <c r="HZ5" s="36" t="s">
+      <c r="HX5" s="39" t="str">
+        <f>128-24-1-1-16 &amp; " bits"</f>
+        <v>86 bits</v>
+      </c>
+      <c r="HY5" s="39"/>
+      <c r="HZ5" s="39"/>
+      <c r="IA5" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="IB5" s="35"/>
+      <c r="IC5" s="35"/>
+      <c r="ID5" s="35"/>
+      <c r="IE5" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="IF5" s="35"/>
+      <c r="IG5" s="35"/>
+      <c r="IH5" s="35"/>
+      <c r="II5" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="IJ5" s="35"/>
+      <c r="IK5" s="35"/>
+      <c r="IL5" s="35"/>
+      <c r="IM5" s="35"/>
+      <c r="IN5" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="IO5" s="35"/>
+      <c r="IP5" s="35"/>
+      <c r="IQ5" s="35"/>
+      <c r="IR5" s="35"/>
+      <c r="IU5" s="36"/>
+      <c r="IV5" s="37"/>
+      <c r="IW5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="IA5" s="38"/>
-      <c r="IB5" s="38"/>
-      <c r="IC5" s="38"/>
-      <c r="ID5" s="38"/>
-      <c r="IE5" s="38"/>
-      <c r="IF5" s="38"/>
-      <c r="IG5" s="38"/>
-      <c r="IH5" s="38"/>
-      <c r="II5" s="38"/>
-      <c r="IJ5" s="37"/>
-      <c r="IK5" s="36"/>
-      <c r="IL5" s="37"/>
+      <c r="IX5" s="38"/>
+      <c r="IY5" s="38"/>
+      <c r="IZ5" s="38"/>
+      <c r="JA5" s="38"/>
+      <c r="JB5" s="38"/>
+      <c r="JC5" s="38"/>
+      <c r="JD5" s="38"/>
+      <c r="JE5" s="38"/>
+      <c r="JF5" s="38"/>
+      <c r="JG5" s="37"/>
+      <c r="JH5" s="36"/>
+      <c r="JI5" s="37"/>
     </row>
-    <row r="6" spans="3:248" x14ac:dyDescent="0.4">
-      <c r="GW6" s="267"/>
-      <c r="GX6" s="267"/>
+    <row r="6" spans="3:271" x14ac:dyDescent="0.4">
+      <c r="GW6" s="269"/>
+      <c r="GX6" s="269"/>
       <c r="HC6" s="144"/>
       <c r="HD6" s="144"/>
       <c r="HU6" s="1"/>
-      <c r="HV6" s="366"/>
-      <c r="HX6" s="267"/>
-      <c r="HY6" s="267"/>
-      <c r="HZ6" s="257" t="s">
+      <c r="IU6" s="269"/>
+      <c r="IV6" s="269"/>
+      <c r="IW6" s="259" t="s">
         <v>15</v>
       </c>
-      <c r="IA6" s="258"/>
-      <c r="IB6" s="259" t="s">
+      <c r="IX6" s="260"/>
+      <c r="IY6" s="261" t="s">
         <v>16</v>
       </c>
-      <c r="IC6" s="258"/>
-      <c r="ID6" s="265" t="s">
+      <c r="IZ6" s="260"/>
+      <c r="JA6" s="267" t="s">
         <v>14</v>
       </c>
-      <c r="IE6" s="259"/>
-      <c r="IF6" s="258"/>
-      <c r="IG6" s="259">
+      <c r="JB6" s="261"/>
+      <c r="JC6" s="260"/>
+      <c r="JD6" s="261">
         <v>1</v>
       </c>
-      <c r="IH6" s="258"/>
-      <c r="II6" s="259">
+      <c r="JE6" s="260"/>
+      <c r="JF6" s="261">
         <v>0</v>
       </c>
-      <c r="IJ6" s="260"/>
-      <c r="IK6" s="3" t="s">
+      <c r="JG6" s="262"/>
+      <c r="JH6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="IL6" s="1"/>
+      <c r="JI6" s="1"/>
     </row>
-    <row r="7" spans="3:248" x14ac:dyDescent="0.4">
-      <c r="HZ7" s="255" t="s">
+    <row r="7" spans="3:271" x14ac:dyDescent="0.4">
+      <c r="IW7" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="IA7" s="261"/>
-      <c r="IC7" s="5"/>
-      <c r="ID7" s="266"/>
-      <c r="IE7" s="40"/>
-      <c r="IF7" s="261"/>
-      <c r="IH7" s="5"/>
-      <c r="II7" s="40" t="s">
+      <c r="IX7" s="263"/>
+      <c r="IZ7" s="5"/>
+      <c r="JA7" s="268"/>
+      <c r="JB7" s="40"/>
+      <c r="JC7" s="263"/>
+      <c r="JE7" s="5"/>
+      <c r="JF7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="IJ7" s="256"/>
+      <c r="JG7" s="258"/>
     </row>
   </sheetData>
-  <mergeCells count="125">
+  <mergeCells count="136">
+    <mergeCell ref="HX3:IR3"/>
+    <mergeCell ref="HX4:HZ4"/>
+    <mergeCell ref="IA4:ID4"/>
+    <mergeCell ref="IE4:IH4"/>
+    <mergeCell ref="II4:IM4"/>
+    <mergeCell ref="IN4:IR4"/>
+    <mergeCell ref="HX5:HZ5"/>
+    <mergeCell ref="IA5:ID5"/>
+    <mergeCell ref="IE5:IH5"/>
+    <mergeCell ref="II5:IM5"/>
+    <mergeCell ref="IN5:IR5"/>
     <mergeCell ref="GW5:GY5"/>
     <mergeCell ref="GZ5:HC5"/>
     <mergeCell ref="HD5:HG5"/>
@@ -36212,12 +37788,12 @@
     <mergeCell ref="DC4:DG4"/>
     <mergeCell ref="CR5:CT5"/>
     <mergeCell ref="CU5:CX5"/>
-    <mergeCell ref="HZ2:IJ2"/>
-    <mergeCell ref="IM2:IN2"/>
-    <mergeCell ref="HX3:IL3"/>
-    <mergeCell ref="HZ4:IJ4"/>
-    <mergeCell ref="IK4:IL4"/>
-    <mergeCell ref="HX4:HY4"/>
+    <mergeCell ref="IW2:JG2"/>
+    <mergeCell ref="JJ2:JK2"/>
+    <mergeCell ref="IU3:JI3"/>
+    <mergeCell ref="IW4:JG4"/>
+    <mergeCell ref="JH4:JI4"/>
+    <mergeCell ref="IU4:IV4"/>
     <mergeCell ref="EA5:EC5"/>
     <mergeCell ref="ED5:EG5"/>
     <mergeCell ref="EH5:EL5"/>
@@ -36231,17 +37807,17 @@
     <mergeCell ref="ER4:EU4"/>
     <mergeCell ref="BE4:BJ4"/>
     <mergeCell ref="BE5:BJ5"/>
-    <mergeCell ref="IK5:IL5"/>
-    <mergeCell ref="HX6:HY6"/>
-    <mergeCell ref="HZ6:IA6"/>
-    <mergeCell ref="IB6:IC6"/>
-    <mergeCell ref="ID6:IF7"/>
-    <mergeCell ref="IG6:IH6"/>
-    <mergeCell ref="II6:IJ6"/>
-    <mergeCell ref="HZ7:IA7"/>
-    <mergeCell ref="II7:IJ7"/>
-    <mergeCell ref="HX5:HY5"/>
-    <mergeCell ref="HZ5:IJ5"/>
+    <mergeCell ref="JH5:JI5"/>
+    <mergeCell ref="IU6:IV6"/>
+    <mergeCell ref="IW6:IX6"/>
+    <mergeCell ref="IY6:IZ6"/>
+    <mergeCell ref="JA6:JC7"/>
+    <mergeCell ref="JD6:JE6"/>
+    <mergeCell ref="JF6:JG6"/>
+    <mergeCell ref="IW7:IX7"/>
+    <mergeCell ref="JF7:JG7"/>
+    <mergeCell ref="IU5:IV5"/>
+    <mergeCell ref="IW5:JG5"/>
     <mergeCell ref="EA4:EC4"/>
     <mergeCell ref="ED4:EG4"/>
     <mergeCell ref="DT4:DX4"/>
@@ -36293,3082 +37869,3082 @@
   <sheetData>
     <row r="4" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F4" s="2"/>
-      <c r="G4" s="300" t="str">
+      <c r="G4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="H4" s="40"/>
       <c r="I4" s="40"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="300" t="str">
+      <c r="J4" s="258"/>
+      <c r="K4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
-      <c r="N4" s="256"/>
-      <c r="O4" s="300" t="str">
+      <c r="N4" s="258"/>
+      <c r="O4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
-      <c r="R4" s="256"/>
-      <c r="S4" s="300" t="str">
+      <c r="R4" s="258"/>
+      <c r="S4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="T4" s="40"/>
       <c r="U4" s="40"/>
-      <c r="V4" s="256"/>
+      <c r="V4" s="258"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="300" t="str">
+      <c r="AD4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="AE4" s="40"/>
       <c r="AF4" s="40"/>
-      <c r="AG4" s="256"/>
-      <c r="AH4" s="300" t="str">
+      <c r="AG4" s="258"/>
+      <c r="AH4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="AI4" s="40"/>
       <c r="AJ4" s="40"/>
-      <c r="AK4" s="256"/>
-      <c r="AL4" s="300" t="str">
+      <c r="AK4" s="258"/>
+      <c r="AL4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="AM4" s="40"/>
       <c r="AN4" s="40"/>
-      <c r="AO4" s="256"/>
-      <c r="AP4" s="300" t="str">
+      <c r="AO4" s="258"/>
+      <c r="AP4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="AQ4" s="40"/>
       <c r="AR4" s="40"/>
-      <c r="AS4" s="256"/>
+      <c r="AS4" s="258"/>
       <c r="AV4" s="13"/>
       <c r="AW4" s="13"/>
       <c r="AX4" s="13"/>
       <c r="AY4" s="2"/>
-      <c r="AZ4" s="300" t="str">
+      <c r="AZ4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="BA4" s="40"/>
       <c r="BB4" s="40"/>
-      <c r="BC4" s="256"/>
-      <c r="BD4" s="300" t="str">
+      <c r="BC4" s="258"/>
+      <c r="BD4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="BE4" s="40"/>
       <c r="BF4" s="40"/>
-      <c r="BG4" s="256"/>
-      <c r="BH4" s="300" t="str">
+      <c r="BG4" s="258"/>
+      <c r="BH4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="BI4" s="40"/>
       <c r="BJ4" s="40"/>
-      <c r="BK4" s="256"/>
-      <c r="BL4" s="300" t="str">
+      <c r="BK4" s="258"/>
+      <c r="BL4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="BM4" s="40"/>
       <c r="BN4" s="40"/>
-      <c r="BO4" s="256"/>
+      <c r="BO4" s="258"/>
       <c r="BT4" s="2"/>
-      <c r="BU4" s="300" t="str">
+      <c r="BU4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="BV4" s="40"/>
       <c r="BW4" s="40"/>
-      <c r="BX4" s="256"/>
-      <c r="BY4" s="300" t="str">
+      <c r="BX4" s="258"/>
+      <c r="BY4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="BZ4" s="40"/>
       <c r="CA4" s="40"/>
-      <c r="CB4" s="256"/>
-      <c r="CC4" s="300" t="str">
+      <c r="CB4" s="258"/>
+      <c r="CC4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="CD4" s="40"/>
       <c r="CE4" s="40"/>
-      <c r="CF4" s="256"/>
-      <c r="CG4" s="300" t="str">
+      <c r="CF4" s="258"/>
+      <c r="CG4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="CH4" s="40"/>
       <c r="CI4" s="40"/>
-      <c r="CJ4" s="256"/>
+      <c r="CJ4" s="258"/>
       <c r="CM4" s="13"/>
       <c r="CN4" s="13"/>
       <c r="CO4" s="13"/>
       <c r="CP4" s="2"/>
-      <c r="CQ4" s="300" t="str">
+      <c r="CQ4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="CR4" s="40"/>
       <c r="CS4" s="40"/>
-      <c r="CT4" s="256"/>
-      <c r="CU4" s="300" t="str">
+      <c r="CT4" s="258"/>
+      <c r="CU4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="CV4" s="40"/>
       <c r="CW4" s="40"/>
-      <c r="CX4" s="256"/>
-      <c r="CY4" s="300" t="str">
+      <c r="CX4" s="258"/>
+      <c r="CY4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="CZ4" s="40"/>
       <c r="DA4" s="40"/>
-      <c r="DB4" s="256"/>
-      <c r="DC4" s="300" t="str">
+      <c r="DB4" s="258"/>
+      <c r="DC4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="DD4" s="40"/>
       <c r="DE4" s="40"/>
-      <c r="DF4" s="256"/>
-      <c r="DG4" s="300" t="str">
+      <c r="DF4" s="258"/>
+      <c r="DG4" s="303" t="str">
         <f>"+4"</f>
         <v>+4</v>
       </c>
       <c r="DH4" s="40"/>
       <c r="DI4" s="40"/>
-      <c r="DJ4" s="256"/>
-      <c r="DK4" s="300" t="str">
+      <c r="DJ4" s="258"/>
+      <c r="DK4" s="303" t="str">
         <f>"+5"</f>
         <v>+5</v>
       </c>
       <c r="DL4" s="40"/>
       <c r="DM4" s="40"/>
-      <c r="DN4" s="256"/>
-      <c r="DO4" s="300" t="str">
+      <c r="DN4" s="258"/>
+      <c r="DO4" s="303" t="str">
         <f>"+6"</f>
         <v>+6</v>
       </c>
       <c r="DP4" s="40"/>
       <c r="DQ4" s="40"/>
-      <c r="DR4" s="256"/>
-      <c r="DS4" s="300" t="str">
+      <c r="DR4" s="258"/>
+      <c r="DS4" s="303" t="str">
         <f>"+7"</f>
         <v>+7</v>
       </c>
       <c r="DT4" s="40"/>
       <c r="DU4" s="40"/>
-      <c r="DV4" s="256"/>
+      <c r="DV4" s="258"/>
       <c r="DZ4" s="13"/>
       <c r="EA4" s="13"/>
       <c r="EB4" s="13"/>
       <c r="EC4" s="2"/>
-      <c r="ED4" s="300" t="str">
+      <c r="ED4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="EE4" s="40"/>
       <c r="EF4" s="40"/>
-      <c r="EG4" s="256"/>
-      <c r="EH4" s="300" t="str">
+      <c r="EG4" s="258"/>
+      <c r="EH4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="EI4" s="40"/>
       <c r="EJ4" s="40"/>
-      <c r="EK4" s="256"/>
-      <c r="EL4" s="300" t="str">
+      <c r="EK4" s="258"/>
+      <c r="EL4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="EM4" s="40"/>
       <c r="EN4" s="40"/>
-      <c r="EO4" s="256"/>
-      <c r="EP4" s="300" t="str">
+      <c r="EO4" s="258"/>
+      <c r="EP4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="EQ4" s="40"/>
       <c r="ER4" s="40"/>
-      <c r="ES4" s="256"/>
-      <c r="ET4" s="300" t="str">
+      <c r="ES4" s="258"/>
+      <c r="ET4" s="303" t="str">
         <f>"+4"</f>
         <v>+4</v>
       </c>
       <c r="EU4" s="40"/>
       <c r="EV4" s="40"/>
-      <c r="EW4" s="256"/>
-      <c r="EX4" s="300" t="str">
+      <c r="EW4" s="258"/>
+      <c r="EX4" s="303" t="str">
         <f>"+5"</f>
         <v>+5</v>
       </c>
       <c r="EY4" s="40"/>
       <c r="EZ4" s="40"/>
-      <c r="FA4" s="256"/>
-      <c r="FB4" s="300" t="str">
+      <c r="FA4" s="258"/>
+      <c r="FB4" s="303" t="str">
         <f>"+6"</f>
         <v>+6</v>
       </c>
       <c r="FC4" s="40"/>
       <c r="FD4" s="40"/>
-      <c r="FE4" s="256"/>
-      <c r="FF4" s="300" t="str">
+      <c r="FE4" s="258"/>
+      <c r="FF4" s="303" t="str">
         <f>"+7"</f>
         <v>+7</v>
       </c>
       <c r="FG4" s="40"/>
       <c r="FH4" s="40"/>
-      <c r="FI4" s="256"/>
+      <c r="FI4" s="258"/>
       <c r="FR4" s="2"/>
-      <c r="FS4" s="300" t="str">
+      <c r="FS4" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="FT4" s="40"/>
       <c r="FU4" s="40"/>
-      <c r="FV4" s="256"/>
-      <c r="FW4" s="300" t="str">
+      <c r="FV4" s="258"/>
+      <c r="FW4" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="FX4" s="40"/>
       <c r="FY4" s="40"/>
-      <c r="FZ4" s="256"/>
-      <c r="GA4" s="300" t="str">
+      <c r="FZ4" s="258"/>
+      <c r="GA4" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="GB4" s="40"/>
       <c r="GC4" s="40"/>
-      <c r="GD4" s="256"/>
-      <c r="GE4" s="300" t="str">
+      <c r="GD4" s="258"/>
+      <c r="GE4" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="GF4" s="40"/>
       <c r="GG4" s="40"/>
-      <c r="GH4" s="256"/>
-      <c r="GI4" s="300" t="str">
+      <c r="GH4" s="258"/>
+      <c r="GI4" s="303" t="str">
         <f>"+4"</f>
         <v>+4</v>
       </c>
       <c r="GJ4" s="40"/>
       <c r="GK4" s="40"/>
-      <c r="GL4" s="256"/>
-      <c r="GM4" s="300" t="str">
+      <c r="GL4" s="258"/>
+      <c r="GM4" s="303" t="str">
         <f>"+5"</f>
         <v>+5</v>
       </c>
       <c r="GN4" s="40"/>
       <c r="GO4" s="40"/>
-      <c r="GP4" s="256"/>
-      <c r="GQ4" s="300" t="str">
+      <c r="GP4" s="258"/>
+      <c r="GQ4" s="303" t="str">
         <f>"+6"</f>
         <v>+6</v>
       </c>
       <c r="GR4" s="40"/>
       <c r="GS4" s="40"/>
-      <c r="GT4" s="256"/>
-      <c r="GU4" s="300" t="str">
+      <c r="GT4" s="258"/>
+      <c r="GU4" s="303" t="str">
         <f>"+7"</f>
         <v>+7</v>
       </c>
       <c r="GV4" s="40"/>
       <c r="GW4" s="40"/>
-      <c r="GX4" s="256"/>
-      <c r="GY4" s="300" t="str">
+      <c r="GX4" s="258"/>
+      <c r="GY4" s="303" t="str">
         <f>"+8"</f>
         <v>+8</v>
       </c>
       <c r="GZ4" s="40"/>
       <c r="HA4" s="40"/>
-      <c r="HB4" s="256"/>
-      <c r="HC4" s="300" t="str">
+      <c r="HB4" s="258"/>
+      <c r="HC4" s="303" t="str">
         <f>"+9"</f>
         <v>+9</v>
       </c>
       <c r="HD4" s="40"/>
       <c r="HE4" s="40"/>
-      <c r="HF4" s="256"/>
-      <c r="HG4" s="300" t="str">
+      <c r="HF4" s="258"/>
+      <c r="HG4" s="303" t="str">
         <f>"+10"</f>
         <v>+10</v>
       </c>
       <c r="HH4" s="40"/>
       <c r="HI4" s="40"/>
-      <c r="HJ4" s="256"/>
-      <c r="HK4" s="300" t="str">
+      <c r="HJ4" s="258"/>
+      <c r="HK4" s="303" t="str">
         <f>"+11"</f>
         <v>+11</v>
       </c>
       <c r="HL4" s="40"/>
       <c r="HM4" s="40"/>
-      <c r="HN4" s="256"/>
-      <c r="HO4" s="300" t="str">
+      <c r="HN4" s="258"/>
+      <c r="HO4" s="303" t="str">
         <f>"+12"</f>
         <v>+12</v>
       </c>
       <c r="HP4" s="40"/>
       <c r="HQ4" s="40"/>
-      <c r="HR4" s="256"/>
-      <c r="HS4" s="300" t="str">
+      <c r="HR4" s="258"/>
+      <c r="HS4" s="303" t="str">
         <f>"+13"</f>
         <v>+13</v>
       </c>
       <c r="HT4" s="40"/>
       <c r="HU4" s="40"/>
-      <c r="HV4" s="256"/>
-      <c r="HW4" s="300" t="str">
+      <c r="HV4" s="258"/>
+      <c r="HW4" s="303" t="str">
         <f>"+14"</f>
         <v>+14</v>
       </c>
       <c r="HX4" s="40"/>
       <c r="HY4" s="40"/>
-      <c r="HZ4" s="256"/>
-      <c r="IA4" s="300" t="str">
+      <c r="HZ4" s="258"/>
+      <c r="IA4" s="303" t="str">
         <f>"+15"</f>
         <v>+15</v>
       </c>
       <c r="IB4" s="40"/>
       <c r="IC4" s="40"/>
-      <c r="ID4" s="256"/>
+      <c r="ID4" s="258"/>
     </row>
     <row r="5" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="D5" s="292" t="s">
+      <c r="D5" s="295" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="292"/>
+      <c r="E5" s="295"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="307" t="s">
+      <c r="G5" s="310" t="s">
         <v>401</v>
       </c>
-      <c r="H5" s="287"/>
-      <c r="I5" s="287"/>
-      <c r="J5" s="288"/>
-      <c r="K5" s="289" t="s">
+      <c r="H5" s="290"/>
+      <c r="I5" s="290"/>
+      <c r="J5" s="291"/>
+      <c r="K5" s="292" t="s">
         <v>403</v>
       </c>
-      <c r="L5" s="289"/>
-      <c r="M5" s="289"/>
-      <c r="N5" s="289"/>
-      <c r="O5" s="289"/>
-      <c r="P5" s="289"/>
-      <c r="Q5" s="289"/>
-      <c r="R5" s="289"/>
-      <c r="S5" s="289"/>
-      <c r="T5" s="289"/>
-      <c r="U5" s="289"/>
-      <c r="V5" s="290"/>
-      <c r="Z5" s="285" t="s">
+      <c r="L5" s="292"/>
+      <c r="M5" s="292"/>
+      <c r="N5" s="292"/>
+      <c r="O5" s="292"/>
+      <c r="P5" s="292"/>
+      <c r="Q5" s="292"/>
+      <c r="R5" s="292"/>
+      <c r="S5" s="292"/>
+      <c r="T5" s="292"/>
+      <c r="U5" s="292"/>
+      <c r="V5" s="293"/>
+      <c r="Z5" s="288" t="s">
         <v>122</v>
       </c>
-      <c r="AA5" s="285"/>
-      <c r="AB5" s="285"/>
+      <c r="AA5" s="288"/>
+      <c r="AB5" s="288"/>
       <c r="AC5" s="10"/>
-      <c r="AD5" s="286" t="s">
+      <c r="AD5" s="289" t="s">
         <v>402</v>
       </c>
-      <c r="AE5" s="287"/>
-      <c r="AF5" s="287"/>
-      <c r="AG5" s="288"/>
-      <c r="AH5" s="289" t="s">
+      <c r="AE5" s="290"/>
+      <c r="AF5" s="290"/>
+      <c r="AG5" s="291"/>
+      <c r="AH5" s="292" t="s">
         <v>403</v>
       </c>
-      <c r="AI5" s="289"/>
-      <c r="AJ5" s="289"/>
-      <c r="AK5" s="289"/>
-      <c r="AL5" s="289"/>
-      <c r="AM5" s="289"/>
-      <c r="AN5" s="289"/>
-      <c r="AO5" s="289"/>
-      <c r="AP5" s="289"/>
-      <c r="AQ5" s="289"/>
-      <c r="AR5" s="289"/>
-      <c r="AS5" s="290"/>
-      <c r="AV5" s="285" t="s">
+      <c r="AI5" s="292"/>
+      <c r="AJ5" s="292"/>
+      <c r="AK5" s="292"/>
+      <c r="AL5" s="292"/>
+      <c r="AM5" s="292"/>
+      <c r="AN5" s="292"/>
+      <c r="AO5" s="292"/>
+      <c r="AP5" s="292"/>
+      <c r="AQ5" s="292"/>
+      <c r="AR5" s="292"/>
+      <c r="AS5" s="293"/>
+      <c r="AV5" s="288" t="s">
         <v>122</v>
       </c>
-      <c r="AW5" s="285"/>
-      <c r="AX5" s="285"/>
+      <c r="AW5" s="288"/>
+      <c r="AX5" s="288"/>
       <c r="AY5" s="10"/>
-      <c r="AZ5" s="286" t="s">
+      <c r="AZ5" s="289" t="s">
         <v>405</v>
       </c>
-      <c r="BA5" s="287"/>
-      <c r="BB5" s="287"/>
-      <c r="BC5" s="288"/>
-      <c r="BD5" s="289" t="s">
+      <c r="BA5" s="290"/>
+      <c r="BB5" s="290"/>
+      <c r="BC5" s="291"/>
+      <c r="BD5" s="292" t="s">
         <v>403</v>
       </c>
-      <c r="BE5" s="289"/>
-      <c r="BF5" s="289"/>
-      <c r="BG5" s="289"/>
-      <c r="BH5" s="289"/>
-      <c r="BI5" s="289"/>
-      <c r="BJ5" s="289"/>
-      <c r="BK5" s="289"/>
-      <c r="BL5" s="289"/>
-      <c r="BM5" s="289"/>
-      <c r="BN5" s="289"/>
-      <c r="BO5" s="290"/>
-      <c r="BR5" s="292" t="s">
+      <c r="BE5" s="292"/>
+      <c r="BF5" s="292"/>
+      <c r="BG5" s="292"/>
+      <c r="BH5" s="292"/>
+      <c r="BI5" s="292"/>
+      <c r="BJ5" s="292"/>
+      <c r="BK5" s="292"/>
+      <c r="BL5" s="292"/>
+      <c r="BM5" s="292"/>
+      <c r="BN5" s="292"/>
+      <c r="BO5" s="293"/>
+      <c r="BR5" s="295" t="s">
         <v>122</v>
       </c>
-      <c r="BS5" s="292"/>
+      <c r="BS5" s="295"/>
       <c r="BT5" s="10"/>
-      <c r="BU5" s="286" t="s">
+      <c r="BU5" s="289" t="s">
         <v>406</v>
       </c>
-      <c r="BV5" s="287"/>
-      <c r="BW5" s="287"/>
-      <c r="BX5" s="288"/>
-      <c r="BY5" s="289" t="s">
+      <c r="BV5" s="290"/>
+      <c r="BW5" s="290"/>
+      <c r="BX5" s="291"/>
+      <c r="BY5" s="292" t="s">
         <v>53</v>
       </c>
-      <c r="BZ5" s="289"/>
-      <c r="CA5" s="289"/>
-      <c r="CB5" s="289"/>
-      <c r="CC5" s="289"/>
-      <c r="CD5" s="289"/>
-      <c r="CE5" s="289"/>
-      <c r="CF5" s="289"/>
-      <c r="CG5" s="289"/>
-      <c r="CH5" s="289"/>
-      <c r="CI5" s="289"/>
-      <c r="CJ5" s="290"/>
-      <c r="CM5" s="285" t="s">
+      <c r="BZ5" s="292"/>
+      <c r="CA5" s="292"/>
+      <c r="CB5" s="292"/>
+      <c r="CC5" s="292"/>
+      <c r="CD5" s="292"/>
+      <c r="CE5" s="292"/>
+      <c r="CF5" s="292"/>
+      <c r="CG5" s="292"/>
+      <c r="CH5" s="292"/>
+      <c r="CI5" s="292"/>
+      <c r="CJ5" s="293"/>
+      <c r="CM5" s="288" t="s">
         <v>122</v>
       </c>
-      <c r="CN5" s="285"/>
-      <c r="CO5" s="285"/>
+      <c r="CN5" s="288"/>
+      <c r="CO5" s="288"/>
       <c r="CP5" s="1"/>
-      <c r="CQ5" s="310" t="s">
+      <c r="CQ5" s="313" t="s">
         <v>407</v>
       </c>
-      <c r="CR5" s="294"/>
-      <c r="CS5" s="294"/>
-      <c r="CT5" s="294"/>
-      <c r="CU5" s="311" t="s">
+      <c r="CR5" s="297"/>
+      <c r="CS5" s="297"/>
+      <c r="CT5" s="297"/>
+      <c r="CU5" s="314" t="s">
         <v>412</v>
       </c>
-      <c r="CV5" s="311"/>
-      <c r="CW5" s="311"/>
-      <c r="CX5" s="311"/>
-      <c r="CY5" s="311"/>
-      <c r="CZ5" s="311"/>
-      <c r="DA5" s="311"/>
-      <c r="DB5" s="311"/>
-      <c r="DC5" s="311"/>
-      <c r="DD5" s="311"/>
-      <c r="DE5" s="311"/>
-      <c r="DF5" s="311"/>
-      <c r="DG5" s="311"/>
-      <c r="DH5" s="311"/>
-      <c r="DI5" s="311"/>
-      <c r="DJ5" s="311"/>
-      <c r="DK5" s="311"/>
-      <c r="DL5" s="311"/>
-      <c r="DM5" s="311"/>
-      <c r="DN5" s="311"/>
-      <c r="DO5" s="289" t="s">
+      <c r="CV5" s="314"/>
+      <c r="CW5" s="314"/>
+      <c r="CX5" s="314"/>
+      <c r="CY5" s="314"/>
+      <c r="CZ5" s="314"/>
+      <c r="DA5" s="314"/>
+      <c r="DB5" s="314"/>
+      <c r="DC5" s="314"/>
+      <c r="DD5" s="314"/>
+      <c r="DE5" s="314"/>
+      <c r="DF5" s="314"/>
+      <c r="DG5" s="314"/>
+      <c r="DH5" s="314"/>
+      <c r="DI5" s="314"/>
+      <c r="DJ5" s="314"/>
+      <c r="DK5" s="314"/>
+      <c r="DL5" s="314"/>
+      <c r="DM5" s="314"/>
+      <c r="DN5" s="314"/>
+      <c r="DO5" s="292" t="s">
         <v>411</v>
       </c>
-      <c r="DP5" s="289"/>
-      <c r="DQ5" s="289"/>
-      <c r="DR5" s="289"/>
-      <c r="DS5" s="289"/>
-      <c r="DT5" s="289"/>
-      <c r="DU5" s="289"/>
-      <c r="DV5" s="290"/>
-      <c r="DZ5" s="285" t="s">
+      <c r="DP5" s="292"/>
+      <c r="DQ5" s="292"/>
+      <c r="DR5" s="292"/>
+      <c r="DS5" s="292"/>
+      <c r="DT5" s="292"/>
+      <c r="DU5" s="292"/>
+      <c r="DV5" s="293"/>
+      <c r="DZ5" s="288" t="s">
         <v>122</v>
       </c>
-      <c r="EA5" s="285"/>
-      <c r="EB5" s="285"/>
+      <c r="EA5" s="288"/>
+      <c r="EB5" s="288"/>
       <c r="EC5" s="10"/>
-      <c r="ED5" s="286" t="s">
+      <c r="ED5" s="289" t="s">
         <v>408</v>
       </c>
-      <c r="EE5" s="287"/>
-      <c r="EF5" s="287"/>
-      <c r="EG5" s="288"/>
-      <c r="EH5" s="311" t="s">
+      <c r="EE5" s="290"/>
+      <c r="EF5" s="290"/>
+      <c r="EG5" s="291"/>
+      <c r="EH5" s="314" t="s">
         <v>412</v>
       </c>
-      <c r="EI5" s="311"/>
-      <c r="EJ5" s="311"/>
-      <c r="EK5" s="311"/>
-      <c r="EL5" s="311"/>
-      <c r="EM5" s="311"/>
-      <c r="EN5" s="311"/>
-      <c r="EO5" s="311"/>
-      <c r="EP5" s="311"/>
-      <c r="EQ5" s="311"/>
-      <c r="ER5" s="311"/>
-      <c r="ES5" s="311"/>
-      <c r="ET5" s="311"/>
-      <c r="EU5" s="311"/>
-      <c r="EV5" s="311"/>
-      <c r="EW5" s="311"/>
-      <c r="EX5" s="311"/>
-      <c r="EY5" s="311"/>
-      <c r="EZ5" s="311"/>
-      <c r="FA5" s="311"/>
-      <c r="FB5" s="289" t="s">
+      <c r="EI5" s="314"/>
+      <c r="EJ5" s="314"/>
+      <c r="EK5" s="314"/>
+      <c r="EL5" s="314"/>
+      <c r="EM5" s="314"/>
+      <c r="EN5" s="314"/>
+      <c r="EO5" s="314"/>
+      <c r="EP5" s="314"/>
+      <c r="EQ5" s="314"/>
+      <c r="ER5" s="314"/>
+      <c r="ES5" s="314"/>
+      <c r="ET5" s="314"/>
+      <c r="EU5" s="314"/>
+      <c r="EV5" s="314"/>
+      <c r="EW5" s="314"/>
+      <c r="EX5" s="314"/>
+      <c r="EY5" s="314"/>
+      <c r="EZ5" s="314"/>
+      <c r="FA5" s="314"/>
+      <c r="FB5" s="292" t="s">
         <v>129</v>
       </c>
-      <c r="FC5" s="289"/>
-      <c r="FD5" s="289"/>
-      <c r="FE5" s="289"/>
-      <c r="FF5" s="289"/>
-      <c r="FG5" s="289"/>
-      <c r="FH5" s="289"/>
-      <c r="FI5" s="290"/>
-      <c r="FO5" s="292" t="s">
+      <c r="FC5" s="292"/>
+      <c r="FD5" s="292"/>
+      <c r="FE5" s="292"/>
+      <c r="FF5" s="292"/>
+      <c r="FG5" s="292"/>
+      <c r="FH5" s="292"/>
+      <c r="FI5" s="293"/>
+      <c r="FO5" s="295" t="s">
         <v>122</v>
       </c>
-      <c r="FP5" s="292"/>
-      <c r="FQ5" s="292"/>
+      <c r="FP5" s="295"/>
+      <c r="FQ5" s="295"/>
       <c r="FR5" s="1"/>
-      <c r="FS5" s="293" t="s">
+      <c r="FS5" s="296" t="s">
         <v>409</v>
       </c>
-      <c r="FT5" s="294"/>
-      <c r="FU5" s="294"/>
-      <c r="FV5" s="294"/>
-      <c r="FW5" s="311" t="s">
+      <c r="FT5" s="297"/>
+      <c r="FU5" s="297"/>
+      <c r="FV5" s="297"/>
+      <c r="FW5" s="314" t="s">
         <v>412</v>
       </c>
-      <c r="FX5" s="311"/>
-      <c r="FY5" s="311"/>
-      <c r="FZ5" s="311"/>
-      <c r="GA5" s="311"/>
-      <c r="GB5" s="311"/>
-      <c r="GC5" s="311"/>
-      <c r="GD5" s="311"/>
-      <c r="GE5" s="311"/>
-      <c r="GF5" s="311"/>
-      <c r="GG5" s="311"/>
-      <c r="GH5" s="311"/>
-      <c r="GI5" s="311"/>
-      <c r="GJ5" s="311"/>
-      <c r="GK5" s="311"/>
-      <c r="GL5" s="311"/>
-      <c r="GM5" s="311"/>
-      <c r="GN5" s="311"/>
-      <c r="GO5" s="311"/>
-      <c r="GP5" s="311"/>
-      <c r="GQ5" s="289" t="s">
+      <c r="FX5" s="314"/>
+      <c r="FY5" s="314"/>
+      <c r="FZ5" s="314"/>
+      <c r="GA5" s="314"/>
+      <c r="GB5" s="314"/>
+      <c r="GC5" s="314"/>
+      <c r="GD5" s="314"/>
+      <c r="GE5" s="314"/>
+      <c r="GF5" s="314"/>
+      <c r="GG5" s="314"/>
+      <c r="GH5" s="314"/>
+      <c r="GI5" s="314"/>
+      <c r="GJ5" s="314"/>
+      <c r="GK5" s="314"/>
+      <c r="GL5" s="314"/>
+      <c r="GM5" s="314"/>
+      <c r="GN5" s="314"/>
+      <c r="GO5" s="314"/>
+      <c r="GP5" s="314"/>
+      <c r="GQ5" s="292" t="s">
         <v>411</v>
       </c>
-      <c r="GR5" s="289"/>
-      <c r="GS5" s="289"/>
-      <c r="GT5" s="289"/>
-      <c r="GU5" s="289"/>
-      <c r="GV5" s="289"/>
-      <c r="GW5" s="289"/>
-      <c r="GX5" s="289"/>
-      <c r="GY5" s="282" t="s">
+      <c r="GR5" s="292"/>
+      <c r="GS5" s="292"/>
+      <c r="GT5" s="292"/>
+      <c r="GU5" s="292"/>
+      <c r="GV5" s="292"/>
+      <c r="GW5" s="292"/>
+      <c r="GX5" s="292"/>
+      <c r="GY5" s="285" t="s">
         <v>414</v>
       </c>
-      <c r="GZ5" s="283"/>
-      <c r="HA5" s="283"/>
-      <c r="HB5" s="283"/>
-      <c r="HC5" s="283"/>
-      <c r="HD5" s="283"/>
-      <c r="HE5" s="283"/>
-      <c r="HF5" s="283"/>
-      <c r="HG5" s="283"/>
-      <c r="HH5" s="283"/>
-      <c r="HI5" s="283"/>
-      <c r="HJ5" s="283"/>
-      <c r="HK5" s="283"/>
-      <c r="HL5" s="283"/>
-      <c r="HM5" s="283"/>
-      <c r="HN5" s="283"/>
-      <c r="HO5" s="283"/>
-      <c r="HP5" s="283"/>
-      <c r="HQ5" s="283"/>
-      <c r="HR5" s="283"/>
-      <c r="HS5" s="283"/>
-      <c r="HT5" s="283"/>
-      <c r="HU5" s="283"/>
-      <c r="HV5" s="283"/>
-      <c r="HW5" s="283"/>
-      <c r="HX5" s="283"/>
-      <c r="HY5" s="283"/>
-      <c r="HZ5" s="283"/>
-      <c r="IA5" s="283"/>
-      <c r="IB5" s="283"/>
-      <c r="IC5" s="283"/>
-      <c r="ID5" s="284"/>
+      <c r="GZ5" s="286"/>
+      <c r="HA5" s="286"/>
+      <c r="HB5" s="286"/>
+      <c r="HC5" s="286"/>
+      <c r="HD5" s="286"/>
+      <c r="HE5" s="286"/>
+      <c r="HF5" s="286"/>
+      <c r="HG5" s="286"/>
+      <c r="HH5" s="286"/>
+      <c r="HI5" s="286"/>
+      <c r="HJ5" s="286"/>
+      <c r="HK5" s="286"/>
+      <c r="HL5" s="286"/>
+      <c r="HM5" s="286"/>
+      <c r="HN5" s="286"/>
+      <c r="HO5" s="286"/>
+      <c r="HP5" s="286"/>
+      <c r="HQ5" s="286"/>
+      <c r="HR5" s="286"/>
+      <c r="HS5" s="286"/>
+      <c r="HT5" s="286"/>
+      <c r="HU5" s="286"/>
+      <c r="HV5" s="286"/>
+      <c r="HW5" s="286"/>
+      <c r="HX5" s="286"/>
+      <c r="HY5" s="286"/>
+      <c r="HZ5" s="286"/>
+      <c r="IA5" s="286"/>
+      <c r="IB5" s="286"/>
+      <c r="IC5" s="286"/>
+      <c r="ID5" s="287"/>
     </row>
     <row r="6" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D6" s="216"/>
       <c r="E6" s="216"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="301" t="s">
+      <c r="G6" s="304" t="s">
         <v>128</v>
       </c>
-      <c r="H6" s="302"/>
-      <c r="I6" s="302"/>
-      <c r="J6" s="302"/>
-      <c r="K6" s="302" t="s">
+      <c r="H6" s="305"/>
+      <c r="I6" s="305"/>
+      <c r="J6" s="305"/>
+      <c r="K6" s="305" t="s">
         <v>123</v>
       </c>
-      <c r="L6" s="302"/>
-      <c r="M6" s="302"/>
-      <c r="N6" s="302"/>
-      <c r="O6" s="302" t="s">
+      <c r="L6" s="305"/>
+      <c r="M6" s="305"/>
+      <c r="N6" s="305"/>
+      <c r="O6" s="305" t="s">
         <v>124</v>
       </c>
-      <c r="P6" s="302"/>
-      <c r="Q6" s="302"/>
-      <c r="R6" s="302"/>
-      <c r="S6" s="302" t="s">
+      <c r="P6" s="305"/>
+      <c r="Q6" s="305"/>
+      <c r="R6" s="305"/>
+      <c r="S6" s="305" t="s">
         <v>125</v>
       </c>
-      <c r="T6" s="302"/>
-      <c r="U6" s="302"/>
-      <c r="V6" s="303"/>
+      <c r="T6" s="305"/>
+      <c r="U6" s="305"/>
+      <c r="V6" s="306"/>
       <c r="Z6" s="216"/>
       <c r="AA6" s="216"/>
       <c r="AB6" s="216"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="301" t="s">
+      <c r="AD6" s="304" t="s">
         <v>128</v>
       </c>
-      <c r="AE6" s="302"/>
-      <c r="AF6" s="302"/>
-      <c r="AG6" s="302"/>
-      <c r="AH6" s="302" t="s">
+      <c r="AE6" s="305"/>
+      <c r="AF6" s="305"/>
+      <c r="AG6" s="305"/>
+      <c r="AH6" s="305" t="s">
         <v>123</v>
       </c>
-      <c r="AI6" s="302"/>
-      <c r="AJ6" s="302"/>
-      <c r="AK6" s="302"/>
-      <c r="AL6" s="302" t="s">
+      <c r="AI6" s="305"/>
+      <c r="AJ6" s="305"/>
+      <c r="AK6" s="305"/>
+      <c r="AL6" s="305" t="s">
         <v>124</v>
       </c>
-      <c r="AM6" s="302"/>
-      <c r="AN6" s="302"/>
-      <c r="AO6" s="302"/>
-      <c r="AP6" s="302" t="s">
+      <c r="AM6" s="305"/>
+      <c r="AN6" s="305"/>
+      <c r="AO6" s="305"/>
+      <c r="AP6" s="305" t="s">
         <v>125</v>
       </c>
-      <c r="AQ6" s="302"/>
-      <c r="AR6" s="302"/>
-      <c r="AS6" s="303"/>
+      <c r="AQ6" s="305"/>
+      <c r="AR6" s="305"/>
+      <c r="AS6" s="306"/>
       <c r="AV6" s="216"/>
       <c r="AW6" s="216"/>
       <c r="AX6" s="216"/>
       <c r="AY6" s="11"/>
-      <c r="AZ6" s="301" t="s">
+      <c r="AZ6" s="304" t="s">
         <v>128</v>
       </c>
-      <c r="BA6" s="302"/>
-      <c r="BB6" s="302"/>
-      <c r="BC6" s="302"/>
-      <c r="BD6" s="302" t="s">
+      <c r="BA6" s="305"/>
+      <c r="BB6" s="305"/>
+      <c r="BC6" s="305"/>
+      <c r="BD6" s="305" t="s">
         <v>123</v>
       </c>
-      <c r="BE6" s="302"/>
-      <c r="BF6" s="302"/>
-      <c r="BG6" s="302"/>
-      <c r="BH6" s="302" t="s">
+      <c r="BE6" s="305"/>
+      <c r="BF6" s="305"/>
+      <c r="BG6" s="305"/>
+      <c r="BH6" s="305" t="s">
         <v>124</v>
       </c>
-      <c r="BI6" s="302"/>
-      <c r="BJ6" s="302"/>
-      <c r="BK6" s="302"/>
-      <c r="BL6" s="302" t="s">
+      <c r="BI6" s="305"/>
+      <c r="BJ6" s="305"/>
+      <c r="BK6" s="305"/>
+      <c r="BL6" s="305" t="s">
         <v>125</v>
       </c>
-      <c r="BM6" s="302"/>
-      <c r="BN6" s="302"/>
-      <c r="BO6" s="303"/>
+      <c r="BM6" s="305"/>
+      <c r="BN6" s="305"/>
+      <c r="BO6" s="306"/>
       <c r="BR6" s="216"/>
       <c r="BS6" s="216"/>
       <c r="BT6" s="11"/>
-      <c r="BU6" s="301" t="s">
+      <c r="BU6" s="304" t="s">
         <v>128</v>
       </c>
-      <c r="BV6" s="302"/>
-      <c r="BW6" s="302"/>
-      <c r="BX6" s="302"/>
-      <c r="BY6" s="302" t="s">
+      <c r="BV6" s="305"/>
+      <c r="BW6" s="305"/>
+      <c r="BX6" s="305"/>
+      <c r="BY6" s="305" t="s">
         <v>123</v>
       </c>
-      <c r="BZ6" s="302"/>
-      <c r="CA6" s="302"/>
-      <c r="CB6" s="302"/>
-      <c r="CC6" s="302" t="s">
+      <c r="BZ6" s="305"/>
+      <c r="CA6" s="305"/>
+      <c r="CB6" s="305"/>
+      <c r="CC6" s="305" t="s">
         <v>124</v>
       </c>
-      <c r="CD6" s="302"/>
-      <c r="CE6" s="302"/>
-      <c r="CF6" s="302"/>
-      <c r="CG6" s="302" t="s">
+      <c r="CD6" s="305"/>
+      <c r="CE6" s="305"/>
+      <c r="CF6" s="305"/>
+      <c r="CG6" s="305" t="s">
         <v>125</v>
       </c>
-      <c r="CH6" s="302"/>
-      <c r="CI6" s="302"/>
-      <c r="CJ6" s="303"/>
+      <c r="CH6" s="305"/>
+      <c r="CI6" s="305"/>
+      <c r="CJ6" s="306"/>
       <c r="CM6" s="216"/>
       <c r="CN6" s="216"/>
       <c r="CO6" s="216"/>
-      <c r="CQ6" s="291" t="s">
+      <c r="CQ6" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="CR6" s="280"/>
-      <c r="CS6" s="280"/>
-      <c r="CT6" s="280"/>
-      <c r="CU6" s="280" t="s">
+      <c r="CR6" s="283"/>
+      <c r="CS6" s="283"/>
+      <c r="CT6" s="283"/>
+      <c r="CU6" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="CV6" s="280"/>
-      <c r="CW6" s="280"/>
-      <c r="CX6" s="280"/>
-      <c r="CY6" s="280" t="s">
+      <c r="CV6" s="283"/>
+      <c r="CW6" s="283"/>
+      <c r="CX6" s="283"/>
+      <c r="CY6" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="CZ6" s="280"/>
-      <c r="DA6" s="280"/>
-      <c r="DB6" s="280"/>
-      <c r="DC6" s="280" t="s">
+      <c r="CZ6" s="283"/>
+      <c r="DA6" s="283"/>
+      <c r="DB6" s="283"/>
+      <c r="DC6" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="DD6" s="280"/>
-      <c r="DE6" s="280"/>
-      <c r="DF6" s="280"/>
-      <c r="DG6" s="280" t="s">
+      <c r="DD6" s="283"/>
+      <c r="DE6" s="283"/>
+      <c r="DF6" s="283"/>
+      <c r="DG6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="DH6" s="280"/>
-      <c r="DI6" s="280"/>
-      <c r="DJ6" s="280"/>
-      <c r="DK6" s="280" t="s">
+      <c r="DH6" s="283"/>
+      <c r="DI6" s="283"/>
+      <c r="DJ6" s="283"/>
+      <c r="DK6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="DL6" s="280"/>
-      <c r="DM6" s="280"/>
-      <c r="DN6" s="280"/>
-      <c r="DO6" s="280" t="s">
+      <c r="DL6" s="283"/>
+      <c r="DM6" s="283"/>
+      <c r="DN6" s="283"/>
+      <c r="DO6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="DP6" s="280"/>
-      <c r="DQ6" s="280"/>
-      <c r="DR6" s="280"/>
-      <c r="DS6" s="280" t="s">
+      <c r="DP6" s="283"/>
+      <c r="DQ6" s="283"/>
+      <c r="DR6" s="283"/>
+      <c r="DS6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="DT6" s="280"/>
-      <c r="DU6" s="280"/>
-      <c r="DV6" s="281"/>
+      <c r="DT6" s="283"/>
+      <c r="DU6" s="283"/>
+      <c r="DV6" s="284"/>
       <c r="DZ6" s="216"/>
       <c r="EA6" s="216"/>
-      <c r="EB6" s="285"/>
+      <c r="EB6" s="288"/>
       <c r="EC6" s="11"/>
-      <c r="ED6" s="291" t="s">
+      <c r="ED6" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="EE6" s="280"/>
-      <c r="EF6" s="280"/>
-      <c r="EG6" s="280"/>
-      <c r="EH6" s="280" t="s">
+      <c r="EE6" s="283"/>
+      <c r="EF6" s="283"/>
+      <c r="EG6" s="283"/>
+      <c r="EH6" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="EI6" s="280"/>
-      <c r="EJ6" s="280"/>
-      <c r="EK6" s="280"/>
-      <c r="EL6" s="280" t="s">
+      <c r="EI6" s="283"/>
+      <c r="EJ6" s="283"/>
+      <c r="EK6" s="283"/>
+      <c r="EL6" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="EM6" s="280"/>
-      <c r="EN6" s="280"/>
-      <c r="EO6" s="280"/>
-      <c r="EP6" s="280" t="s">
+      <c r="EM6" s="283"/>
+      <c r="EN6" s="283"/>
+      <c r="EO6" s="283"/>
+      <c r="EP6" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="EQ6" s="280"/>
-      <c r="ER6" s="280"/>
-      <c r="ES6" s="280"/>
-      <c r="ET6" s="280" t="s">
+      <c r="EQ6" s="283"/>
+      <c r="ER6" s="283"/>
+      <c r="ES6" s="283"/>
+      <c r="ET6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="EU6" s="280"/>
-      <c r="EV6" s="280"/>
-      <c r="EW6" s="280"/>
-      <c r="EX6" s="280" t="s">
+      <c r="EU6" s="283"/>
+      <c r="EV6" s="283"/>
+      <c r="EW6" s="283"/>
+      <c r="EX6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="EY6" s="280"/>
-      <c r="EZ6" s="280"/>
-      <c r="FA6" s="280"/>
-      <c r="FB6" s="280" t="s">
+      <c r="EY6" s="283"/>
+      <c r="EZ6" s="283"/>
+      <c r="FA6" s="283"/>
+      <c r="FB6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="FC6" s="280"/>
-      <c r="FD6" s="280"/>
-      <c r="FE6" s="280"/>
-      <c r="FF6" s="280" t="s">
+      <c r="FC6" s="283"/>
+      <c r="FD6" s="283"/>
+      <c r="FE6" s="283"/>
+      <c r="FF6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="FG6" s="280"/>
-      <c r="FH6" s="280"/>
-      <c r="FI6" s="281"/>
+      <c r="FG6" s="283"/>
+      <c r="FH6" s="283"/>
+      <c r="FI6" s="284"/>
       <c r="FO6" s="216"/>
       <c r="FP6" s="216"/>
       <c r="FQ6" s="216"/>
       <c r="FR6" s="13"/>
-      <c r="FS6" s="291" t="s">
+      <c r="FS6" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT6" s="280"/>
-      <c r="FU6" s="280"/>
-      <c r="FV6" s="280"/>
-      <c r="FW6" s="280" t="s">
+      <c r="FT6" s="283"/>
+      <c r="FU6" s="283"/>
+      <c r="FV6" s="283"/>
+      <c r="FW6" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="FX6" s="280"/>
-      <c r="FY6" s="280"/>
-      <c r="FZ6" s="280"/>
-      <c r="GA6" s="280" t="s">
+      <c r="FX6" s="283"/>
+      <c r="FY6" s="283"/>
+      <c r="FZ6" s="283"/>
+      <c r="GA6" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="GB6" s="280"/>
-      <c r="GC6" s="280"/>
-      <c r="GD6" s="280"/>
-      <c r="GE6" s="280" t="s">
+      <c r="GB6" s="283"/>
+      <c r="GC6" s="283"/>
+      <c r="GD6" s="283"/>
+      <c r="GE6" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="GF6" s="280"/>
-      <c r="GG6" s="280"/>
-      <c r="GH6" s="280"/>
-      <c r="GI6" s="280" t="s">
+      <c r="GF6" s="283"/>
+      <c r="GG6" s="283"/>
+      <c r="GH6" s="283"/>
+      <c r="GI6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="GJ6" s="280"/>
-      <c r="GK6" s="280"/>
-      <c r="GL6" s="280"/>
-      <c r="GM6" s="280" t="s">
+      <c r="GJ6" s="283"/>
+      <c r="GK6" s="283"/>
+      <c r="GL6" s="283"/>
+      <c r="GM6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="GN6" s="280"/>
-      <c r="GO6" s="280"/>
-      <c r="GP6" s="280"/>
-      <c r="GQ6" s="280" t="s">
+      <c r="GN6" s="283"/>
+      <c r="GO6" s="283"/>
+      <c r="GP6" s="283"/>
+      <c r="GQ6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="GR6" s="280"/>
-      <c r="GS6" s="280"/>
-      <c r="GT6" s="280"/>
-      <c r="GU6" s="280" t="s">
+      <c r="GR6" s="283"/>
+      <c r="GS6" s="283"/>
+      <c r="GT6" s="283"/>
+      <c r="GU6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="GV6" s="280"/>
-      <c r="GW6" s="280"/>
-      <c r="GX6" s="280"/>
-      <c r="GY6" s="280" t="s">
+      <c r="GV6" s="283"/>
+      <c r="GW6" s="283"/>
+      <c r="GX6" s="283"/>
+      <c r="GY6" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="GZ6" s="280"/>
-      <c r="HA6" s="280"/>
-      <c r="HB6" s="280"/>
-      <c r="HC6" s="280" t="s">
+      <c r="GZ6" s="283"/>
+      <c r="HA6" s="283"/>
+      <c r="HB6" s="283"/>
+      <c r="HC6" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="HD6" s="280"/>
-      <c r="HE6" s="280"/>
-      <c r="HF6" s="280"/>
-      <c r="HG6" s="280" t="s">
+      <c r="HD6" s="283"/>
+      <c r="HE6" s="283"/>
+      <c r="HF6" s="283"/>
+      <c r="HG6" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="HH6" s="280"/>
-      <c r="HI6" s="280"/>
-      <c r="HJ6" s="280"/>
-      <c r="HK6" s="280" t="s">
+      <c r="HH6" s="283"/>
+      <c r="HI6" s="283"/>
+      <c r="HJ6" s="283"/>
+      <c r="HK6" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="HL6" s="280"/>
-      <c r="HM6" s="280"/>
-      <c r="HN6" s="280"/>
-      <c r="HO6" s="280" t="s">
+      <c r="HL6" s="283"/>
+      <c r="HM6" s="283"/>
+      <c r="HN6" s="283"/>
+      <c r="HO6" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="HP6" s="280"/>
-      <c r="HQ6" s="280"/>
-      <c r="HR6" s="280"/>
-      <c r="HS6" s="280" t="s">
+      <c r="HP6" s="283"/>
+      <c r="HQ6" s="283"/>
+      <c r="HR6" s="283"/>
+      <c r="HS6" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="HT6" s="280"/>
-      <c r="HU6" s="280"/>
-      <c r="HV6" s="280"/>
-      <c r="HW6" s="280" t="s">
+      <c r="HT6" s="283"/>
+      <c r="HU6" s="283"/>
+      <c r="HV6" s="283"/>
+      <c r="HW6" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="HX6" s="280"/>
-      <c r="HY6" s="280"/>
-      <c r="HZ6" s="280"/>
-      <c r="IA6" s="280" t="s">
+      <c r="HX6" s="283"/>
+      <c r="HY6" s="283"/>
+      <c r="HZ6" s="283"/>
+      <c r="IA6" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="IB6" s="280"/>
-      <c r="IC6" s="280"/>
-      <c r="ID6" s="281"/>
+      <c r="IB6" s="283"/>
+      <c r="IC6" s="283"/>
+      <c r="ID6" s="284"/>
     </row>
     <row r="7" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="D7" s="292" t="s">
+      <c r="D7" s="295" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="292"/>
+      <c r="E7" s="295"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="304" t="s">
+      <c r="G7" s="307" t="s">
         <v>403</v>
       </c>
-      <c r="H7" s="289"/>
-      <c r="I7" s="289"/>
-      <c r="J7" s="289"/>
-      <c r="K7" s="289"/>
-      <c r="L7" s="289"/>
-      <c r="M7" s="289"/>
-      <c r="N7" s="289"/>
-      <c r="O7" s="289" t="s">
+      <c r="H7" s="292"/>
+      <c r="I7" s="292"/>
+      <c r="J7" s="292"/>
+      <c r="K7" s="292"/>
+      <c r="L7" s="292"/>
+      <c r="M7" s="292"/>
+      <c r="N7" s="292"/>
+      <c r="O7" s="292" t="s">
         <v>404</v>
       </c>
-      <c r="P7" s="289"/>
-      <c r="Q7" s="289"/>
-      <c r="R7" s="289"/>
-      <c r="S7" s="289"/>
-      <c r="T7" s="289"/>
-      <c r="U7" s="289"/>
-      <c r="V7" s="290"/>
-      <c r="Z7" s="285" t="s">
+      <c r="P7" s="292"/>
+      <c r="Q7" s="292"/>
+      <c r="R7" s="292"/>
+      <c r="S7" s="292"/>
+      <c r="T7" s="292"/>
+      <c r="U7" s="292"/>
+      <c r="V7" s="293"/>
+      <c r="Z7" s="288" t="s">
         <v>126</v>
       </c>
-      <c r="AA7" s="285"/>
-      <c r="AB7" s="285"/>
+      <c r="AA7" s="288"/>
+      <c r="AB7" s="288"/>
       <c r="AC7" s="10"/>
-      <c r="AD7" s="304" t="s">
+      <c r="AD7" s="307" t="s">
         <v>403</v>
       </c>
-      <c r="AE7" s="289"/>
-      <c r="AF7" s="289"/>
-      <c r="AG7" s="289"/>
-      <c r="AH7" s="289"/>
-      <c r="AI7" s="289"/>
-      <c r="AJ7" s="289"/>
-      <c r="AK7" s="289"/>
-      <c r="AL7" s="289" t="s">
+      <c r="AE7" s="292"/>
+      <c r="AF7" s="292"/>
+      <c r="AG7" s="292"/>
+      <c r="AH7" s="292"/>
+      <c r="AI7" s="292"/>
+      <c r="AJ7" s="292"/>
+      <c r="AK7" s="292"/>
+      <c r="AL7" s="292" t="s">
         <v>129</v>
       </c>
-      <c r="AM7" s="289"/>
-      <c r="AN7" s="289"/>
-      <c r="AO7" s="289"/>
-      <c r="AP7" s="289"/>
-      <c r="AQ7" s="289"/>
-      <c r="AR7" s="289"/>
-      <c r="AS7" s="290"/>
-      <c r="AV7" s="285" t="s">
+      <c r="AM7" s="292"/>
+      <c r="AN7" s="292"/>
+      <c r="AO7" s="292"/>
+      <c r="AP7" s="292"/>
+      <c r="AQ7" s="292"/>
+      <c r="AR7" s="292"/>
+      <c r="AS7" s="293"/>
+      <c r="AV7" s="288" t="s">
         <v>126</v>
       </c>
-      <c r="AW7" s="285"/>
-      <c r="AX7" s="285"/>
+      <c r="AW7" s="288"/>
+      <c r="AX7" s="288"/>
       <c r="AY7" s="10"/>
-      <c r="AZ7" s="304" t="s">
+      <c r="AZ7" s="307" t="s">
         <v>403</v>
       </c>
-      <c r="BA7" s="289"/>
-      <c r="BB7" s="289"/>
-      <c r="BC7" s="289"/>
-      <c r="BD7" s="289"/>
-      <c r="BE7" s="289"/>
-      <c r="BF7" s="289"/>
-      <c r="BG7" s="289"/>
-      <c r="BH7" s="289" t="s">
+      <c r="BA7" s="292"/>
+      <c r="BB7" s="292"/>
+      <c r="BC7" s="292"/>
+      <c r="BD7" s="292"/>
+      <c r="BE7" s="292"/>
+      <c r="BF7" s="292"/>
+      <c r="BG7" s="292"/>
+      <c r="BH7" s="292" t="s">
         <v>404</v>
       </c>
-      <c r="BI7" s="289"/>
-      <c r="BJ7" s="289"/>
-      <c r="BK7" s="289"/>
-      <c r="BL7" s="289"/>
-      <c r="BM7" s="289"/>
-      <c r="BN7" s="289"/>
-      <c r="BO7" s="290"/>
-      <c r="BR7" s="292" t="s">
+      <c r="BI7" s="292"/>
+      <c r="BJ7" s="292"/>
+      <c r="BK7" s="292"/>
+      <c r="BL7" s="292"/>
+      <c r="BM7" s="292"/>
+      <c r="BN7" s="292"/>
+      <c r="BO7" s="293"/>
+      <c r="BR7" s="295" t="s">
         <v>126</v>
       </c>
-      <c r="BS7" s="292"/>
+      <c r="BS7" s="295"/>
       <c r="BT7" s="10"/>
-      <c r="BU7" s="304" t="s">
+      <c r="BU7" s="307" t="s">
         <v>53</v>
       </c>
-      <c r="BV7" s="289"/>
-      <c r="BW7" s="289"/>
-      <c r="BX7" s="289"/>
-      <c r="BY7" s="289"/>
-      <c r="BZ7" s="289"/>
-      <c r="CA7" s="289"/>
-      <c r="CB7" s="289"/>
-      <c r="CC7" s="289" t="s">
+      <c r="BV7" s="292"/>
+      <c r="BW7" s="292"/>
+      <c r="BX7" s="292"/>
+      <c r="BY7" s="292"/>
+      <c r="BZ7" s="292"/>
+      <c r="CA7" s="292"/>
+      <c r="CB7" s="292"/>
+      <c r="CC7" s="292" t="s">
         <v>129</v>
       </c>
-      <c r="CD7" s="289"/>
-      <c r="CE7" s="289"/>
-      <c r="CF7" s="289"/>
-      <c r="CG7" s="289"/>
-      <c r="CH7" s="289"/>
-      <c r="CI7" s="289"/>
-      <c r="CJ7" s="290"/>
-      <c r="CM7" s="285" t="s">
+      <c r="CD7" s="292"/>
+      <c r="CE7" s="292"/>
+      <c r="CF7" s="292"/>
+      <c r="CG7" s="292"/>
+      <c r="CH7" s="292"/>
+      <c r="CI7" s="292"/>
+      <c r="CJ7" s="293"/>
+      <c r="CM7" s="288" t="s">
         <v>130</v>
       </c>
-      <c r="CN7" s="285"/>
-      <c r="CO7" s="285"/>
+      <c r="CN7" s="288"/>
+      <c r="CO7" s="288"/>
       <c r="CP7" s="10"/>
-      <c r="CQ7" s="308" t="s">
+      <c r="CQ7" s="311" t="s">
         <v>410</v>
       </c>
-      <c r="CR7" s="309"/>
-      <c r="CS7" s="309"/>
-      <c r="CT7" s="309"/>
-      <c r="CU7" s="309"/>
-      <c r="CV7" s="309"/>
-      <c r="CW7" s="309"/>
-      <c r="CX7" s="309"/>
-      <c r="CY7" s="312" t="s">
+      <c r="CR7" s="312"/>
+      <c r="CS7" s="312"/>
+      <c r="CT7" s="312"/>
+      <c r="CU7" s="312"/>
+      <c r="CV7" s="312"/>
+      <c r="CW7" s="312"/>
+      <c r="CX7" s="312"/>
+      <c r="CY7" s="315" t="s">
         <v>413</v>
       </c>
-      <c r="CZ7" s="313"/>
-      <c r="DA7" s="313"/>
-      <c r="DB7" s="313"/>
-      <c r="DC7" s="313"/>
-      <c r="DD7" s="313"/>
-      <c r="DE7" s="313"/>
-      <c r="DF7" s="313"/>
-      <c r="DG7" s="313"/>
-      <c r="DH7" s="313"/>
-      <c r="DI7" s="313"/>
-      <c r="DJ7" s="313"/>
-      <c r="DK7" s="313"/>
-      <c r="DL7" s="313"/>
-      <c r="DM7" s="313"/>
-      <c r="DN7" s="313"/>
-      <c r="DO7" s="313"/>
-      <c r="DP7" s="313"/>
-      <c r="DQ7" s="313"/>
-      <c r="DR7" s="313"/>
-      <c r="DS7" s="313"/>
-      <c r="DT7" s="313"/>
-      <c r="DU7" s="313"/>
-      <c r="DV7" s="314"/>
+      <c r="CZ7" s="316"/>
+      <c r="DA7" s="316"/>
+      <c r="DB7" s="316"/>
+      <c r="DC7" s="316"/>
+      <c r="DD7" s="316"/>
+      <c r="DE7" s="316"/>
+      <c r="DF7" s="316"/>
+      <c r="DG7" s="316"/>
+      <c r="DH7" s="316"/>
+      <c r="DI7" s="316"/>
+      <c r="DJ7" s="316"/>
+      <c r="DK7" s="316"/>
+      <c r="DL7" s="316"/>
+      <c r="DM7" s="316"/>
+      <c r="DN7" s="316"/>
+      <c r="DO7" s="316"/>
+      <c r="DP7" s="316"/>
+      <c r="DQ7" s="316"/>
+      <c r="DR7" s="316"/>
+      <c r="DS7" s="316"/>
+      <c r="DT7" s="316"/>
+      <c r="DU7" s="316"/>
+      <c r="DV7" s="317"/>
       <c r="EB7" s="1"/>
       <c r="EC7" s="1"/>
-      <c r="FO7" s="292" t="s">
+      <c r="FO7" s="295" t="s">
         <v>143</v>
       </c>
-      <c r="FP7" s="292"/>
-      <c r="FQ7" s="292"/>
+      <c r="FP7" s="295"/>
+      <c r="FQ7" s="295"/>
       <c r="FR7" s="1"/>
-      <c r="FS7" s="315" t="s">
+      <c r="FS7" s="318" t="s">
         <v>147</v>
       </c>
-      <c r="FT7" s="316"/>
-      <c r="FU7" s="316"/>
-      <c r="FV7" s="316"/>
-      <c r="FW7" s="316"/>
-      <c r="FX7" s="316"/>
-      <c r="FY7" s="316"/>
-      <c r="FZ7" s="316"/>
-      <c r="GA7" s="316"/>
-      <c r="GB7" s="316"/>
-      <c r="GC7" s="316"/>
-      <c r="GD7" s="316"/>
-      <c r="GE7" s="316"/>
-      <c r="GF7" s="316"/>
-      <c r="GG7" s="316"/>
-      <c r="GH7" s="316"/>
-      <c r="GI7" s="316"/>
-      <c r="GJ7" s="316"/>
-      <c r="GK7" s="316"/>
-      <c r="GL7" s="316"/>
-      <c r="GM7" s="316"/>
-      <c r="GN7" s="316"/>
-      <c r="GO7" s="316"/>
-      <c r="GP7" s="316"/>
-      <c r="GQ7" s="316"/>
-      <c r="GR7" s="316"/>
-      <c r="GS7" s="316"/>
-      <c r="GT7" s="316"/>
-      <c r="GU7" s="316"/>
-      <c r="GV7" s="316"/>
-      <c r="GW7" s="316"/>
-      <c r="GX7" s="316"/>
-      <c r="GY7" s="316"/>
-      <c r="GZ7" s="316"/>
-      <c r="HA7" s="316"/>
-      <c r="HB7" s="316"/>
-      <c r="HC7" s="316"/>
-      <c r="HD7" s="316"/>
-      <c r="HE7" s="316"/>
-      <c r="HF7" s="316"/>
-      <c r="HG7" s="316"/>
-      <c r="HH7" s="316"/>
-      <c r="HI7" s="316"/>
-      <c r="HJ7" s="316"/>
-      <c r="HK7" s="316"/>
-      <c r="HL7" s="316"/>
-      <c r="HM7" s="316"/>
-      <c r="HN7" s="316"/>
-      <c r="HO7" s="316"/>
-      <c r="HP7" s="316"/>
-      <c r="HQ7" s="316"/>
-      <c r="HR7" s="316"/>
-      <c r="HS7" s="316"/>
-      <c r="HT7" s="316"/>
-      <c r="HU7" s="316"/>
-      <c r="HV7" s="316"/>
-      <c r="HW7" s="316"/>
-      <c r="HX7" s="316"/>
-      <c r="HY7" s="316"/>
-      <c r="HZ7" s="316"/>
-      <c r="IA7" s="316"/>
-      <c r="IB7" s="316"/>
-      <c r="IC7" s="316"/>
-      <c r="ID7" s="317"/>
+      <c r="FT7" s="319"/>
+      <c r="FU7" s="319"/>
+      <c r="FV7" s="319"/>
+      <c r="FW7" s="319"/>
+      <c r="FX7" s="319"/>
+      <c r="FY7" s="319"/>
+      <c r="FZ7" s="319"/>
+      <c r="GA7" s="319"/>
+      <c r="GB7" s="319"/>
+      <c r="GC7" s="319"/>
+      <c r="GD7" s="319"/>
+      <c r="GE7" s="319"/>
+      <c r="GF7" s="319"/>
+      <c r="GG7" s="319"/>
+      <c r="GH7" s="319"/>
+      <c r="GI7" s="319"/>
+      <c r="GJ7" s="319"/>
+      <c r="GK7" s="319"/>
+      <c r="GL7" s="319"/>
+      <c r="GM7" s="319"/>
+      <c r="GN7" s="319"/>
+      <c r="GO7" s="319"/>
+      <c r="GP7" s="319"/>
+      <c r="GQ7" s="319"/>
+      <c r="GR7" s="319"/>
+      <c r="GS7" s="319"/>
+      <c r="GT7" s="319"/>
+      <c r="GU7" s="319"/>
+      <c r="GV7" s="319"/>
+      <c r="GW7" s="319"/>
+      <c r="GX7" s="319"/>
+      <c r="GY7" s="319"/>
+      <c r="GZ7" s="319"/>
+      <c r="HA7" s="319"/>
+      <c r="HB7" s="319"/>
+      <c r="HC7" s="319"/>
+      <c r="HD7" s="319"/>
+      <c r="HE7" s="319"/>
+      <c r="HF7" s="319"/>
+      <c r="HG7" s="319"/>
+      <c r="HH7" s="319"/>
+      <c r="HI7" s="319"/>
+      <c r="HJ7" s="319"/>
+      <c r="HK7" s="319"/>
+      <c r="HL7" s="319"/>
+      <c r="HM7" s="319"/>
+      <c r="HN7" s="319"/>
+      <c r="HO7" s="319"/>
+      <c r="HP7" s="319"/>
+      <c r="HQ7" s="319"/>
+      <c r="HR7" s="319"/>
+      <c r="HS7" s="319"/>
+      <c r="HT7" s="319"/>
+      <c r="HU7" s="319"/>
+      <c r="HV7" s="319"/>
+      <c r="HW7" s="319"/>
+      <c r="HX7" s="319"/>
+      <c r="HY7" s="319"/>
+      <c r="HZ7" s="319"/>
+      <c r="IA7" s="319"/>
+      <c r="IB7" s="319"/>
+      <c r="IC7" s="319"/>
+      <c r="ID7" s="320"/>
     </row>
     <row r="8" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D8" s="216"/>
       <c r="E8" s="216"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="291" t="s">
+      <c r="G8" s="294" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="280"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="280"/>
-      <c r="K8" s="280" t="s">
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="283"/>
+      <c r="K8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="295" t="s">
+      <c r="L8" s="283"/>
+      <c r="M8" s="283"/>
+      <c r="N8" s="283"/>
+      <c r="O8" s="298" t="s">
         <v>127</v>
       </c>
-      <c r="P8" s="305"/>
-      <c r="Q8" s="305"/>
-      <c r="R8" s="299"/>
-      <c r="S8" s="295" t="s">
+      <c r="P8" s="308"/>
+      <c r="Q8" s="308"/>
+      <c r="R8" s="302"/>
+      <c r="S8" s="298" t="s">
         <v>128</v>
       </c>
-      <c r="T8" s="305"/>
-      <c r="U8" s="305"/>
-      <c r="V8" s="306"/>
+      <c r="T8" s="308"/>
+      <c r="U8" s="308"/>
+      <c r="V8" s="309"/>
       <c r="Z8" s="216"/>
       <c r="AA8" s="216"/>
       <c r="AB8" s="216"/>
       <c r="AC8" s="12"/>
-      <c r="AD8" s="291" t="s">
+      <c r="AD8" s="294" t="s">
         <v>127</v>
       </c>
-      <c r="AE8" s="280"/>
-      <c r="AF8" s="280"/>
-      <c r="AG8" s="280"/>
-      <c r="AH8" s="280" t="s">
+      <c r="AE8" s="283"/>
+      <c r="AF8" s="283"/>
+      <c r="AG8" s="283"/>
+      <c r="AH8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="AI8" s="280"/>
-      <c r="AJ8" s="280"/>
-      <c r="AK8" s="295"/>
-      <c r="AL8" s="280" t="s">
+      <c r="AI8" s="283"/>
+      <c r="AJ8" s="283"/>
+      <c r="AK8" s="298"/>
+      <c r="AL8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="AM8" s="280"/>
-      <c r="AN8" s="280"/>
-      <c r="AO8" s="280"/>
-      <c r="AP8" s="280" t="s">
+      <c r="AM8" s="283"/>
+      <c r="AN8" s="283"/>
+      <c r="AO8" s="283"/>
+      <c r="AP8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="AQ8" s="280"/>
-      <c r="AR8" s="280"/>
-      <c r="AS8" s="281"/>
+      <c r="AQ8" s="283"/>
+      <c r="AR8" s="283"/>
+      <c r="AS8" s="284"/>
       <c r="AV8" s="216"/>
       <c r="AW8" s="216"/>
       <c r="AX8" s="216"/>
       <c r="AY8" s="12"/>
-      <c r="AZ8" s="291" t="s">
+      <c r="AZ8" s="294" t="s">
         <v>127</v>
       </c>
-      <c r="BA8" s="280"/>
-      <c r="BB8" s="280"/>
-      <c r="BC8" s="280"/>
-      <c r="BD8" s="280" t="s">
+      <c r="BA8" s="283"/>
+      <c r="BB8" s="283"/>
+      <c r="BC8" s="283"/>
+      <c r="BD8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="BE8" s="280"/>
-      <c r="BF8" s="280"/>
-      <c r="BG8" s="280"/>
-      <c r="BH8" s="280" t="s">
+      <c r="BE8" s="283"/>
+      <c r="BF8" s="283"/>
+      <c r="BG8" s="283"/>
+      <c r="BH8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="BI8" s="280"/>
-      <c r="BJ8" s="280"/>
-      <c r="BK8" s="280"/>
-      <c r="BL8" s="280" t="s">
+      <c r="BI8" s="283"/>
+      <c r="BJ8" s="283"/>
+      <c r="BK8" s="283"/>
+      <c r="BL8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="BM8" s="280"/>
-      <c r="BN8" s="280"/>
-      <c r="BO8" s="281"/>
+      <c r="BM8" s="283"/>
+      <c r="BN8" s="283"/>
+      <c r="BO8" s="284"/>
       <c r="BR8" s="216"/>
       <c r="BS8" s="216"/>
       <c r="BT8" s="12"/>
-      <c r="BU8" s="291" t="s">
+      <c r="BU8" s="294" t="s">
         <v>127</v>
       </c>
-      <c r="BV8" s="280"/>
-      <c r="BW8" s="280"/>
-      <c r="BX8" s="280"/>
-      <c r="BY8" s="280" t="s">
+      <c r="BV8" s="283"/>
+      <c r="BW8" s="283"/>
+      <c r="BX8" s="283"/>
+      <c r="BY8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="BZ8" s="280"/>
-      <c r="CA8" s="280"/>
-      <c r="CB8" s="280"/>
-      <c r="CC8" s="280" t="s">
+      <c r="BZ8" s="283"/>
+      <c r="CA8" s="283"/>
+      <c r="CB8" s="283"/>
+      <c r="CC8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="CD8" s="280"/>
-      <c r="CE8" s="280"/>
-      <c r="CF8" s="280"/>
-      <c r="CG8" s="280" t="s">
+      <c r="CD8" s="283"/>
+      <c r="CE8" s="283"/>
+      <c r="CF8" s="283"/>
+      <c r="CG8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="CH8" s="280"/>
-      <c r="CI8" s="280"/>
-      <c r="CJ8" s="281"/>
+      <c r="CH8" s="283"/>
+      <c r="CI8" s="283"/>
+      <c r="CJ8" s="284"/>
       <c r="CM8" s="216"/>
       <c r="CN8" s="216"/>
       <c r="CO8" s="216"/>
       <c r="CP8" s="12"/>
-      <c r="CQ8" s="291" t="s">
+      <c r="CQ8" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="CR8" s="280"/>
-      <c r="CS8" s="280"/>
-      <c r="CT8" s="280"/>
-      <c r="CU8" s="280" t="s">
+      <c r="CR8" s="283"/>
+      <c r="CS8" s="283"/>
+      <c r="CT8" s="283"/>
+      <c r="CU8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="CV8" s="280"/>
-      <c r="CW8" s="280"/>
-      <c r="CX8" s="280"/>
-      <c r="CY8" s="280" t="s">
+      <c r="CV8" s="283"/>
+      <c r="CW8" s="283"/>
+      <c r="CX8" s="283"/>
+      <c r="CY8" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="CZ8" s="280"/>
-      <c r="DA8" s="280"/>
-      <c r="DB8" s="280"/>
-      <c r="DC8" s="280" t="s">
+      <c r="CZ8" s="283"/>
+      <c r="DA8" s="283"/>
+      <c r="DB8" s="283"/>
+      <c r="DC8" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="DD8" s="280"/>
-      <c r="DE8" s="280"/>
-      <c r="DF8" s="280"/>
-      <c r="DG8" s="280" t="s">
+      <c r="DD8" s="283"/>
+      <c r="DE8" s="283"/>
+      <c r="DF8" s="283"/>
+      <c r="DG8" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="DH8" s="280"/>
-      <c r="DI8" s="280"/>
-      <c r="DJ8" s="280"/>
-      <c r="DK8" s="280" t="s">
+      <c r="DH8" s="283"/>
+      <c r="DI8" s="283"/>
+      <c r="DJ8" s="283"/>
+      <c r="DK8" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="DL8" s="280"/>
-      <c r="DM8" s="280"/>
-      <c r="DN8" s="280"/>
-      <c r="DO8" s="280" t="s">
+      <c r="DL8" s="283"/>
+      <c r="DM8" s="283"/>
+      <c r="DN8" s="283"/>
+      <c r="DO8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="DP8" s="280"/>
-      <c r="DQ8" s="280"/>
-      <c r="DR8" s="280"/>
-      <c r="DS8" s="280" t="s">
+      <c r="DP8" s="283"/>
+      <c r="DQ8" s="283"/>
+      <c r="DR8" s="283"/>
+      <c r="DS8" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="DT8" s="280"/>
-      <c r="DU8" s="280"/>
-      <c r="DV8" s="280"/>
+      <c r="DT8" s="283"/>
+      <c r="DU8" s="283"/>
+      <c r="DV8" s="283"/>
       <c r="FO8" s="216"/>
       <c r="FP8" s="216"/>
       <c r="FQ8" s="216"/>
       <c r="FR8" s="13"/>
-      <c r="FS8" s="291" t="s">
+      <c r="FS8" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT8" s="280"/>
-      <c r="FU8" s="280"/>
-      <c r="FV8" s="280"/>
-      <c r="FW8" s="280" t="s">
+      <c r="FT8" s="283"/>
+      <c r="FU8" s="283"/>
+      <c r="FV8" s="283"/>
+      <c r="FW8" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="FX8" s="280"/>
-      <c r="FY8" s="280"/>
-      <c r="FZ8" s="280"/>
-      <c r="GA8" s="280" t="s">
+      <c r="FX8" s="283"/>
+      <c r="FY8" s="283"/>
+      <c r="FZ8" s="283"/>
+      <c r="GA8" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="GB8" s="280"/>
-      <c r="GC8" s="280"/>
-      <c r="GD8" s="280"/>
-      <c r="GE8" s="280" t="s">
+      <c r="GB8" s="283"/>
+      <c r="GC8" s="283"/>
+      <c r="GD8" s="283"/>
+      <c r="GE8" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="GF8" s="280"/>
-      <c r="GG8" s="280"/>
-      <c r="GH8" s="280"/>
-      <c r="GI8" s="280" t="s">
+      <c r="GF8" s="283"/>
+      <c r="GG8" s="283"/>
+      <c r="GH8" s="283"/>
+      <c r="GI8" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="GJ8" s="280"/>
-      <c r="GK8" s="280"/>
-      <c r="GL8" s="280"/>
-      <c r="GM8" s="280" t="s">
+      <c r="GJ8" s="283"/>
+      <c r="GK8" s="283"/>
+      <c r="GL8" s="283"/>
+      <c r="GM8" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="GN8" s="280"/>
-      <c r="GO8" s="280"/>
-      <c r="GP8" s="280"/>
-      <c r="GQ8" s="280" t="s">
+      <c r="GN8" s="283"/>
+      <c r="GO8" s="283"/>
+      <c r="GP8" s="283"/>
+      <c r="GQ8" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="GR8" s="280"/>
-      <c r="GS8" s="280"/>
-      <c r="GT8" s="280"/>
-      <c r="GU8" s="280" t="s">
+      <c r="GR8" s="283"/>
+      <c r="GS8" s="283"/>
+      <c r="GT8" s="283"/>
+      <c r="GU8" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="GV8" s="280"/>
-      <c r="GW8" s="280"/>
-      <c r="GX8" s="280"/>
-      <c r="GY8" s="280" t="s">
+      <c r="GV8" s="283"/>
+      <c r="GW8" s="283"/>
+      <c r="GX8" s="283"/>
+      <c r="GY8" s="283" t="s">
         <v>135</v>
       </c>
-      <c r="GZ8" s="280"/>
-      <c r="HA8" s="280"/>
-      <c r="HB8" s="280"/>
-      <c r="HC8" s="280" t="s">
+      <c r="GZ8" s="283"/>
+      <c r="HA8" s="283"/>
+      <c r="HB8" s="283"/>
+      <c r="HC8" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="HD8" s="280"/>
-      <c r="HE8" s="280"/>
-      <c r="HF8" s="280"/>
-      <c r="HG8" s="280" t="s">
+      <c r="HD8" s="283"/>
+      <c r="HE8" s="283"/>
+      <c r="HF8" s="283"/>
+      <c r="HG8" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="HH8" s="280"/>
-      <c r="HI8" s="280"/>
-      <c r="HJ8" s="280"/>
-      <c r="HK8" s="280" t="s">
+      <c r="HH8" s="283"/>
+      <c r="HI8" s="283"/>
+      <c r="HJ8" s="283"/>
+      <c r="HK8" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="HL8" s="280"/>
-      <c r="HM8" s="280"/>
-      <c r="HN8" s="280"/>
-      <c r="HO8" s="280" t="s">
+      <c r="HL8" s="283"/>
+      <c r="HM8" s="283"/>
+      <c r="HN8" s="283"/>
+      <c r="HO8" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="HP8" s="280"/>
-      <c r="HQ8" s="280"/>
-      <c r="HR8" s="280"/>
-      <c r="HS8" s="280" t="s">
+      <c r="HP8" s="283"/>
+      <c r="HQ8" s="283"/>
+      <c r="HR8" s="283"/>
+      <c r="HS8" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="HT8" s="280"/>
-      <c r="HU8" s="280"/>
-      <c r="HV8" s="280"/>
-      <c r="HW8" s="280" t="s">
+      <c r="HT8" s="283"/>
+      <c r="HU8" s="283"/>
+      <c r="HV8" s="283"/>
+      <c r="HW8" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="HX8" s="280"/>
-      <c r="HY8" s="280"/>
-      <c r="HZ8" s="280"/>
-      <c r="IA8" s="280" t="s">
+      <c r="HX8" s="283"/>
+      <c r="HY8" s="283"/>
+      <c r="HZ8" s="283"/>
+      <c r="IA8" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="IB8" s="280"/>
-      <c r="IC8" s="280"/>
-      <c r="ID8" s="281"/>
+      <c r="IB8" s="283"/>
+      <c r="IC8" s="283"/>
+      <c r="ID8" s="284"/>
     </row>
     <row r="9" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="Z9" s="285" t="s">
+      <c r="Z9" s="288" t="s">
         <v>130</v>
       </c>
-      <c r="AA9" s="285"/>
-      <c r="AB9" s="285"/>
+      <c r="AA9" s="288"/>
+      <c r="AB9" s="288"/>
       <c r="AC9" s="10"/>
-      <c r="AD9" s="296" t="s">
+      <c r="AD9" s="299" t="s">
         <v>131</v>
       </c>
-      <c r="AE9" s="297"/>
-      <c r="AF9" s="297"/>
-      <c r="AG9" s="297"/>
-      <c r="AH9" s="297"/>
-      <c r="AI9" s="297"/>
-      <c r="AJ9" s="297"/>
-      <c r="AK9" s="297"/>
-      <c r="AL9" s="297"/>
-      <c r="AM9" s="297"/>
-      <c r="AN9" s="297"/>
-      <c r="AO9" s="297"/>
-      <c r="AP9" s="297"/>
-      <c r="AQ9" s="297"/>
-      <c r="AR9" s="297"/>
-      <c r="AS9" s="298"/>
-      <c r="AV9" s="285" t="s">
+      <c r="AE9" s="300"/>
+      <c r="AF9" s="300"/>
+      <c r="AG9" s="300"/>
+      <c r="AH9" s="300"/>
+      <c r="AI9" s="300"/>
+      <c r="AJ9" s="300"/>
+      <c r="AK9" s="300"/>
+      <c r="AL9" s="300"/>
+      <c r="AM9" s="300"/>
+      <c r="AN9" s="300"/>
+      <c r="AO9" s="300"/>
+      <c r="AP9" s="300"/>
+      <c r="AQ9" s="300"/>
+      <c r="AR9" s="300"/>
+      <c r="AS9" s="301"/>
+      <c r="AV9" s="288" t="s">
         <v>130</v>
       </c>
-      <c r="AW9" s="285"/>
-      <c r="AX9" s="285"/>
+      <c r="AW9" s="288"/>
+      <c r="AX9" s="288"/>
       <c r="AY9" s="10"/>
-      <c r="AZ9" s="296" t="s">
+      <c r="AZ9" s="299" t="s">
         <v>131</v>
       </c>
-      <c r="BA9" s="297"/>
-      <c r="BB9" s="297"/>
-      <c r="BC9" s="297"/>
-      <c r="BD9" s="297"/>
-      <c r="BE9" s="297"/>
-      <c r="BF9" s="297"/>
-      <c r="BG9" s="297"/>
-      <c r="BH9" s="297"/>
-      <c r="BI9" s="297"/>
-      <c r="BJ9" s="297"/>
-      <c r="BK9" s="297"/>
-      <c r="BL9" s="297"/>
-      <c r="BM9" s="297"/>
-      <c r="BN9" s="297"/>
-      <c r="BO9" s="298"/>
-      <c r="CM9" s="285" t="s">
+      <c r="BA9" s="300"/>
+      <c r="BB9" s="300"/>
+      <c r="BC9" s="300"/>
+      <c r="BD9" s="300"/>
+      <c r="BE9" s="300"/>
+      <c r="BF9" s="300"/>
+      <c r="BG9" s="300"/>
+      <c r="BH9" s="300"/>
+      <c r="BI9" s="300"/>
+      <c r="BJ9" s="300"/>
+      <c r="BK9" s="300"/>
+      <c r="BL9" s="300"/>
+      <c r="BM9" s="300"/>
+      <c r="BN9" s="300"/>
+      <c r="BO9" s="301"/>
+      <c r="CM9" s="288" t="s">
         <v>143</v>
       </c>
-      <c r="CN9" s="285"/>
-      <c r="CO9" s="285"/>
+      <c r="CN9" s="288"/>
+      <c r="CO9" s="288"/>
       <c r="CP9" s="10"/>
-      <c r="CQ9" s="315" t="s">
+      <c r="CQ9" s="318" t="s">
         <v>149</v>
       </c>
-      <c r="CR9" s="316"/>
-      <c r="CS9" s="316"/>
-      <c r="CT9" s="316"/>
-      <c r="CU9" s="316"/>
-      <c r="CV9" s="316"/>
-      <c r="CW9" s="316"/>
-      <c r="CX9" s="316"/>
-      <c r="CY9" s="316"/>
-      <c r="CZ9" s="316"/>
-      <c r="DA9" s="316"/>
-      <c r="DB9" s="316"/>
-      <c r="DC9" s="316"/>
-      <c r="DD9" s="316"/>
-      <c r="DE9" s="316"/>
-      <c r="DF9" s="316"/>
-      <c r="DG9" s="316"/>
-      <c r="DH9" s="316"/>
-      <c r="DI9" s="316"/>
-      <c r="DJ9" s="316"/>
-      <c r="DK9" s="316"/>
-      <c r="DL9" s="316"/>
-      <c r="DM9" s="316"/>
-      <c r="DN9" s="316"/>
-      <c r="DO9" s="316"/>
-      <c r="DP9" s="316"/>
-      <c r="DQ9" s="316"/>
-      <c r="DR9" s="316"/>
-      <c r="DS9" s="316"/>
-      <c r="DT9" s="316"/>
-      <c r="DU9" s="316"/>
-      <c r="DV9" s="317"/>
-      <c r="FO9" s="292" t="s">
+      <c r="CR9" s="319"/>
+      <c r="CS9" s="319"/>
+      <c r="CT9" s="319"/>
+      <c r="CU9" s="319"/>
+      <c r="CV9" s="319"/>
+      <c r="CW9" s="319"/>
+      <c r="CX9" s="319"/>
+      <c r="CY9" s="319"/>
+      <c r="CZ9" s="319"/>
+      <c r="DA9" s="319"/>
+      <c r="DB9" s="319"/>
+      <c r="DC9" s="319"/>
+      <c r="DD9" s="319"/>
+      <c r="DE9" s="319"/>
+      <c r="DF9" s="319"/>
+      <c r="DG9" s="319"/>
+      <c r="DH9" s="319"/>
+      <c r="DI9" s="319"/>
+      <c r="DJ9" s="319"/>
+      <c r="DK9" s="319"/>
+      <c r="DL9" s="319"/>
+      <c r="DM9" s="319"/>
+      <c r="DN9" s="319"/>
+      <c r="DO9" s="319"/>
+      <c r="DP9" s="319"/>
+      <c r="DQ9" s="319"/>
+      <c r="DR9" s="319"/>
+      <c r="DS9" s="319"/>
+      <c r="DT9" s="319"/>
+      <c r="DU9" s="319"/>
+      <c r="DV9" s="320"/>
+      <c r="FO9" s="295" t="s">
         <v>14</v>
       </c>
-      <c r="FP9" s="292"/>
-      <c r="FQ9" s="292"/>
+      <c r="FP9" s="295"/>
+      <c r="FQ9" s="295"/>
       <c r="FR9" s="1"/>
-      <c r="FS9" s="324" t="s">
+      <c r="FS9" s="327" t="s">
         <v>14</v>
       </c>
-      <c r="FT9" s="325"/>
-      <c r="FU9" s="325"/>
-      <c r="FV9" s="325"/>
-      <c r="FW9" s="325"/>
-      <c r="FX9" s="325"/>
-      <c r="FY9" s="325"/>
-      <c r="FZ9" s="325"/>
-      <c r="GA9" s="325"/>
-      <c r="GB9" s="325"/>
-      <c r="GC9" s="325"/>
-      <c r="GD9" s="325"/>
-      <c r="GE9" s="325"/>
-      <c r="GF9" s="325"/>
-      <c r="GG9" s="325"/>
-      <c r="GH9" s="325"/>
-      <c r="GI9" s="325"/>
-      <c r="GJ9" s="325"/>
-      <c r="GK9" s="325"/>
-      <c r="GL9" s="325"/>
-      <c r="GM9" s="325"/>
-      <c r="GN9" s="325"/>
-      <c r="GO9" s="325"/>
-      <c r="GP9" s="325"/>
-      <c r="GQ9" s="325"/>
-      <c r="GR9" s="325"/>
-      <c r="GS9" s="325"/>
-      <c r="GT9" s="325"/>
-      <c r="GU9" s="325"/>
-      <c r="GV9" s="325"/>
-      <c r="GW9" s="325"/>
-      <c r="GX9" s="325"/>
-      <c r="GY9" s="325"/>
-      <c r="GZ9" s="325"/>
-      <c r="HA9" s="325"/>
-      <c r="HB9" s="325"/>
-      <c r="HC9" s="325"/>
-      <c r="HD9" s="325"/>
-      <c r="HE9" s="325"/>
-      <c r="HF9" s="325"/>
-      <c r="HG9" s="325"/>
-      <c r="HH9" s="325"/>
-      <c r="HI9" s="325"/>
-      <c r="HJ9" s="325"/>
-      <c r="HK9" s="325"/>
-      <c r="HL9" s="325"/>
-      <c r="HM9" s="325"/>
-      <c r="HN9" s="325"/>
-      <c r="HO9" s="325"/>
-      <c r="HP9" s="325"/>
-      <c r="HQ9" s="325"/>
-      <c r="HR9" s="325"/>
-      <c r="HS9" s="325"/>
-      <c r="HT9" s="325"/>
-      <c r="HU9" s="325"/>
-      <c r="HV9" s="325"/>
-      <c r="HW9" s="325"/>
-      <c r="HX9" s="325"/>
-      <c r="HY9" s="325"/>
-      <c r="HZ9" s="325"/>
-      <c r="IA9" s="325"/>
-      <c r="IB9" s="325"/>
-      <c r="IC9" s="325"/>
-      <c r="ID9" s="326"/>
+      <c r="FT9" s="328"/>
+      <c r="FU9" s="328"/>
+      <c r="FV9" s="328"/>
+      <c r="FW9" s="328"/>
+      <c r="FX9" s="328"/>
+      <c r="FY9" s="328"/>
+      <c r="FZ9" s="328"/>
+      <c r="GA9" s="328"/>
+      <c r="GB9" s="328"/>
+      <c r="GC9" s="328"/>
+      <c r="GD9" s="328"/>
+      <c r="GE9" s="328"/>
+      <c r="GF9" s="328"/>
+      <c r="GG9" s="328"/>
+      <c r="GH9" s="328"/>
+      <c r="GI9" s="328"/>
+      <c r="GJ9" s="328"/>
+      <c r="GK9" s="328"/>
+      <c r="GL9" s="328"/>
+      <c r="GM9" s="328"/>
+      <c r="GN9" s="328"/>
+      <c r="GO9" s="328"/>
+      <c r="GP9" s="328"/>
+      <c r="GQ9" s="328"/>
+      <c r="GR9" s="328"/>
+      <c r="GS9" s="328"/>
+      <c r="GT9" s="328"/>
+      <c r="GU9" s="328"/>
+      <c r="GV9" s="328"/>
+      <c r="GW9" s="328"/>
+      <c r="GX9" s="328"/>
+      <c r="GY9" s="328"/>
+      <c r="GZ9" s="328"/>
+      <c r="HA9" s="328"/>
+      <c r="HB9" s="328"/>
+      <c r="HC9" s="328"/>
+      <c r="HD9" s="328"/>
+      <c r="HE9" s="328"/>
+      <c r="HF9" s="328"/>
+      <c r="HG9" s="328"/>
+      <c r="HH9" s="328"/>
+      <c r="HI9" s="328"/>
+      <c r="HJ9" s="328"/>
+      <c r="HK9" s="328"/>
+      <c r="HL9" s="328"/>
+      <c r="HM9" s="328"/>
+      <c r="HN9" s="328"/>
+      <c r="HO9" s="328"/>
+      <c r="HP9" s="328"/>
+      <c r="HQ9" s="328"/>
+      <c r="HR9" s="328"/>
+      <c r="HS9" s="328"/>
+      <c r="HT9" s="328"/>
+      <c r="HU9" s="328"/>
+      <c r="HV9" s="328"/>
+      <c r="HW9" s="328"/>
+      <c r="HX9" s="328"/>
+      <c r="HY9" s="328"/>
+      <c r="HZ9" s="328"/>
+      <c r="IA9" s="328"/>
+      <c r="IB9" s="328"/>
+      <c r="IC9" s="328"/>
+      <c r="ID9" s="329"/>
     </row>
     <row r="10" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="Z10" s="216"/>
       <c r="AA10" s="216"/>
       <c r="AB10" s="216"/>
       <c r="AC10" s="12"/>
-      <c r="AD10" s="291" t="s">
+      <c r="AD10" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="AE10" s="280"/>
-      <c r="AF10" s="280"/>
-      <c r="AG10" s="280"/>
-      <c r="AH10" s="299" t="s">
+      <c r="AE10" s="283"/>
+      <c r="AF10" s="283"/>
+      <c r="AG10" s="283"/>
+      <c r="AH10" s="302" t="s">
         <v>127</v>
       </c>
-      <c r="AI10" s="280"/>
-      <c r="AJ10" s="280"/>
-      <c r="AK10" s="280"/>
-      <c r="AL10" s="280" t="s">
+      <c r="AI10" s="283"/>
+      <c r="AJ10" s="283"/>
+      <c r="AK10" s="283"/>
+      <c r="AL10" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="AM10" s="280"/>
-      <c r="AN10" s="280"/>
-      <c r="AO10" s="295"/>
-      <c r="AP10" s="280" t="s">
+      <c r="AM10" s="283"/>
+      <c r="AN10" s="283"/>
+      <c r="AO10" s="298"/>
+      <c r="AP10" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="AQ10" s="280"/>
-      <c r="AR10" s="280"/>
-      <c r="AS10" s="281"/>
+      <c r="AQ10" s="283"/>
+      <c r="AR10" s="283"/>
+      <c r="AS10" s="284"/>
       <c r="AV10" s="216"/>
       <c r="AW10" s="216"/>
       <c r="AX10" s="216"/>
       <c r="AY10" s="12"/>
-      <c r="AZ10" s="291" t="s">
+      <c r="AZ10" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="BA10" s="280"/>
-      <c r="BB10" s="280"/>
-      <c r="BC10" s="280"/>
-      <c r="BD10" s="299" t="s">
+      <c r="BA10" s="283"/>
+      <c r="BB10" s="283"/>
+      <c r="BC10" s="283"/>
+      <c r="BD10" s="302" t="s">
         <v>127</v>
       </c>
-      <c r="BE10" s="280"/>
-      <c r="BF10" s="280"/>
-      <c r="BG10" s="280"/>
-      <c r="BH10" s="280" t="s">
+      <c r="BE10" s="283"/>
+      <c r="BF10" s="283"/>
+      <c r="BG10" s="283"/>
+      <c r="BH10" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="BI10" s="280"/>
-      <c r="BJ10" s="280"/>
-      <c r="BK10" s="295"/>
-      <c r="BL10" s="280" t="s">
+      <c r="BI10" s="283"/>
+      <c r="BJ10" s="283"/>
+      <c r="BK10" s="298"/>
+      <c r="BL10" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="BM10" s="280"/>
-      <c r="BN10" s="280"/>
-      <c r="BO10" s="281"/>
+      <c r="BM10" s="283"/>
+      <c r="BN10" s="283"/>
+      <c r="BO10" s="284"/>
       <c r="CM10" s="216"/>
       <c r="CN10" s="216"/>
       <c r="CO10" s="216"/>
       <c r="CP10" s="12"/>
-      <c r="CQ10" s="291" t="s">
+      <c r="CQ10" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="CR10" s="280"/>
-      <c r="CS10" s="280"/>
-      <c r="CT10" s="280"/>
-      <c r="CU10" s="280" t="s">
+      <c r="CR10" s="283"/>
+      <c r="CS10" s="283"/>
+      <c r="CT10" s="283"/>
+      <c r="CU10" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="CV10" s="280"/>
-      <c r="CW10" s="280"/>
-      <c r="CX10" s="280"/>
-      <c r="CY10" s="280" t="s">
+      <c r="CV10" s="283"/>
+      <c r="CW10" s="283"/>
+      <c r="CX10" s="283"/>
+      <c r="CY10" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="CZ10" s="280"/>
-      <c r="DA10" s="280"/>
-      <c r="DB10" s="280"/>
-      <c r="DC10" s="280" t="s">
+      <c r="CZ10" s="283"/>
+      <c r="DA10" s="283"/>
+      <c r="DB10" s="283"/>
+      <c r="DC10" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="DD10" s="280"/>
-      <c r="DE10" s="280"/>
-      <c r="DF10" s="280"/>
-      <c r="DG10" s="280" t="s">
+      <c r="DD10" s="283"/>
+      <c r="DE10" s="283"/>
+      <c r="DF10" s="283"/>
+      <c r="DG10" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="DH10" s="280"/>
-      <c r="DI10" s="280"/>
-      <c r="DJ10" s="280"/>
-      <c r="DK10" s="280" t="s">
+      <c r="DH10" s="283"/>
+      <c r="DI10" s="283"/>
+      <c r="DJ10" s="283"/>
+      <c r="DK10" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="DL10" s="280"/>
-      <c r="DM10" s="280"/>
-      <c r="DN10" s="280"/>
-      <c r="DO10" s="280" t="s">
+      <c r="DL10" s="283"/>
+      <c r="DM10" s="283"/>
+      <c r="DN10" s="283"/>
+      <c r="DO10" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="DP10" s="280"/>
-      <c r="DQ10" s="280"/>
-      <c r="DR10" s="280"/>
-      <c r="DS10" s="280" t="s">
+      <c r="DP10" s="283"/>
+      <c r="DQ10" s="283"/>
+      <c r="DR10" s="283"/>
+      <c r="DS10" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="DT10" s="280"/>
-      <c r="DU10" s="280"/>
-      <c r="DV10" s="281"/>
+      <c r="DT10" s="283"/>
+      <c r="DU10" s="283"/>
+      <c r="DV10" s="284"/>
       <c r="FO10" s="216"/>
       <c r="FP10" s="216"/>
       <c r="FQ10" s="216"/>
       <c r="FR10" s="13"/>
-      <c r="FS10" s="327"/>
-      <c r="FT10" s="328"/>
-      <c r="FU10" s="328"/>
-      <c r="FV10" s="328"/>
-      <c r="FW10" s="328"/>
-      <c r="FX10" s="328"/>
-      <c r="FY10" s="328"/>
-      <c r="FZ10" s="328"/>
-      <c r="GA10" s="328"/>
-      <c r="GB10" s="328"/>
-      <c r="GC10" s="328"/>
-      <c r="GD10" s="328"/>
-      <c r="GE10" s="328"/>
-      <c r="GF10" s="328"/>
-      <c r="GG10" s="328"/>
-      <c r="GH10" s="328"/>
-      <c r="GI10" s="328"/>
-      <c r="GJ10" s="328"/>
-      <c r="GK10" s="328"/>
-      <c r="GL10" s="328"/>
-      <c r="GM10" s="328"/>
-      <c r="GN10" s="328"/>
-      <c r="GO10" s="328"/>
-      <c r="GP10" s="328"/>
-      <c r="GQ10" s="328"/>
-      <c r="GR10" s="328"/>
-      <c r="GS10" s="328"/>
-      <c r="GT10" s="328"/>
-      <c r="GU10" s="328"/>
-      <c r="GV10" s="328"/>
-      <c r="GW10" s="328"/>
-      <c r="GX10" s="328"/>
-      <c r="GY10" s="328"/>
-      <c r="GZ10" s="328"/>
-      <c r="HA10" s="328"/>
-      <c r="HB10" s="328"/>
-      <c r="HC10" s="328"/>
-      <c r="HD10" s="328"/>
-      <c r="HE10" s="328"/>
-      <c r="HF10" s="328"/>
-      <c r="HG10" s="328"/>
-      <c r="HH10" s="328"/>
-      <c r="HI10" s="328"/>
-      <c r="HJ10" s="328"/>
-      <c r="HK10" s="328"/>
-      <c r="HL10" s="328"/>
-      <c r="HM10" s="328"/>
-      <c r="HN10" s="328"/>
-      <c r="HO10" s="328"/>
-      <c r="HP10" s="328"/>
-      <c r="HQ10" s="328"/>
-      <c r="HR10" s="328"/>
-      <c r="HS10" s="328"/>
-      <c r="HT10" s="328"/>
-      <c r="HU10" s="328"/>
-      <c r="HV10" s="328"/>
-      <c r="HW10" s="328"/>
-      <c r="HX10" s="328"/>
-      <c r="HY10" s="328"/>
-      <c r="HZ10" s="328"/>
-      <c r="IA10" s="328"/>
-      <c r="IB10" s="328"/>
-      <c r="IC10" s="328"/>
-      <c r="ID10" s="329"/>
+      <c r="FS10" s="330"/>
+      <c r="FT10" s="331"/>
+      <c r="FU10" s="331"/>
+      <c r="FV10" s="331"/>
+      <c r="FW10" s="331"/>
+      <c r="FX10" s="331"/>
+      <c r="FY10" s="331"/>
+      <c r="FZ10" s="331"/>
+      <c r="GA10" s="331"/>
+      <c r="GB10" s="331"/>
+      <c r="GC10" s="331"/>
+      <c r="GD10" s="331"/>
+      <c r="GE10" s="331"/>
+      <c r="GF10" s="331"/>
+      <c r="GG10" s="331"/>
+      <c r="GH10" s="331"/>
+      <c r="GI10" s="331"/>
+      <c r="GJ10" s="331"/>
+      <c r="GK10" s="331"/>
+      <c r="GL10" s="331"/>
+      <c r="GM10" s="331"/>
+      <c r="GN10" s="331"/>
+      <c r="GO10" s="331"/>
+      <c r="GP10" s="331"/>
+      <c r="GQ10" s="331"/>
+      <c r="GR10" s="331"/>
+      <c r="GS10" s="331"/>
+      <c r="GT10" s="331"/>
+      <c r="GU10" s="331"/>
+      <c r="GV10" s="331"/>
+      <c r="GW10" s="331"/>
+      <c r="GX10" s="331"/>
+      <c r="GY10" s="331"/>
+      <c r="GZ10" s="331"/>
+      <c r="HA10" s="331"/>
+      <c r="HB10" s="331"/>
+      <c r="HC10" s="331"/>
+      <c r="HD10" s="331"/>
+      <c r="HE10" s="331"/>
+      <c r="HF10" s="331"/>
+      <c r="HG10" s="331"/>
+      <c r="HH10" s="331"/>
+      <c r="HI10" s="331"/>
+      <c r="HJ10" s="331"/>
+      <c r="HK10" s="331"/>
+      <c r="HL10" s="331"/>
+      <c r="HM10" s="331"/>
+      <c r="HN10" s="331"/>
+      <c r="HO10" s="331"/>
+      <c r="HP10" s="331"/>
+      <c r="HQ10" s="331"/>
+      <c r="HR10" s="331"/>
+      <c r="HS10" s="331"/>
+      <c r="HT10" s="331"/>
+      <c r="HU10" s="331"/>
+      <c r="HV10" s="331"/>
+      <c r="HW10" s="331"/>
+      <c r="HX10" s="331"/>
+      <c r="HY10" s="331"/>
+      <c r="HZ10" s="331"/>
+      <c r="IA10" s="331"/>
+      <c r="IB10" s="331"/>
+      <c r="IC10" s="331"/>
+      <c r="ID10" s="332"/>
     </row>
     <row r="11" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="CM11" s="285" t="s">
+      <c r="CM11" s="288" t="s">
         <v>144</v>
       </c>
-      <c r="CN11" s="285"/>
-      <c r="CO11" s="285"/>
+      <c r="CN11" s="288"/>
+      <c r="CO11" s="288"/>
       <c r="CP11" s="10"/>
-      <c r="CQ11" s="315" t="s">
+      <c r="CQ11" s="318" t="s">
         <v>151</v>
       </c>
-      <c r="CR11" s="316"/>
-      <c r="CS11" s="316"/>
-      <c r="CT11" s="316"/>
-      <c r="CU11" s="316"/>
-      <c r="CV11" s="316"/>
-      <c r="CW11" s="316"/>
-      <c r="CX11" s="316"/>
-      <c r="CY11" s="316"/>
-      <c r="CZ11" s="316"/>
-      <c r="DA11" s="316"/>
-      <c r="DB11" s="316"/>
-      <c r="DC11" s="316"/>
-      <c r="DD11" s="316"/>
-      <c r="DE11" s="316"/>
-      <c r="DF11" s="316"/>
-      <c r="DG11" s="316"/>
-      <c r="DH11" s="316"/>
-      <c r="DI11" s="316"/>
-      <c r="DJ11" s="316"/>
-      <c r="DK11" s="316"/>
-      <c r="DL11" s="316"/>
-      <c r="DM11" s="316"/>
-      <c r="DN11" s="316"/>
-      <c r="DO11" s="316"/>
-      <c r="DP11" s="316"/>
-      <c r="DQ11" s="316"/>
-      <c r="DR11" s="316"/>
-      <c r="DS11" s="316"/>
-      <c r="DT11" s="316"/>
-      <c r="DU11" s="316"/>
-      <c r="DV11" s="317"/>
-      <c r="FO11" s="292" t="s">
+      <c r="CR11" s="319"/>
+      <c r="CS11" s="319"/>
+      <c r="CT11" s="319"/>
+      <c r="CU11" s="319"/>
+      <c r="CV11" s="319"/>
+      <c r="CW11" s="319"/>
+      <c r="CX11" s="319"/>
+      <c r="CY11" s="319"/>
+      <c r="CZ11" s="319"/>
+      <c r="DA11" s="319"/>
+      <c r="DB11" s="319"/>
+      <c r="DC11" s="319"/>
+      <c r="DD11" s="319"/>
+      <c r="DE11" s="319"/>
+      <c r="DF11" s="319"/>
+      <c r="DG11" s="319"/>
+      <c r="DH11" s="319"/>
+      <c r="DI11" s="319"/>
+      <c r="DJ11" s="319"/>
+      <c r="DK11" s="319"/>
+      <c r="DL11" s="319"/>
+      <c r="DM11" s="319"/>
+      <c r="DN11" s="319"/>
+      <c r="DO11" s="319"/>
+      <c r="DP11" s="319"/>
+      <c r="DQ11" s="319"/>
+      <c r="DR11" s="319"/>
+      <c r="DS11" s="319"/>
+      <c r="DT11" s="319"/>
+      <c r="DU11" s="319"/>
+      <c r="DV11" s="320"/>
+      <c r="FO11" s="295" t="s">
         <v>145</v>
       </c>
-      <c r="FP11" s="292"/>
-      <c r="FQ11" s="292"/>
+      <c r="FP11" s="295"/>
+      <c r="FQ11" s="295"/>
       <c r="FR11" s="1"/>
-      <c r="FS11" s="315" t="s">
+      <c r="FS11" s="318" t="s">
         <v>148</v>
       </c>
-      <c r="FT11" s="316"/>
-      <c r="FU11" s="316"/>
-      <c r="FV11" s="316"/>
-      <c r="FW11" s="316"/>
-      <c r="FX11" s="316"/>
-      <c r="FY11" s="316"/>
-      <c r="FZ11" s="316"/>
-      <c r="GA11" s="316"/>
-      <c r="GB11" s="316"/>
-      <c r="GC11" s="316"/>
-      <c r="GD11" s="316"/>
-      <c r="GE11" s="316"/>
-      <c r="GF11" s="316"/>
-      <c r="GG11" s="316"/>
-      <c r="GH11" s="316"/>
-      <c r="GI11" s="316"/>
-      <c r="GJ11" s="316"/>
-      <c r="GK11" s="316"/>
-      <c r="GL11" s="316"/>
-      <c r="GM11" s="316"/>
-      <c r="GN11" s="316"/>
-      <c r="GO11" s="316"/>
-      <c r="GP11" s="316"/>
-      <c r="GQ11" s="316"/>
-      <c r="GR11" s="316"/>
-      <c r="GS11" s="316"/>
-      <c r="GT11" s="316"/>
-      <c r="GU11" s="316"/>
-      <c r="GV11" s="316"/>
-      <c r="GW11" s="316"/>
-      <c r="GX11" s="316"/>
-      <c r="GY11" s="316"/>
-      <c r="GZ11" s="316"/>
-      <c r="HA11" s="316"/>
-      <c r="HB11" s="316"/>
-      <c r="HC11" s="316"/>
-      <c r="HD11" s="316"/>
-      <c r="HE11" s="316"/>
-      <c r="HF11" s="316"/>
-      <c r="HG11" s="316"/>
-      <c r="HH11" s="316"/>
-      <c r="HI11" s="316"/>
-      <c r="HJ11" s="316"/>
-      <c r="HK11" s="316"/>
-      <c r="HL11" s="316"/>
-      <c r="HM11" s="316"/>
-      <c r="HN11" s="316"/>
-      <c r="HO11" s="316"/>
-      <c r="HP11" s="316"/>
-      <c r="HQ11" s="316"/>
-      <c r="HR11" s="316"/>
-      <c r="HS11" s="316"/>
-      <c r="HT11" s="316"/>
-      <c r="HU11" s="316"/>
-      <c r="HV11" s="316"/>
-      <c r="HW11" s="316"/>
-      <c r="HX11" s="316"/>
-      <c r="HY11" s="316"/>
-      <c r="HZ11" s="316"/>
-      <c r="IA11" s="316"/>
-      <c r="IB11" s="316"/>
-      <c r="IC11" s="316"/>
-      <c r="ID11" s="317"/>
+      <c r="FT11" s="319"/>
+      <c r="FU11" s="319"/>
+      <c r="FV11" s="319"/>
+      <c r="FW11" s="319"/>
+      <c r="FX11" s="319"/>
+      <c r="FY11" s="319"/>
+      <c r="FZ11" s="319"/>
+      <c r="GA11" s="319"/>
+      <c r="GB11" s="319"/>
+      <c r="GC11" s="319"/>
+      <c r="GD11" s="319"/>
+      <c r="GE11" s="319"/>
+      <c r="GF11" s="319"/>
+      <c r="GG11" s="319"/>
+      <c r="GH11" s="319"/>
+      <c r="GI11" s="319"/>
+      <c r="GJ11" s="319"/>
+      <c r="GK11" s="319"/>
+      <c r="GL11" s="319"/>
+      <c r="GM11" s="319"/>
+      <c r="GN11" s="319"/>
+      <c r="GO11" s="319"/>
+      <c r="GP11" s="319"/>
+      <c r="GQ11" s="319"/>
+      <c r="GR11" s="319"/>
+      <c r="GS11" s="319"/>
+      <c r="GT11" s="319"/>
+      <c r="GU11" s="319"/>
+      <c r="GV11" s="319"/>
+      <c r="GW11" s="319"/>
+      <c r="GX11" s="319"/>
+      <c r="GY11" s="319"/>
+      <c r="GZ11" s="319"/>
+      <c r="HA11" s="319"/>
+      <c r="HB11" s="319"/>
+      <c r="HC11" s="319"/>
+      <c r="HD11" s="319"/>
+      <c r="HE11" s="319"/>
+      <c r="HF11" s="319"/>
+      <c r="HG11" s="319"/>
+      <c r="HH11" s="319"/>
+      <c r="HI11" s="319"/>
+      <c r="HJ11" s="319"/>
+      <c r="HK11" s="319"/>
+      <c r="HL11" s="319"/>
+      <c r="HM11" s="319"/>
+      <c r="HN11" s="319"/>
+      <c r="HO11" s="319"/>
+      <c r="HP11" s="319"/>
+      <c r="HQ11" s="319"/>
+      <c r="HR11" s="319"/>
+      <c r="HS11" s="319"/>
+      <c r="HT11" s="319"/>
+      <c r="HU11" s="319"/>
+      <c r="HV11" s="319"/>
+      <c r="HW11" s="319"/>
+      <c r="HX11" s="319"/>
+      <c r="HY11" s="319"/>
+      <c r="HZ11" s="319"/>
+      <c r="IA11" s="319"/>
+      <c r="IB11" s="319"/>
+      <c r="IC11" s="319"/>
+      <c r="ID11" s="320"/>
     </row>
     <row r="12" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="CM12" s="216"/>
       <c r="CN12" s="216"/>
       <c r="CO12" s="216"/>
       <c r="CP12" s="12"/>
-      <c r="CQ12" s="291" t="s">
+      <c r="CQ12" s="294" t="s">
         <v>135</v>
       </c>
-      <c r="CR12" s="280"/>
-      <c r="CS12" s="280"/>
-      <c r="CT12" s="280"/>
-      <c r="CU12" s="280" t="s">
+      <c r="CR12" s="283"/>
+      <c r="CS12" s="283"/>
+      <c r="CT12" s="283"/>
+      <c r="CU12" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="CV12" s="280"/>
-      <c r="CW12" s="280"/>
-      <c r="CX12" s="280"/>
-      <c r="CY12" s="280" t="s">
+      <c r="CV12" s="283"/>
+      <c r="CW12" s="283"/>
+      <c r="CX12" s="283"/>
+      <c r="CY12" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="CZ12" s="280"/>
-      <c r="DA12" s="280"/>
-      <c r="DB12" s="280"/>
-      <c r="DC12" s="280" t="s">
+      <c r="CZ12" s="283"/>
+      <c r="DA12" s="283"/>
+      <c r="DB12" s="283"/>
+      <c r="DC12" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="DD12" s="280"/>
-      <c r="DE12" s="280"/>
-      <c r="DF12" s="280"/>
-      <c r="DG12" s="280" t="s">
+      <c r="DD12" s="283"/>
+      <c r="DE12" s="283"/>
+      <c r="DF12" s="283"/>
+      <c r="DG12" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="DH12" s="280"/>
-      <c r="DI12" s="280"/>
-      <c r="DJ12" s="280"/>
-      <c r="DK12" s="280" t="s">
+      <c r="DH12" s="283"/>
+      <c r="DI12" s="283"/>
+      <c r="DJ12" s="283"/>
+      <c r="DK12" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="DL12" s="280"/>
-      <c r="DM12" s="280"/>
-      <c r="DN12" s="280"/>
-      <c r="DO12" s="280" t="s">
+      <c r="DL12" s="283"/>
+      <c r="DM12" s="283"/>
+      <c r="DN12" s="283"/>
+      <c r="DO12" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="DP12" s="280"/>
-      <c r="DQ12" s="280"/>
-      <c r="DR12" s="280"/>
-      <c r="DS12" s="280" t="s">
+      <c r="DP12" s="283"/>
+      <c r="DQ12" s="283"/>
+      <c r="DR12" s="283"/>
+      <c r="DS12" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="DT12" s="280"/>
-      <c r="DU12" s="280"/>
-      <c r="DV12" s="281"/>
+      <c r="DT12" s="283"/>
+      <c r="DU12" s="283"/>
+      <c r="DV12" s="284"/>
       <c r="FO12" s="216"/>
       <c r="FP12" s="216"/>
       <c r="FQ12" s="216"/>
       <c r="FR12" s="13"/>
-      <c r="FS12" s="291" t="s">
+      <c r="FS12" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT12" s="280"/>
-      <c r="FU12" s="280"/>
-      <c r="FV12" s="280"/>
-      <c r="FW12" s="280" t="s">
+      <c r="FT12" s="283"/>
+      <c r="FU12" s="283"/>
+      <c r="FV12" s="283"/>
+      <c r="FW12" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="FX12" s="280"/>
-      <c r="FY12" s="280"/>
-      <c r="FZ12" s="280"/>
-      <c r="GA12" s="280" t="s">
+      <c r="FX12" s="283"/>
+      <c r="FY12" s="283"/>
+      <c r="FZ12" s="283"/>
+      <c r="GA12" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="GB12" s="280"/>
-      <c r="GC12" s="280"/>
-      <c r="GD12" s="280"/>
-      <c r="GE12" s="280" t="s">
+      <c r="GB12" s="283"/>
+      <c r="GC12" s="283"/>
+      <c r="GD12" s="283"/>
+      <c r="GE12" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="GF12" s="280"/>
-      <c r="GG12" s="280"/>
-      <c r="GH12" s="280"/>
-      <c r="GI12" s="280" t="s">
+      <c r="GF12" s="283"/>
+      <c r="GG12" s="283"/>
+      <c r="GH12" s="283"/>
+      <c r="GI12" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="GJ12" s="280"/>
-      <c r="GK12" s="280"/>
-      <c r="GL12" s="280"/>
-      <c r="GM12" s="280" t="s">
+      <c r="GJ12" s="283"/>
+      <c r="GK12" s="283"/>
+      <c r="GL12" s="283"/>
+      <c r="GM12" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="GN12" s="280"/>
-      <c r="GO12" s="280"/>
-      <c r="GP12" s="280"/>
-      <c r="GQ12" s="280" t="s">
+      <c r="GN12" s="283"/>
+      <c r="GO12" s="283"/>
+      <c r="GP12" s="283"/>
+      <c r="GQ12" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="GR12" s="280"/>
-      <c r="GS12" s="280"/>
-      <c r="GT12" s="280"/>
-      <c r="GU12" s="280" t="s">
+      <c r="GR12" s="283"/>
+      <c r="GS12" s="283"/>
+      <c r="GT12" s="283"/>
+      <c r="GU12" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="GV12" s="280"/>
-      <c r="GW12" s="280"/>
-      <c r="GX12" s="280"/>
-      <c r="GY12" s="280" t="s">
+      <c r="GV12" s="283"/>
+      <c r="GW12" s="283"/>
+      <c r="GX12" s="283"/>
+      <c r="GY12" s="283" t="s">
         <v>135</v>
       </c>
-      <c r="GZ12" s="280"/>
-      <c r="HA12" s="280"/>
-      <c r="HB12" s="280"/>
-      <c r="HC12" s="280" t="s">
+      <c r="GZ12" s="283"/>
+      <c r="HA12" s="283"/>
+      <c r="HB12" s="283"/>
+      <c r="HC12" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="HD12" s="280"/>
-      <c r="HE12" s="280"/>
-      <c r="HF12" s="280"/>
-      <c r="HG12" s="280" t="s">
+      <c r="HD12" s="283"/>
+      <c r="HE12" s="283"/>
+      <c r="HF12" s="283"/>
+      <c r="HG12" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="HH12" s="280"/>
-      <c r="HI12" s="280"/>
-      <c r="HJ12" s="280"/>
-      <c r="HK12" s="280" t="s">
+      <c r="HH12" s="283"/>
+      <c r="HI12" s="283"/>
+      <c r="HJ12" s="283"/>
+      <c r="HK12" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="HL12" s="280"/>
-      <c r="HM12" s="280"/>
-      <c r="HN12" s="280"/>
-      <c r="HO12" s="280" t="s">
+      <c r="HL12" s="283"/>
+      <c r="HM12" s="283"/>
+      <c r="HN12" s="283"/>
+      <c r="HO12" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="HP12" s="280"/>
-      <c r="HQ12" s="280"/>
-      <c r="HR12" s="280"/>
-      <c r="HS12" s="280" t="s">
+      <c r="HP12" s="283"/>
+      <c r="HQ12" s="283"/>
+      <c r="HR12" s="283"/>
+      <c r="HS12" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="HT12" s="280"/>
-      <c r="HU12" s="280"/>
-      <c r="HV12" s="280"/>
-      <c r="HW12" s="280" t="s">
+      <c r="HT12" s="283"/>
+      <c r="HU12" s="283"/>
+      <c r="HV12" s="283"/>
+      <c r="HW12" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="HX12" s="280"/>
-      <c r="HY12" s="280"/>
-      <c r="HZ12" s="280"/>
-      <c r="IA12" s="280" t="s">
+      <c r="HX12" s="283"/>
+      <c r="HY12" s="283"/>
+      <c r="HZ12" s="283"/>
+      <c r="IA12" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="IB12" s="280"/>
-      <c r="IC12" s="280"/>
-      <c r="ID12" s="281"/>
+      <c r="IB12" s="283"/>
+      <c r="IC12" s="283"/>
+      <c r="ID12" s="284"/>
     </row>
     <row r="13" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="CM13" s="285" t="s">
+      <c r="CM13" s="288" t="s">
         <v>14</v>
       </c>
-      <c r="CN13" s="285"/>
-      <c r="CO13" s="285"/>
+      <c r="CN13" s="288"/>
+      <c r="CO13" s="288"/>
       <c r="CP13" s="10"/>
-      <c r="CQ13" s="318" t="s">
+      <c r="CQ13" s="321" t="s">
         <v>14</v>
       </c>
-      <c r="CR13" s="319"/>
-      <c r="CS13" s="319"/>
-      <c r="CT13" s="319"/>
-      <c r="CU13" s="319"/>
-      <c r="CV13" s="319"/>
-      <c r="CW13" s="319"/>
-      <c r="CX13" s="319"/>
-      <c r="CY13" s="319"/>
-      <c r="CZ13" s="319"/>
-      <c r="DA13" s="319"/>
-      <c r="DB13" s="319"/>
-      <c r="DC13" s="319"/>
-      <c r="DD13" s="319"/>
-      <c r="DE13" s="319"/>
-      <c r="DF13" s="319"/>
-      <c r="DG13" s="319"/>
-      <c r="DH13" s="319"/>
-      <c r="DI13" s="319"/>
-      <c r="DJ13" s="319"/>
-      <c r="DK13" s="319"/>
-      <c r="DL13" s="319"/>
-      <c r="DM13" s="319"/>
-      <c r="DN13" s="319"/>
-      <c r="DO13" s="319"/>
-      <c r="DP13" s="319"/>
-      <c r="DQ13" s="319"/>
-      <c r="DR13" s="319"/>
-      <c r="DS13" s="319"/>
-      <c r="DT13" s="319"/>
-      <c r="DU13" s="319"/>
-      <c r="DV13" s="320"/>
+      <c r="CR13" s="322"/>
+      <c r="CS13" s="322"/>
+      <c r="CT13" s="322"/>
+      <c r="CU13" s="322"/>
+      <c r="CV13" s="322"/>
+      <c r="CW13" s="322"/>
+      <c r="CX13" s="322"/>
+      <c r="CY13" s="322"/>
+      <c r="CZ13" s="322"/>
+      <c r="DA13" s="322"/>
+      <c r="DB13" s="322"/>
+      <c r="DC13" s="322"/>
+      <c r="DD13" s="322"/>
+      <c r="DE13" s="322"/>
+      <c r="DF13" s="322"/>
+      <c r="DG13" s="322"/>
+      <c r="DH13" s="322"/>
+      <c r="DI13" s="322"/>
+      <c r="DJ13" s="322"/>
+      <c r="DK13" s="322"/>
+      <c r="DL13" s="322"/>
+      <c r="DM13" s="322"/>
+      <c r="DN13" s="322"/>
+      <c r="DO13" s="322"/>
+      <c r="DP13" s="322"/>
+      <c r="DQ13" s="322"/>
+      <c r="DR13" s="322"/>
+      <c r="DS13" s="322"/>
+      <c r="DT13" s="322"/>
+      <c r="DU13" s="322"/>
+      <c r="DV13" s="323"/>
     </row>
     <row r="14" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="CM14" s="216"/>
       <c r="CN14" s="216"/>
       <c r="CO14" s="216"/>
       <c r="CP14" s="12"/>
-      <c r="CQ14" s="321"/>
-      <c r="CR14" s="322"/>
-      <c r="CS14" s="322"/>
-      <c r="CT14" s="322"/>
-      <c r="CU14" s="322"/>
-      <c r="CV14" s="322"/>
-      <c r="CW14" s="322"/>
-      <c r="CX14" s="322"/>
-      <c r="CY14" s="322"/>
-      <c r="CZ14" s="322"/>
-      <c r="DA14" s="322"/>
-      <c r="DB14" s="322"/>
-      <c r="DC14" s="322"/>
-      <c r="DD14" s="322"/>
-      <c r="DE14" s="322"/>
-      <c r="DF14" s="322"/>
-      <c r="DG14" s="322"/>
-      <c r="DH14" s="322"/>
-      <c r="DI14" s="322"/>
-      <c r="DJ14" s="322"/>
-      <c r="DK14" s="322"/>
-      <c r="DL14" s="322"/>
-      <c r="DM14" s="322"/>
-      <c r="DN14" s="322"/>
-      <c r="DO14" s="322"/>
-      <c r="DP14" s="322"/>
-      <c r="DQ14" s="322"/>
-      <c r="DR14" s="322"/>
-      <c r="DS14" s="322"/>
-      <c r="DT14" s="322"/>
-      <c r="DU14" s="322"/>
-      <c r="DV14" s="323"/>
+      <c r="CQ14" s="324"/>
+      <c r="CR14" s="325"/>
+      <c r="CS14" s="325"/>
+      <c r="CT14" s="325"/>
+      <c r="CU14" s="325"/>
+      <c r="CV14" s="325"/>
+      <c r="CW14" s="325"/>
+      <c r="CX14" s="325"/>
+      <c r="CY14" s="325"/>
+      <c r="CZ14" s="325"/>
+      <c r="DA14" s="325"/>
+      <c r="DB14" s="325"/>
+      <c r="DC14" s="325"/>
+      <c r="DD14" s="325"/>
+      <c r="DE14" s="325"/>
+      <c r="DF14" s="325"/>
+      <c r="DG14" s="325"/>
+      <c r="DH14" s="325"/>
+      <c r="DI14" s="325"/>
+      <c r="DJ14" s="325"/>
+      <c r="DK14" s="325"/>
+      <c r="DL14" s="325"/>
+      <c r="DM14" s="325"/>
+      <c r="DN14" s="325"/>
+      <c r="DO14" s="325"/>
+      <c r="DP14" s="325"/>
+      <c r="DQ14" s="325"/>
+      <c r="DR14" s="325"/>
+      <c r="DS14" s="325"/>
+      <c r="DT14" s="325"/>
+      <c r="DU14" s="325"/>
+      <c r="DV14" s="326"/>
     </row>
     <row r="15" spans="4:238" x14ac:dyDescent="0.4">
-      <c r="CM15" s="285" t="s">
+      <c r="CM15" s="288" t="s">
         <v>145</v>
       </c>
-      <c r="CN15" s="285"/>
-      <c r="CO15" s="285"/>
+      <c r="CN15" s="288"/>
+      <c r="CO15" s="288"/>
       <c r="CP15" s="10"/>
-      <c r="CQ15" s="315" t="s">
+      <c r="CQ15" s="318" t="s">
         <v>150</v>
       </c>
-      <c r="CR15" s="316"/>
-      <c r="CS15" s="316"/>
-      <c r="CT15" s="316"/>
-      <c r="CU15" s="316"/>
-      <c r="CV15" s="316"/>
-      <c r="CW15" s="316"/>
-      <c r="CX15" s="316"/>
-      <c r="CY15" s="316"/>
-      <c r="CZ15" s="316"/>
-      <c r="DA15" s="316"/>
-      <c r="DB15" s="316"/>
-      <c r="DC15" s="316"/>
-      <c r="DD15" s="316"/>
-      <c r="DE15" s="316"/>
-      <c r="DF15" s="316"/>
-      <c r="DG15" s="316"/>
-      <c r="DH15" s="316"/>
-      <c r="DI15" s="316"/>
-      <c r="DJ15" s="316"/>
-      <c r="DK15" s="316"/>
-      <c r="DL15" s="316"/>
-      <c r="DM15" s="316"/>
-      <c r="DN15" s="316"/>
-      <c r="DO15" s="316"/>
-      <c r="DP15" s="316"/>
-      <c r="DQ15" s="316"/>
-      <c r="DR15" s="316"/>
-      <c r="DS15" s="316"/>
-      <c r="DT15" s="316"/>
-      <c r="DU15" s="316"/>
-      <c r="DV15" s="317"/>
+      <c r="CR15" s="319"/>
+      <c r="CS15" s="319"/>
+      <c r="CT15" s="319"/>
+      <c r="CU15" s="319"/>
+      <c r="CV15" s="319"/>
+      <c r="CW15" s="319"/>
+      <c r="CX15" s="319"/>
+      <c r="CY15" s="319"/>
+      <c r="CZ15" s="319"/>
+      <c r="DA15" s="319"/>
+      <c r="DB15" s="319"/>
+      <c r="DC15" s="319"/>
+      <c r="DD15" s="319"/>
+      <c r="DE15" s="319"/>
+      <c r="DF15" s="319"/>
+      <c r="DG15" s="319"/>
+      <c r="DH15" s="319"/>
+      <c r="DI15" s="319"/>
+      <c r="DJ15" s="319"/>
+      <c r="DK15" s="319"/>
+      <c r="DL15" s="319"/>
+      <c r="DM15" s="319"/>
+      <c r="DN15" s="319"/>
+      <c r="DO15" s="319"/>
+      <c r="DP15" s="319"/>
+      <c r="DQ15" s="319"/>
+      <c r="DR15" s="319"/>
+      <c r="DS15" s="319"/>
+      <c r="DT15" s="319"/>
+      <c r="DU15" s="319"/>
+      <c r="DV15" s="320"/>
     </row>
     <row r="16" spans="4:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="CM16" s="216"/>
       <c r="CN16" s="216"/>
       <c r="CO16" s="216"/>
       <c r="CP16" s="12"/>
-      <c r="CQ16" s="291" t="s">
+      <c r="CQ16" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="CR16" s="280"/>
-      <c r="CS16" s="280"/>
-      <c r="CT16" s="280"/>
-      <c r="CU16" s="280" t="s">
+      <c r="CR16" s="283"/>
+      <c r="CS16" s="283"/>
+      <c r="CT16" s="283"/>
+      <c r="CU16" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="CV16" s="280"/>
-      <c r="CW16" s="280"/>
-      <c r="CX16" s="280"/>
-      <c r="CY16" s="280" t="s">
+      <c r="CV16" s="283"/>
+      <c r="CW16" s="283"/>
+      <c r="CX16" s="283"/>
+      <c r="CY16" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="CZ16" s="280"/>
-      <c r="DA16" s="280"/>
-      <c r="DB16" s="280"/>
-      <c r="DC16" s="280" t="s">
+      <c r="CZ16" s="283"/>
+      <c r="DA16" s="283"/>
+      <c r="DB16" s="283"/>
+      <c r="DC16" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="DD16" s="280"/>
-      <c r="DE16" s="280"/>
-      <c r="DF16" s="280"/>
-      <c r="DG16" s="280" t="s">
+      <c r="DD16" s="283"/>
+      <c r="DE16" s="283"/>
+      <c r="DF16" s="283"/>
+      <c r="DG16" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="DH16" s="280"/>
-      <c r="DI16" s="280"/>
-      <c r="DJ16" s="280"/>
-      <c r="DK16" s="280" t="s">
+      <c r="DH16" s="283"/>
+      <c r="DI16" s="283"/>
+      <c r="DJ16" s="283"/>
+      <c r="DK16" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="DL16" s="280"/>
-      <c r="DM16" s="280"/>
-      <c r="DN16" s="280"/>
-      <c r="DO16" s="280" t="s">
+      <c r="DL16" s="283"/>
+      <c r="DM16" s="283"/>
+      <c r="DN16" s="283"/>
+      <c r="DO16" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="DP16" s="280"/>
-      <c r="DQ16" s="280"/>
-      <c r="DR16" s="280"/>
-      <c r="DS16" s="280" t="s">
+      <c r="DP16" s="283"/>
+      <c r="DQ16" s="283"/>
+      <c r="DR16" s="283"/>
+      <c r="DS16" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="DT16" s="280"/>
-      <c r="DU16" s="280"/>
-      <c r="DV16" s="281"/>
+      <c r="DT16" s="283"/>
+      <c r="DU16" s="283"/>
+      <c r="DV16" s="284"/>
     </row>
     <row r="17" spans="91:238" x14ac:dyDescent="0.4">
-      <c r="CM17" s="285" t="s">
+      <c r="CM17" s="288" t="s">
         <v>146</v>
       </c>
-      <c r="CN17" s="285"/>
-      <c r="CO17" s="285"/>
+      <c r="CN17" s="288"/>
+      <c r="CO17" s="288"/>
       <c r="CP17" s="10"/>
-      <c r="CQ17" s="315" t="s">
+      <c r="CQ17" s="318" t="s">
         <v>150</v>
       </c>
-      <c r="CR17" s="316"/>
-      <c r="CS17" s="316"/>
-      <c r="CT17" s="316"/>
-      <c r="CU17" s="316"/>
-      <c r="CV17" s="316"/>
-      <c r="CW17" s="316"/>
-      <c r="CX17" s="316"/>
-      <c r="CY17" s="316"/>
-      <c r="CZ17" s="316"/>
-      <c r="DA17" s="316"/>
-      <c r="DB17" s="316"/>
-      <c r="DC17" s="316"/>
-      <c r="DD17" s="316"/>
-      <c r="DE17" s="316"/>
-      <c r="DF17" s="316"/>
-      <c r="DG17" s="316"/>
-      <c r="DH17" s="316"/>
-      <c r="DI17" s="316"/>
-      <c r="DJ17" s="316"/>
-      <c r="DK17" s="316"/>
-      <c r="DL17" s="316"/>
-      <c r="DM17" s="316"/>
-      <c r="DN17" s="316"/>
-      <c r="DO17" s="316"/>
-      <c r="DP17" s="316"/>
-      <c r="DQ17" s="316"/>
-      <c r="DR17" s="316"/>
-      <c r="DS17" s="316"/>
-      <c r="DT17" s="316"/>
-      <c r="DU17" s="316"/>
-      <c r="DV17" s="317"/>
+      <c r="CR17" s="319"/>
+      <c r="CS17" s="319"/>
+      <c r="CT17" s="319"/>
+      <c r="CU17" s="319"/>
+      <c r="CV17" s="319"/>
+      <c r="CW17" s="319"/>
+      <c r="CX17" s="319"/>
+      <c r="CY17" s="319"/>
+      <c r="CZ17" s="319"/>
+      <c r="DA17" s="319"/>
+      <c r="DB17" s="319"/>
+      <c r="DC17" s="319"/>
+      <c r="DD17" s="319"/>
+      <c r="DE17" s="319"/>
+      <c r="DF17" s="319"/>
+      <c r="DG17" s="319"/>
+      <c r="DH17" s="319"/>
+      <c r="DI17" s="319"/>
+      <c r="DJ17" s="319"/>
+      <c r="DK17" s="319"/>
+      <c r="DL17" s="319"/>
+      <c r="DM17" s="319"/>
+      <c r="DN17" s="319"/>
+      <c r="DO17" s="319"/>
+      <c r="DP17" s="319"/>
+      <c r="DQ17" s="319"/>
+      <c r="DR17" s="319"/>
+      <c r="DS17" s="319"/>
+      <c r="DT17" s="319"/>
+      <c r="DU17" s="319"/>
+      <c r="DV17" s="320"/>
     </row>
     <row r="18" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="CM18" s="216"/>
       <c r="CN18" s="216"/>
       <c r="CO18" s="216"/>
       <c r="CP18" s="12"/>
-      <c r="CQ18" s="291" t="s">
+      <c r="CQ18" s="294" t="s">
         <v>135</v>
       </c>
-      <c r="CR18" s="280"/>
-      <c r="CS18" s="280"/>
-      <c r="CT18" s="280"/>
-      <c r="CU18" s="280" t="s">
+      <c r="CR18" s="283"/>
+      <c r="CS18" s="283"/>
+      <c r="CT18" s="283"/>
+      <c r="CU18" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="CV18" s="280"/>
-      <c r="CW18" s="280"/>
-      <c r="CX18" s="280"/>
-      <c r="CY18" s="280" t="s">
+      <c r="CV18" s="283"/>
+      <c r="CW18" s="283"/>
+      <c r="CX18" s="283"/>
+      <c r="CY18" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="CZ18" s="280"/>
-      <c r="DA18" s="280"/>
-      <c r="DB18" s="280"/>
-      <c r="DC18" s="280" t="s">
+      <c r="CZ18" s="283"/>
+      <c r="DA18" s="283"/>
+      <c r="DB18" s="283"/>
+      <c r="DC18" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="DD18" s="280"/>
-      <c r="DE18" s="280"/>
-      <c r="DF18" s="280"/>
-      <c r="DG18" s="280" t="s">
+      <c r="DD18" s="283"/>
+      <c r="DE18" s="283"/>
+      <c r="DF18" s="283"/>
+      <c r="DG18" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="DH18" s="280"/>
-      <c r="DI18" s="280"/>
-      <c r="DJ18" s="280"/>
-      <c r="DK18" s="280" t="s">
+      <c r="DH18" s="283"/>
+      <c r="DI18" s="283"/>
+      <c r="DJ18" s="283"/>
+      <c r="DK18" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="DL18" s="280"/>
-      <c r="DM18" s="280"/>
-      <c r="DN18" s="280"/>
-      <c r="DO18" s="280" t="s">
+      <c r="DL18" s="283"/>
+      <c r="DM18" s="283"/>
+      <c r="DN18" s="283"/>
+      <c r="DO18" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="DP18" s="280"/>
-      <c r="DQ18" s="280"/>
-      <c r="DR18" s="280"/>
-      <c r="DS18" s="280" t="s">
+      <c r="DP18" s="283"/>
+      <c r="DQ18" s="283"/>
+      <c r="DR18" s="283"/>
+      <c r="DS18" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="DT18" s="280"/>
-      <c r="DU18" s="280"/>
-      <c r="DV18" s="281"/>
+      <c r="DT18" s="283"/>
+      <c r="DU18" s="283"/>
+      <c r="DV18" s="284"/>
     </row>
     <row r="19" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="FR19" s="2"/>
-      <c r="FS19" s="300" t="str">
+      <c r="FS19" s="303" t="str">
         <f>"+0"</f>
         <v>+0</v>
       </c>
       <c r="FT19" s="40"/>
       <c r="FU19" s="40"/>
-      <c r="FV19" s="256"/>
-      <c r="FW19" s="300" t="str">
+      <c r="FV19" s="258"/>
+      <c r="FW19" s="303" t="str">
         <f>"+1"</f>
         <v>+1</v>
       </c>
       <c r="FX19" s="40"/>
       <c r="FY19" s="40"/>
-      <c r="FZ19" s="256"/>
-      <c r="GA19" s="300" t="str">
+      <c r="FZ19" s="258"/>
+      <c r="GA19" s="303" t="str">
         <f>"+2"</f>
         <v>+2</v>
       </c>
       <c r="GB19" s="40"/>
       <c r="GC19" s="40"/>
-      <c r="GD19" s="256"/>
-      <c r="GE19" s="300" t="str">
+      <c r="GD19" s="258"/>
+      <c r="GE19" s="303" t="str">
         <f>"+3"</f>
         <v>+3</v>
       </c>
       <c r="GF19" s="40"/>
       <c r="GG19" s="40"/>
-      <c r="GH19" s="256"/>
-      <c r="GI19" s="300" t="str">
+      <c r="GH19" s="258"/>
+      <c r="GI19" s="303" t="str">
         <f>"+4"</f>
         <v>+4</v>
       </c>
       <c r="GJ19" s="40"/>
       <c r="GK19" s="40"/>
-      <c r="GL19" s="256"/>
-      <c r="GM19" s="300" t="str">
+      <c r="GL19" s="258"/>
+      <c r="GM19" s="303" t="str">
         <f>"+5"</f>
         <v>+5</v>
       </c>
       <c r="GN19" s="40"/>
       <c r="GO19" s="40"/>
-      <c r="GP19" s="256"/>
-      <c r="GQ19" s="330" t="str">
+      <c r="GP19" s="258"/>
+      <c r="GQ19" s="333" t="str">
         <f>"+6"</f>
         <v>+6</v>
       </c>
       <c r="GR19" s="40"/>
       <c r="GS19" s="40"/>
-      <c r="GT19" s="256"/>
-      <c r="GU19" s="300" t="str">
+      <c r="GT19" s="258"/>
+      <c r="GU19" s="303" t="str">
         <f>"+7"</f>
         <v>+7</v>
       </c>
       <c r="GV19" s="40"/>
       <c r="GW19" s="40"/>
-      <c r="GX19" s="256"/>
-      <c r="GY19" s="300" t="str">
+      <c r="GX19" s="258"/>
+      <c r="GY19" s="303" t="str">
         <f>"+8"</f>
         <v>+8</v>
       </c>
       <c r="GZ19" s="40"/>
       <c r="HA19" s="40"/>
-      <c r="HB19" s="256"/>
-      <c r="HC19" s="300" t="str">
+      <c r="HB19" s="258"/>
+      <c r="HC19" s="303" t="str">
         <f>"+9"</f>
         <v>+9</v>
       </c>
       <c r="HD19" s="40"/>
       <c r="HE19" s="40"/>
-      <c r="HF19" s="256"/>
-      <c r="HG19" s="300" t="str">
+      <c r="HF19" s="258"/>
+      <c r="HG19" s="303" t="str">
         <f>"+10"</f>
         <v>+10</v>
       </c>
       <c r="HH19" s="40"/>
       <c r="HI19" s="40"/>
-      <c r="HJ19" s="256"/>
-      <c r="HK19" s="300" t="str">
+      <c r="HJ19" s="258"/>
+      <c r="HK19" s="303" t="str">
         <f>"+11"</f>
         <v>+11</v>
       </c>
       <c r="HL19" s="40"/>
       <c r="HM19" s="40"/>
-      <c r="HN19" s="256"/>
-      <c r="HO19" s="300" t="str">
+      <c r="HN19" s="258"/>
+      <c r="HO19" s="303" t="str">
         <f>"+12"</f>
         <v>+12</v>
       </c>
       <c r="HP19" s="40"/>
       <c r="HQ19" s="40"/>
-      <c r="HR19" s="256"/>
-      <c r="HS19" s="300" t="str">
+      <c r="HR19" s="258"/>
+      <c r="HS19" s="303" t="str">
         <f>"+13"</f>
         <v>+13</v>
       </c>
       <c r="HT19" s="40"/>
       <c r="HU19" s="40"/>
-      <c r="HV19" s="256"/>
-      <c r="HW19" s="300" t="str">
+      <c r="HV19" s="258"/>
+      <c r="HW19" s="303" t="str">
         <f>"+14"</f>
         <v>+14</v>
       </c>
       <c r="HX19" s="40"/>
       <c r="HY19" s="40"/>
-      <c r="HZ19" s="256"/>
-      <c r="IA19" s="300" t="str">
+      <c r="HZ19" s="258"/>
+      <c r="IA19" s="303" t="str">
         <f>"+15"</f>
         <v>+15</v>
       </c>
       <c r="IB19" s="40"/>
       <c r="IC19" s="40"/>
-      <c r="ID19" s="256"/>
+      <c r="ID19" s="258"/>
     </row>
     <row r="20" spans="91:238" x14ac:dyDescent="0.4">
-      <c r="FO20" s="292" t="s">
+      <c r="FO20" s="295" t="s">
         <v>122</v>
       </c>
-      <c r="FP20" s="292"/>
-      <c r="FQ20" s="292"/>
+      <c r="FP20" s="295"/>
+      <c r="FQ20" s="295"/>
       <c r="FR20" s="1"/>
-      <c r="FS20" s="310" t="s">
+      <c r="FS20" s="313" t="s">
         <v>407</v>
       </c>
-      <c r="FT20" s="294"/>
-      <c r="FU20" s="294"/>
-      <c r="FV20" s="294"/>
-      <c r="FW20" s="325" t="s">
+      <c r="FT20" s="297"/>
+      <c r="FU20" s="297"/>
+      <c r="FV20" s="297"/>
+      <c r="FW20" s="328" t="s">
         <v>1</v>
       </c>
-      <c r="FX20" s="325"/>
-      <c r="FY20" s="325"/>
-      <c r="FZ20" s="325"/>
-      <c r="GA20" s="325"/>
-      <c r="GB20" s="325"/>
-      <c r="GC20" s="325"/>
-      <c r="GD20" s="325"/>
-      <c r="GE20" s="325"/>
-      <c r="GF20" s="325"/>
-      <c r="GG20" s="325"/>
-      <c r="GH20" s="325"/>
-      <c r="GI20" s="325"/>
-      <c r="GJ20" s="325"/>
-      <c r="GK20" s="325"/>
-      <c r="GL20" s="325"/>
-      <c r="GM20" s="325"/>
-      <c r="GN20" s="325"/>
-      <c r="GO20" s="325"/>
-      <c r="GP20" s="325"/>
-      <c r="GQ20" s="289" t="s">
+      <c r="FX20" s="328"/>
+      <c r="FY20" s="328"/>
+      <c r="FZ20" s="328"/>
+      <c r="GA20" s="328"/>
+      <c r="GB20" s="328"/>
+      <c r="GC20" s="328"/>
+      <c r="GD20" s="328"/>
+      <c r="GE20" s="328"/>
+      <c r="GF20" s="328"/>
+      <c r="GG20" s="328"/>
+      <c r="GH20" s="328"/>
+      <c r="GI20" s="328"/>
+      <c r="GJ20" s="328"/>
+      <c r="GK20" s="328"/>
+      <c r="GL20" s="328"/>
+      <c r="GM20" s="328"/>
+      <c r="GN20" s="328"/>
+      <c r="GO20" s="328"/>
+      <c r="GP20" s="328"/>
+      <c r="GQ20" s="292" t="s">
         <v>411</v>
       </c>
-      <c r="GR20" s="289"/>
-      <c r="GS20" s="289"/>
-      <c r="GT20" s="289"/>
-      <c r="GU20" s="289"/>
-      <c r="GV20" s="289"/>
-      <c r="GW20" s="289"/>
-      <c r="GX20" s="289"/>
-      <c r="GY20" s="331" t="s">
+      <c r="GR20" s="292"/>
+      <c r="GS20" s="292"/>
+      <c r="GT20" s="292"/>
+      <c r="GU20" s="292"/>
+      <c r="GV20" s="292"/>
+      <c r="GW20" s="292"/>
+      <c r="GX20" s="292"/>
+      <c r="GY20" s="334" t="s">
         <v>410</v>
       </c>
-      <c r="GZ20" s="316"/>
-      <c r="HA20" s="316"/>
-      <c r="HB20" s="316"/>
-      <c r="HC20" s="316"/>
-      <c r="HD20" s="316"/>
-      <c r="HE20" s="316"/>
-      <c r="HF20" s="316"/>
-      <c r="HG20" s="334" t="s">
+      <c r="GZ20" s="319"/>
+      <c r="HA20" s="319"/>
+      <c r="HB20" s="319"/>
+      <c r="HC20" s="319"/>
+      <c r="HD20" s="319"/>
+      <c r="HE20" s="319"/>
+      <c r="HF20" s="319"/>
+      <c r="HG20" s="337" t="s">
         <v>1</v>
       </c>
-      <c r="HH20" s="319"/>
-      <c r="HI20" s="319"/>
-      <c r="HJ20" s="319"/>
-      <c r="HK20" s="319"/>
-      <c r="HL20" s="319"/>
-      <c r="HM20" s="319"/>
-      <c r="HN20" s="319"/>
-      <c r="HO20" s="319"/>
-      <c r="HP20" s="319"/>
-      <c r="HQ20" s="319"/>
-      <c r="HR20" s="319"/>
-      <c r="HS20" s="319"/>
-      <c r="HT20" s="319"/>
-      <c r="HU20" s="319"/>
-      <c r="HV20" s="319"/>
-      <c r="HW20" s="319"/>
-      <c r="HX20" s="319"/>
-      <c r="HY20" s="319"/>
-      <c r="HZ20" s="319"/>
-      <c r="IA20" s="319"/>
-      <c r="IB20" s="319"/>
-      <c r="IC20" s="319"/>
-      <c r="ID20" s="320"/>
+      <c r="HH20" s="322"/>
+      <c r="HI20" s="322"/>
+      <c r="HJ20" s="322"/>
+      <c r="HK20" s="322"/>
+      <c r="HL20" s="322"/>
+      <c r="HM20" s="322"/>
+      <c r="HN20" s="322"/>
+      <c r="HO20" s="322"/>
+      <c r="HP20" s="322"/>
+      <c r="HQ20" s="322"/>
+      <c r="HR20" s="322"/>
+      <c r="HS20" s="322"/>
+      <c r="HT20" s="322"/>
+      <c r="HU20" s="322"/>
+      <c r="HV20" s="322"/>
+      <c r="HW20" s="322"/>
+      <c r="HX20" s="322"/>
+      <c r="HY20" s="322"/>
+      <c r="HZ20" s="322"/>
+      <c r="IA20" s="322"/>
+      <c r="IB20" s="322"/>
+      <c r="IC20" s="322"/>
+      <c r="ID20" s="323"/>
     </row>
     <row r="21" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="FO21" s="216"/>
       <c r="FP21" s="216"/>
       <c r="FQ21" s="216"/>
       <c r="FR21" s="13"/>
-      <c r="FS21" s="291" t="s">
+      <c r="FS21" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT21" s="280"/>
-      <c r="FU21" s="280"/>
-      <c r="FV21" s="280"/>
-      <c r="FW21" s="328"/>
-      <c r="FX21" s="328"/>
-      <c r="FY21" s="328"/>
-      <c r="FZ21" s="328"/>
-      <c r="GA21" s="328"/>
-      <c r="GB21" s="328"/>
-      <c r="GC21" s="328"/>
-      <c r="GD21" s="328"/>
-      <c r="GE21" s="328"/>
-      <c r="GF21" s="328"/>
-      <c r="GG21" s="328"/>
-      <c r="GH21" s="328"/>
-      <c r="GI21" s="328"/>
-      <c r="GJ21" s="328"/>
-      <c r="GK21" s="328"/>
-      <c r="GL21" s="328"/>
-      <c r="GM21" s="328"/>
-      <c r="GN21" s="328"/>
-      <c r="GO21" s="328"/>
-      <c r="GP21" s="328"/>
-      <c r="GQ21" s="280" t="s">
+      <c r="FT21" s="283"/>
+      <c r="FU21" s="283"/>
+      <c r="FV21" s="283"/>
+      <c r="FW21" s="331"/>
+      <c r="FX21" s="331"/>
+      <c r="FY21" s="331"/>
+      <c r="FZ21" s="331"/>
+      <c r="GA21" s="331"/>
+      <c r="GB21" s="331"/>
+      <c r="GC21" s="331"/>
+      <c r="GD21" s="331"/>
+      <c r="GE21" s="331"/>
+      <c r="GF21" s="331"/>
+      <c r="GG21" s="331"/>
+      <c r="GH21" s="331"/>
+      <c r="GI21" s="331"/>
+      <c r="GJ21" s="331"/>
+      <c r="GK21" s="331"/>
+      <c r="GL21" s="331"/>
+      <c r="GM21" s="331"/>
+      <c r="GN21" s="331"/>
+      <c r="GO21" s="331"/>
+      <c r="GP21" s="331"/>
+      <c r="GQ21" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="GR21" s="280"/>
-      <c r="GS21" s="280"/>
-      <c r="GT21" s="280"/>
-      <c r="GU21" s="280" t="s">
+      <c r="GR21" s="283"/>
+      <c r="GS21" s="283"/>
+      <c r="GT21" s="283"/>
+      <c r="GU21" s="283" t="s">
         <v>128</v>
       </c>
-      <c r="GV21" s="280"/>
-      <c r="GW21" s="280"/>
-      <c r="GX21" s="280"/>
-      <c r="GY21" s="299" t="s">
+      <c r="GV21" s="283"/>
+      <c r="GW21" s="283"/>
+      <c r="GX21" s="283"/>
+      <c r="GY21" s="302" t="s">
         <v>128</v>
       </c>
-      <c r="GZ21" s="280"/>
-      <c r="HA21" s="280"/>
-      <c r="HB21" s="280"/>
-      <c r="HC21" s="280" t="s">
+      <c r="GZ21" s="283"/>
+      <c r="HA21" s="283"/>
+      <c r="HB21" s="283"/>
+      <c r="HC21" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="HD21" s="280"/>
-      <c r="HE21" s="280"/>
-      <c r="HF21" s="280"/>
-      <c r="HG21" s="335"/>
-      <c r="HH21" s="322"/>
-      <c r="HI21" s="322"/>
-      <c r="HJ21" s="322"/>
-      <c r="HK21" s="322"/>
-      <c r="HL21" s="322"/>
-      <c r="HM21" s="322"/>
-      <c r="HN21" s="322"/>
-      <c r="HO21" s="322"/>
-      <c r="HP21" s="322"/>
-      <c r="HQ21" s="322"/>
-      <c r="HR21" s="322"/>
-      <c r="HS21" s="322"/>
-      <c r="HT21" s="322"/>
-      <c r="HU21" s="322"/>
-      <c r="HV21" s="322"/>
-      <c r="HW21" s="322"/>
-      <c r="HX21" s="322"/>
-      <c r="HY21" s="322"/>
-      <c r="HZ21" s="322"/>
-      <c r="IA21" s="322"/>
-      <c r="IB21" s="322"/>
-      <c r="IC21" s="322"/>
-      <c r="ID21" s="323"/>
+      <c r="HD21" s="283"/>
+      <c r="HE21" s="283"/>
+      <c r="HF21" s="283"/>
+      <c r="HG21" s="338"/>
+      <c r="HH21" s="325"/>
+      <c r="HI21" s="325"/>
+      <c r="HJ21" s="325"/>
+      <c r="HK21" s="325"/>
+      <c r="HL21" s="325"/>
+      <c r="HM21" s="325"/>
+      <c r="HN21" s="325"/>
+      <c r="HO21" s="325"/>
+      <c r="HP21" s="325"/>
+      <c r="HQ21" s="325"/>
+      <c r="HR21" s="325"/>
+      <c r="HS21" s="325"/>
+      <c r="HT21" s="325"/>
+      <c r="HU21" s="325"/>
+      <c r="HV21" s="325"/>
+      <c r="HW21" s="325"/>
+      <c r="HX21" s="325"/>
+      <c r="HY21" s="325"/>
+      <c r="HZ21" s="325"/>
+      <c r="IA21" s="325"/>
+      <c r="IB21" s="325"/>
+      <c r="IC21" s="325"/>
+      <c r="ID21" s="326"/>
     </row>
     <row r="22" spans="91:238" x14ac:dyDescent="0.4">
-      <c r="FO22" s="292" t="s">
+      <c r="FO22" s="295" t="s">
         <v>143</v>
       </c>
-      <c r="FP22" s="292"/>
-      <c r="FQ22" s="292"/>
+      <c r="FP22" s="295"/>
+      <c r="FQ22" s="295"/>
       <c r="FR22" s="1"/>
-      <c r="FS22" s="315" t="s">
+      <c r="FS22" s="318" t="s">
         <v>149</v>
       </c>
-      <c r="FT22" s="316"/>
-      <c r="FU22" s="316"/>
-      <c r="FV22" s="316"/>
-      <c r="FW22" s="316"/>
-      <c r="FX22" s="316"/>
-      <c r="FY22" s="316"/>
-      <c r="FZ22" s="316"/>
-      <c r="GA22" s="316"/>
-      <c r="GB22" s="316"/>
-      <c r="GC22" s="316"/>
-      <c r="GD22" s="316"/>
-      <c r="GE22" s="316"/>
-      <c r="GF22" s="316"/>
-      <c r="GG22" s="316"/>
-      <c r="GH22" s="316"/>
-      <c r="GI22" s="316"/>
-      <c r="GJ22" s="316"/>
-      <c r="GK22" s="316"/>
-      <c r="GL22" s="316"/>
-      <c r="GM22" s="316"/>
-      <c r="GN22" s="316"/>
-      <c r="GO22" s="316"/>
-      <c r="GP22" s="316"/>
-      <c r="GQ22" s="316"/>
-      <c r="GR22" s="316"/>
-      <c r="GS22" s="316"/>
-      <c r="GT22" s="316"/>
-      <c r="GU22" s="316"/>
-      <c r="GV22" s="316"/>
-      <c r="GW22" s="316"/>
-      <c r="GX22" s="316"/>
-      <c r="GY22" s="316"/>
-      <c r="GZ22" s="316"/>
-      <c r="HA22" s="316"/>
-      <c r="HB22" s="316"/>
-      <c r="HC22" s="316"/>
-      <c r="HD22" s="316"/>
-      <c r="HE22" s="316"/>
-      <c r="HF22" s="316"/>
-      <c r="HG22" s="316"/>
-      <c r="HH22" s="316"/>
-      <c r="HI22" s="316"/>
-      <c r="HJ22" s="316"/>
-      <c r="HK22" s="316"/>
-      <c r="HL22" s="316"/>
-      <c r="HM22" s="316"/>
-      <c r="HN22" s="316"/>
-      <c r="HO22" s="316"/>
-      <c r="HP22" s="316"/>
-      <c r="HQ22" s="316"/>
-      <c r="HR22" s="316"/>
-      <c r="HS22" s="316"/>
-      <c r="HT22" s="316"/>
-      <c r="HU22" s="316"/>
-      <c r="HV22" s="316"/>
-      <c r="HW22" s="316"/>
-      <c r="HX22" s="316"/>
-      <c r="HY22" s="316"/>
-      <c r="HZ22" s="316"/>
-      <c r="IA22" s="316"/>
-      <c r="IB22" s="316"/>
-      <c r="IC22" s="316"/>
-      <c r="ID22" s="317"/>
+      <c r="FT22" s="319"/>
+      <c r="FU22" s="319"/>
+      <c r="FV22" s="319"/>
+      <c r="FW22" s="319"/>
+      <c r="FX22" s="319"/>
+      <c r="FY22" s="319"/>
+      <c r="FZ22" s="319"/>
+      <c r="GA22" s="319"/>
+      <c r="GB22" s="319"/>
+      <c r="GC22" s="319"/>
+      <c r="GD22" s="319"/>
+      <c r="GE22" s="319"/>
+      <c r="GF22" s="319"/>
+      <c r="GG22" s="319"/>
+      <c r="GH22" s="319"/>
+      <c r="GI22" s="319"/>
+      <c r="GJ22" s="319"/>
+      <c r="GK22" s="319"/>
+      <c r="GL22" s="319"/>
+      <c r="GM22" s="319"/>
+      <c r="GN22" s="319"/>
+      <c r="GO22" s="319"/>
+      <c r="GP22" s="319"/>
+      <c r="GQ22" s="319"/>
+      <c r="GR22" s="319"/>
+      <c r="GS22" s="319"/>
+      <c r="GT22" s="319"/>
+      <c r="GU22" s="319"/>
+      <c r="GV22" s="319"/>
+      <c r="GW22" s="319"/>
+      <c r="GX22" s="319"/>
+      <c r="GY22" s="319"/>
+      <c r="GZ22" s="319"/>
+      <c r="HA22" s="319"/>
+      <c r="HB22" s="319"/>
+      <c r="HC22" s="319"/>
+      <c r="HD22" s="319"/>
+      <c r="HE22" s="319"/>
+      <c r="HF22" s="319"/>
+      <c r="HG22" s="319"/>
+      <c r="HH22" s="319"/>
+      <c r="HI22" s="319"/>
+      <c r="HJ22" s="319"/>
+      <c r="HK22" s="319"/>
+      <c r="HL22" s="319"/>
+      <c r="HM22" s="319"/>
+      <c r="HN22" s="319"/>
+      <c r="HO22" s="319"/>
+      <c r="HP22" s="319"/>
+      <c r="HQ22" s="319"/>
+      <c r="HR22" s="319"/>
+      <c r="HS22" s="319"/>
+      <c r="HT22" s="319"/>
+      <c r="HU22" s="319"/>
+      <c r="HV22" s="319"/>
+      <c r="HW22" s="319"/>
+      <c r="HX22" s="319"/>
+      <c r="HY22" s="319"/>
+      <c r="HZ22" s="319"/>
+      <c r="IA22" s="319"/>
+      <c r="IB22" s="319"/>
+      <c r="IC22" s="319"/>
+      <c r="ID22" s="320"/>
     </row>
     <row r="23" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="FO23" s="216"/>
       <c r="FP23" s="216"/>
       <c r="FQ23" s="216"/>
       <c r="FR23" s="13"/>
-      <c r="FS23" s="291" t="s">
+      <c r="FS23" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT23" s="280"/>
-      <c r="FU23" s="280"/>
-      <c r="FV23" s="280"/>
-      <c r="FW23" s="280" t="s">
+      <c r="FT23" s="283"/>
+      <c r="FU23" s="283"/>
+      <c r="FV23" s="283"/>
+      <c r="FW23" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="FX23" s="280"/>
-      <c r="FY23" s="280"/>
-      <c r="FZ23" s="280"/>
-      <c r="GA23" s="280" t="s">
+      <c r="FX23" s="283"/>
+      <c r="FY23" s="283"/>
+      <c r="FZ23" s="283"/>
+      <c r="GA23" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="GB23" s="280"/>
-      <c r="GC23" s="280"/>
-      <c r="GD23" s="280"/>
-      <c r="GE23" s="280" t="s">
+      <c r="GB23" s="283"/>
+      <c r="GC23" s="283"/>
+      <c r="GD23" s="283"/>
+      <c r="GE23" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="GF23" s="280"/>
-      <c r="GG23" s="280"/>
-      <c r="GH23" s="280"/>
-      <c r="GI23" s="280" t="s">
+      <c r="GF23" s="283"/>
+      <c r="GG23" s="283"/>
+      <c r="GH23" s="283"/>
+      <c r="GI23" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="GJ23" s="280"/>
-      <c r="GK23" s="280"/>
-      <c r="GL23" s="280"/>
-      <c r="GM23" s="280" t="s">
+      <c r="GJ23" s="283"/>
+      <c r="GK23" s="283"/>
+      <c r="GL23" s="283"/>
+      <c r="GM23" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="GN23" s="280"/>
-      <c r="GO23" s="280"/>
-      <c r="GP23" s="280"/>
-      <c r="GQ23" s="280" t="s">
+      <c r="GN23" s="283"/>
+      <c r="GO23" s="283"/>
+      <c r="GP23" s="283"/>
+      <c r="GQ23" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="GR23" s="280"/>
-      <c r="GS23" s="280"/>
-      <c r="GT23" s="280"/>
-      <c r="GU23" s="280" t="s">
+      <c r="GR23" s="283"/>
+      <c r="GS23" s="283"/>
+      <c r="GT23" s="283"/>
+      <c r="GU23" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="GV23" s="280"/>
-      <c r="GW23" s="280"/>
-      <c r="GX23" s="280"/>
-      <c r="GY23" s="280" t="s">
+      <c r="GV23" s="283"/>
+      <c r="GW23" s="283"/>
+      <c r="GX23" s="283"/>
+      <c r="GY23" s="283" t="s">
         <v>135</v>
       </c>
-      <c r="GZ23" s="280"/>
-      <c r="HA23" s="280"/>
-      <c r="HB23" s="280"/>
-      <c r="HC23" s="280" t="s">
+      <c r="GZ23" s="283"/>
+      <c r="HA23" s="283"/>
+      <c r="HB23" s="283"/>
+      <c r="HC23" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="HD23" s="280"/>
-      <c r="HE23" s="280"/>
-      <c r="HF23" s="280"/>
-      <c r="HG23" s="280" t="s">
+      <c r="HD23" s="283"/>
+      <c r="HE23" s="283"/>
+      <c r="HF23" s="283"/>
+      <c r="HG23" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="HH23" s="280"/>
-      <c r="HI23" s="280"/>
-      <c r="HJ23" s="280"/>
-      <c r="HK23" s="280" t="s">
+      <c r="HH23" s="283"/>
+      <c r="HI23" s="283"/>
+      <c r="HJ23" s="283"/>
+      <c r="HK23" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="HL23" s="280"/>
-      <c r="HM23" s="280"/>
-      <c r="HN23" s="280"/>
-      <c r="HO23" s="280" t="s">
+      <c r="HL23" s="283"/>
+      <c r="HM23" s="283"/>
+      <c r="HN23" s="283"/>
+      <c r="HO23" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="HP23" s="280"/>
-      <c r="HQ23" s="280"/>
-      <c r="HR23" s="280"/>
-      <c r="HS23" s="280" t="s">
+      <c r="HP23" s="283"/>
+      <c r="HQ23" s="283"/>
+      <c r="HR23" s="283"/>
+      <c r="HS23" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="HT23" s="280"/>
-      <c r="HU23" s="280"/>
-      <c r="HV23" s="280"/>
-      <c r="HW23" s="280" t="s">
+      <c r="HT23" s="283"/>
+      <c r="HU23" s="283"/>
+      <c r="HV23" s="283"/>
+      <c r="HW23" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="HX23" s="280"/>
-      <c r="HY23" s="280"/>
-      <c r="HZ23" s="280"/>
-      <c r="IA23" s="280" t="s">
+      <c r="HX23" s="283"/>
+      <c r="HY23" s="283"/>
+      <c r="HZ23" s="283"/>
+      <c r="IA23" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="IB23" s="280"/>
-      <c r="IC23" s="280"/>
-      <c r="ID23" s="281"/>
+      <c r="IB23" s="283"/>
+      <c r="IC23" s="283"/>
+      <c r="ID23" s="284"/>
     </row>
     <row r="24" spans="91:238" x14ac:dyDescent="0.4">
-      <c r="FO24" s="292" t="s">
+      <c r="FO24" s="295" t="s">
         <v>14</v>
       </c>
-      <c r="FP24" s="292"/>
-      <c r="FQ24" s="292"/>
+      <c r="FP24" s="295"/>
+      <c r="FQ24" s="295"/>
       <c r="FR24" s="1"/>
-      <c r="FS24" s="324" t="s">
+      <c r="FS24" s="327" t="s">
         <v>14</v>
       </c>
-      <c r="FT24" s="325"/>
-      <c r="FU24" s="325"/>
-      <c r="FV24" s="325"/>
-      <c r="FW24" s="325"/>
-      <c r="FX24" s="325"/>
-      <c r="FY24" s="325"/>
-      <c r="FZ24" s="325"/>
-      <c r="GA24" s="325"/>
-      <c r="GB24" s="325"/>
-      <c r="GC24" s="325"/>
-      <c r="GD24" s="325"/>
-      <c r="GE24" s="325"/>
-      <c r="GF24" s="325"/>
-      <c r="GG24" s="325"/>
-      <c r="GH24" s="325"/>
-      <c r="GI24" s="325"/>
-      <c r="GJ24" s="325"/>
-      <c r="GK24" s="325"/>
-      <c r="GL24" s="325"/>
-      <c r="GM24" s="325"/>
-      <c r="GN24" s="325"/>
-      <c r="GO24" s="325"/>
-      <c r="GP24" s="325"/>
-      <c r="GQ24" s="325"/>
-      <c r="GR24" s="325"/>
-      <c r="GS24" s="325"/>
-      <c r="GT24" s="325"/>
-      <c r="GU24" s="325"/>
-      <c r="GV24" s="325"/>
-      <c r="GW24" s="325"/>
-      <c r="GX24" s="325"/>
-      <c r="GY24" s="325"/>
-      <c r="GZ24" s="325"/>
-      <c r="HA24" s="325"/>
-      <c r="HB24" s="325"/>
-      <c r="HC24" s="325"/>
-      <c r="HD24" s="325"/>
-      <c r="HE24" s="325"/>
-      <c r="HF24" s="325"/>
-      <c r="HG24" s="325"/>
-      <c r="HH24" s="325"/>
-      <c r="HI24" s="325"/>
-      <c r="HJ24" s="325"/>
-      <c r="HK24" s="325"/>
-      <c r="HL24" s="325"/>
-      <c r="HM24" s="325"/>
-      <c r="HN24" s="325"/>
-      <c r="HO24" s="325"/>
-      <c r="HP24" s="325"/>
-      <c r="HQ24" s="325"/>
-      <c r="HR24" s="325"/>
-      <c r="HS24" s="325"/>
-      <c r="HT24" s="325"/>
-      <c r="HU24" s="325"/>
-      <c r="HV24" s="325"/>
-      <c r="HW24" s="325"/>
-      <c r="HX24" s="325"/>
-      <c r="HY24" s="325"/>
-      <c r="HZ24" s="325"/>
-      <c r="IA24" s="325"/>
-      <c r="IB24" s="325"/>
-      <c r="IC24" s="325"/>
-      <c r="ID24" s="326"/>
+      <c r="FT24" s="328"/>
+      <c r="FU24" s="328"/>
+      <c r="FV24" s="328"/>
+      <c r="FW24" s="328"/>
+      <c r="FX24" s="328"/>
+      <c r="FY24" s="328"/>
+      <c r="FZ24" s="328"/>
+      <c r="GA24" s="328"/>
+      <c r="GB24" s="328"/>
+      <c r="GC24" s="328"/>
+      <c r="GD24" s="328"/>
+      <c r="GE24" s="328"/>
+      <c r="GF24" s="328"/>
+      <c r="GG24" s="328"/>
+      <c r="GH24" s="328"/>
+      <c r="GI24" s="328"/>
+      <c r="GJ24" s="328"/>
+      <c r="GK24" s="328"/>
+      <c r="GL24" s="328"/>
+      <c r="GM24" s="328"/>
+      <c r="GN24" s="328"/>
+      <c r="GO24" s="328"/>
+      <c r="GP24" s="328"/>
+      <c r="GQ24" s="328"/>
+      <c r="GR24" s="328"/>
+      <c r="GS24" s="328"/>
+      <c r="GT24" s="328"/>
+      <c r="GU24" s="328"/>
+      <c r="GV24" s="328"/>
+      <c r="GW24" s="328"/>
+      <c r="GX24" s="328"/>
+      <c r="GY24" s="328"/>
+      <c r="GZ24" s="328"/>
+      <c r="HA24" s="328"/>
+      <c r="HB24" s="328"/>
+      <c r="HC24" s="328"/>
+      <c r="HD24" s="328"/>
+      <c r="HE24" s="328"/>
+      <c r="HF24" s="328"/>
+      <c r="HG24" s="328"/>
+      <c r="HH24" s="328"/>
+      <c r="HI24" s="328"/>
+      <c r="HJ24" s="328"/>
+      <c r="HK24" s="328"/>
+      <c r="HL24" s="328"/>
+      <c r="HM24" s="328"/>
+      <c r="HN24" s="328"/>
+      <c r="HO24" s="328"/>
+      <c r="HP24" s="328"/>
+      <c r="HQ24" s="328"/>
+      <c r="HR24" s="328"/>
+      <c r="HS24" s="328"/>
+      <c r="HT24" s="328"/>
+      <c r="HU24" s="328"/>
+      <c r="HV24" s="328"/>
+      <c r="HW24" s="328"/>
+      <c r="HX24" s="328"/>
+      <c r="HY24" s="328"/>
+      <c r="HZ24" s="328"/>
+      <c r="IA24" s="328"/>
+      <c r="IB24" s="328"/>
+      <c r="IC24" s="328"/>
+      <c r="ID24" s="329"/>
     </row>
     <row r="25" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="FO25" s="216"/>
       <c r="FP25" s="216"/>
       <c r="FQ25" s="216"/>
       <c r="FR25" s="13"/>
-      <c r="FS25" s="327"/>
-      <c r="FT25" s="328"/>
-      <c r="FU25" s="328"/>
-      <c r="FV25" s="328"/>
-      <c r="FW25" s="328"/>
-      <c r="FX25" s="328"/>
-      <c r="FY25" s="328"/>
-      <c r="FZ25" s="328"/>
-      <c r="GA25" s="328"/>
-      <c r="GB25" s="328"/>
-      <c r="GC25" s="328"/>
-      <c r="GD25" s="328"/>
-      <c r="GE25" s="328"/>
-      <c r="GF25" s="328"/>
-      <c r="GG25" s="328"/>
-      <c r="GH25" s="328"/>
-      <c r="GI25" s="328"/>
-      <c r="GJ25" s="328"/>
-      <c r="GK25" s="328"/>
-      <c r="GL25" s="328"/>
-      <c r="GM25" s="328"/>
-      <c r="GN25" s="328"/>
-      <c r="GO25" s="328"/>
-      <c r="GP25" s="328"/>
-      <c r="GQ25" s="328"/>
-      <c r="GR25" s="328"/>
-      <c r="GS25" s="328"/>
-      <c r="GT25" s="328"/>
-      <c r="GU25" s="328"/>
-      <c r="GV25" s="328"/>
-      <c r="GW25" s="328"/>
-      <c r="GX25" s="328"/>
-      <c r="GY25" s="328"/>
-      <c r="GZ25" s="328"/>
-      <c r="HA25" s="328"/>
-      <c r="HB25" s="328"/>
-      <c r="HC25" s="328"/>
-      <c r="HD25" s="328"/>
-      <c r="HE25" s="328"/>
-      <c r="HF25" s="328"/>
-      <c r="HG25" s="328"/>
-      <c r="HH25" s="328"/>
-      <c r="HI25" s="328"/>
-      <c r="HJ25" s="328"/>
-      <c r="HK25" s="328"/>
-      <c r="HL25" s="328"/>
-      <c r="HM25" s="328"/>
-      <c r="HN25" s="328"/>
-      <c r="HO25" s="328"/>
-      <c r="HP25" s="328"/>
-      <c r="HQ25" s="328"/>
-      <c r="HR25" s="328"/>
-      <c r="HS25" s="328"/>
-      <c r="HT25" s="328"/>
-      <c r="HU25" s="328"/>
-      <c r="HV25" s="328"/>
-      <c r="HW25" s="328"/>
-      <c r="HX25" s="328"/>
-      <c r="HY25" s="328"/>
-      <c r="HZ25" s="328"/>
-      <c r="IA25" s="328"/>
-      <c r="IB25" s="328"/>
-      <c r="IC25" s="328"/>
-      <c r="ID25" s="329"/>
+      <c r="FS25" s="330"/>
+      <c r="FT25" s="331"/>
+      <c r="FU25" s="331"/>
+      <c r="FV25" s="331"/>
+      <c r="FW25" s="331"/>
+      <c r="FX25" s="331"/>
+      <c r="FY25" s="331"/>
+      <c r="FZ25" s="331"/>
+      <c r="GA25" s="331"/>
+      <c r="GB25" s="331"/>
+      <c r="GC25" s="331"/>
+      <c r="GD25" s="331"/>
+      <c r="GE25" s="331"/>
+      <c r="GF25" s="331"/>
+      <c r="GG25" s="331"/>
+      <c r="GH25" s="331"/>
+      <c r="GI25" s="331"/>
+      <c r="GJ25" s="331"/>
+      <c r="GK25" s="331"/>
+      <c r="GL25" s="331"/>
+      <c r="GM25" s="331"/>
+      <c r="GN25" s="331"/>
+      <c r="GO25" s="331"/>
+      <c r="GP25" s="331"/>
+      <c r="GQ25" s="331"/>
+      <c r="GR25" s="331"/>
+      <c r="GS25" s="331"/>
+      <c r="GT25" s="331"/>
+      <c r="GU25" s="331"/>
+      <c r="GV25" s="331"/>
+      <c r="GW25" s="331"/>
+      <c r="GX25" s="331"/>
+      <c r="GY25" s="331"/>
+      <c r="GZ25" s="331"/>
+      <c r="HA25" s="331"/>
+      <c r="HB25" s="331"/>
+      <c r="HC25" s="331"/>
+      <c r="HD25" s="331"/>
+      <c r="HE25" s="331"/>
+      <c r="HF25" s="331"/>
+      <c r="HG25" s="331"/>
+      <c r="HH25" s="331"/>
+      <c r="HI25" s="331"/>
+      <c r="HJ25" s="331"/>
+      <c r="HK25" s="331"/>
+      <c r="HL25" s="331"/>
+      <c r="HM25" s="331"/>
+      <c r="HN25" s="331"/>
+      <c r="HO25" s="331"/>
+      <c r="HP25" s="331"/>
+      <c r="HQ25" s="331"/>
+      <c r="HR25" s="331"/>
+      <c r="HS25" s="331"/>
+      <c r="HT25" s="331"/>
+      <c r="HU25" s="331"/>
+      <c r="HV25" s="331"/>
+      <c r="HW25" s="331"/>
+      <c r="HX25" s="331"/>
+      <c r="HY25" s="331"/>
+      <c r="HZ25" s="331"/>
+      <c r="IA25" s="331"/>
+      <c r="IB25" s="331"/>
+      <c r="IC25" s="331"/>
+      <c r="ID25" s="332"/>
     </row>
     <row r="26" spans="91:238" x14ac:dyDescent="0.4">
-      <c r="FO26" s="332" t="s">
+      <c r="FO26" s="335" t="s">
         <v>145</v>
       </c>
-      <c r="FP26" s="332"/>
-      <c r="FQ26" s="332"/>
+      <c r="FP26" s="335"/>
+      <c r="FQ26" s="335"/>
       <c r="FR26" s="1"/>
-      <c r="FS26" s="315" t="s">
+      <c r="FS26" s="318" t="s">
         <v>150</v>
       </c>
-      <c r="FT26" s="316"/>
-      <c r="FU26" s="316"/>
-      <c r="FV26" s="316"/>
-      <c r="FW26" s="316"/>
-      <c r="FX26" s="316"/>
-      <c r="FY26" s="316"/>
-      <c r="FZ26" s="316"/>
-      <c r="GA26" s="316"/>
-      <c r="GB26" s="316"/>
-      <c r="GC26" s="316"/>
-      <c r="GD26" s="316"/>
-      <c r="GE26" s="316"/>
-      <c r="GF26" s="316"/>
-      <c r="GG26" s="316"/>
-      <c r="GH26" s="316"/>
-      <c r="GI26" s="316"/>
-      <c r="GJ26" s="316"/>
-      <c r="GK26" s="316"/>
-      <c r="GL26" s="316"/>
-      <c r="GM26" s="316"/>
-      <c r="GN26" s="316"/>
-      <c r="GO26" s="316"/>
-      <c r="GP26" s="316"/>
-      <c r="GQ26" s="316"/>
-      <c r="GR26" s="316"/>
-      <c r="GS26" s="316"/>
-      <c r="GT26" s="316"/>
-      <c r="GU26" s="316"/>
-      <c r="GV26" s="316"/>
-      <c r="GW26" s="316"/>
-      <c r="GX26" s="316"/>
-      <c r="GY26" s="316"/>
-      <c r="GZ26" s="316"/>
-      <c r="HA26" s="316"/>
-      <c r="HB26" s="316"/>
-      <c r="HC26" s="316"/>
-      <c r="HD26" s="316"/>
-      <c r="HE26" s="316"/>
-      <c r="HF26" s="316"/>
-      <c r="HG26" s="316"/>
-      <c r="HH26" s="316"/>
-      <c r="HI26" s="316"/>
-      <c r="HJ26" s="316"/>
-      <c r="HK26" s="316"/>
-      <c r="HL26" s="316"/>
-      <c r="HM26" s="316"/>
-      <c r="HN26" s="316"/>
-      <c r="HO26" s="316"/>
-      <c r="HP26" s="316"/>
-      <c r="HQ26" s="316"/>
-      <c r="HR26" s="316"/>
-      <c r="HS26" s="316"/>
-      <c r="HT26" s="316"/>
-      <c r="HU26" s="316"/>
-      <c r="HV26" s="316"/>
-      <c r="HW26" s="316"/>
-      <c r="HX26" s="316"/>
-      <c r="HY26" s="316"/>
-      <c r="HZ26" s="316"/>
-      <c r="IA26" s="316"/>
-      <c r="IB26" s="316"/>
-      <c r="IC26" s="316"/>
-      <c r="ID26" s="317"/>
+      <c r="FT26" s="319"/>
+      <c r="FU26" s="319"/>
+      <c r="FV26" s="319"/>
+      <c r="FW26" s="319"/>
+      <c r="FX26" s="319"/>
+      <c r="FY26" s="319"/>
+      <c r="FZ26" s="319"/>
+      <c r="GA26" s="319"/>
+      <c r="GB26" s="319"/>
+      <c r="GC26" s="319"/>
+      <c r="GD26" s="319"/>
+      <c r="GE26" s="319"/>
+      <c r="GF26" s="319"/>
+      <c r="GG26" s="319"/>
+      <c r="GH26" s="319"/>
+      <c r="GI26" s="319"/>
+      <c r="GJ26" s="319"/>
+      <c r="GK26" s="319"/>
+      <c r="GL26" s="319"/>
+      <c r="GM26" s="319"/>
+      <c r="GN26" s="319"/>
+      <c r="GO26" s="319"/>
+      <c r="GP26" s="319"/>
+      <c r="GQ26" s="319"/>
+      <c r="GR26" s="319"/>
+      <c r="GS26" s="319"/>
+      <c r="GT26" s="319"/>
+      <c r="GU26" s="319"/>
+      <c r="GV26" s="319"/>
+      <c r="GW26" s="319"/>
+      <c r="GX26" s="319"/>
+      <c r="GY26" s="319"/>
+      <c r="GZ26" s="319"/>
+      <c r="HA26" s="319"/>
+      <c r="HB26" s="319"/>
+      <c r="HC26" s="319"/>
+      <c r="HD26" s="319"/>
+      <c r="HE26" s="319"/>
+      <c r="HF26" s="319"/>
+      <c r="HG26" s="319"/>
+      <c r="HH26" s="319"/>
+      <c r="HI26" s="319"/>
+      <c r="HJ26" s="319"/>
+      <c r="HK26" s="319"/>
+      <c r="HL26" s="319"/>
+      <c r="HM26" s="319"/>
+      <c r="HN26" s="319"/>
+      <c r="HO26" s="319"/>
+      <c r="HP26" s="319"/>
+      <c r="HQ26" s="319"/>
+      <c r="HR26" s="319"/>
+      <c r="HS26" s="319"/>
+      <c r="HT26" s="319"/>
+      <c r="HU26" s="319"/>
+      <c r="HV26" s="319"/>
+      <c r="HW26" s="319"/>
+      <c r="HX26" s="319"/>
+      <c r="HY26" s="319"/>
+      <c r="HZ26" s="319"/>
+      <c r="IA26" s="319"/>
+      <c r="IB26" s="319"/>
+      <c r="IC26" s="319"/>
+      <c r="ID26" s="320"/>
     </row>
     <row r="27" spans="91:238" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="FO27" s="333"/>
-      <c r="FP27" s="333"/>
-      <c r="FQ27" s="333"/>
+      <c r="FO27" s="336"/>
+      <c r="FP27" s="336"/>
+      <c r="FQ27" s="336"/>
       <c r="FR27" s="13"/>
-      <c r="FS27" s="291" t="s">
+      <c r="FS27" s="294" t="s">
         <v>128</v>
       </c>
-      <c r="FT27" s="280"/>
-      <c r="FU27" s="280"/>
-      <c r="FV27" s="280"/>
-      <c r="FW27" s="280" t="s">
+      <c r="FT27" s="283"/>
+      <c r="FU27" s="283"/>
+      <c r="FV27" s="283"/>
+      <c r="FW27" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="FX27" s="280"/>
-      <c r="FY27" s="280"/>
-      <c r="FZ27" s="280"/>
-      <c r="GA27" s="280" t="s">
+      <c r="FX27" s="283"/>
+      <c r="FY27" s="283"/>
+      <c r="FZ27" s="283"/>
+      <c r="GA27" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="GB27" s="280"/>
-      <c r="GC27" s="280"/>
-      <c r="GD27" s="280"/>
-      <c r="GE27" s="280" t="s">
+      <c r="GB27" s="283"/>
+      <c r="GC27" s="283"/>
+      <c r="GD27" s="283"/>
+      <c r="GE27" s="283" t="s">
         <v>124</v>
       </c>
-      <c r="GF27" s="280"/>
-      <c r="GG27" s="280"/>
-      <c r="GH27" s="280"/>
-      <c r="GI27" s="280" t="s">
+      <c r="GF27" s="283"/>
+      <c r="GG27" s="283"/>
+      <c r="GH27" s="283"/>
+      <c r="GI27" s="283" t="s">
         <v>123</v>
       </c>
-      <c r="GJ27" s="280"/>
-      <c r="GK27" s="280"/>
-      <c r="GL27" s="280"/>
-      <c r="GM27" s="280" t="s">
+      <c r="GJ27" s="283"/>
+      <c r="GK27" s="283"/>
+      <c r="GL27" s="283"/>
+      <c r="GM27" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="GN27" s="280"/>
-      <c r="GO27" s="280"/>
-      <c r="GP27" s="280"/>
-      <c r="GQ27" s="280" t="s">
+      <c r="GN27" s="283"/>
+      <c r="GO27" s="283"/>
+      <c r="GP27" s="283"/>
+      <c r="GQ27" s="283" t="s">
         <v>133</v>
       </c>
-      <c r="GR27" s="280"/>
-      <c r="GS27" s="280"/>
-      <c r="GT27" s="280"/>
-      <c r="GU27" s="280" t="s">
+      <c r="GR27" s="283"/>
+      <c r="GS27" s="283"/>
+      <c r="GT27" s="283"/>
+      <c r="GU27" s="283" t="s">
         <v>134</v>
       </c>
-      <c r="GV27" s="280"/>
-      <c r="GW27" s="280"/>
-      <c r="GX27" s="280"/>
-      <c r="GY27" s="280" t="s">
+      <c r="GV27" s="283"/>
+      <c r="GW27" s="283"/>
+      <c r="GX27" s="283"/>
+      <c r="GY27" s="283" t="s">
         <v>135</v>
       </c>
-      <c r="GZ27" s="280"/>
-      <c r="HA27" s="280"/>
-      <c r="HB27" s="280"/>
-      <c r="HC27" s="280" t="s">
+      <c r="GZ27" s="283"/>
+      <c r="HA27" s="283"/>
+      <c r="HB27" s="283"/>
+      <c r="HC27" s="283" t="s">
         <v>136</v>
       </c>
-      <c r="HD27" s="280"/>
-      <c r="HE27" s="280"/>
-      <c r="HF27" s="280"/>
-      <c r="HG27" s="280" t="s">
+      <c r="HD27" s="283"/>
+      <c r="HE27" s="283"/>
+      <c r="HF27" s="283"/>
+      <c r="HG27" s="283" t="s">
         <v>137</v>
       </c>
-      <c r="HH27" s="280"/>
-      <c r="HI27" s="280"/>
-      <c r="HJ27" s="280"/>
-      <c r="HK27" s="280" t="s">
+      <c r="HH27" s="283"/>
+      <c r="HI27" s="283"/>
+      <c r="HJ27" s="283"/>
+      <c r="HK27" s="283" t="s">
         <v>138</v>
       </c>
-      <c r="HL27" s="280"/>
-      <c r="HM27" s="280"/>
-      <c r="HN27" s="280"/>
-      <c r="HO27" s="280" t="s">
+      <c r="HL27" s="283"/>
+      <c r="HM27" s="283"/>
+      <c r="HN27" s="283"/>
+      <c r="HO27" s="283" t="s">
         <v>139</v>
       </c>
-      <c r="HP27" s="280"/>
-      <c r="HQ27" s="280"/>
-      <c r="HR27" s="280"/>
-      <c r="HS27" s="280" t="s">
+      <c r="HP27" s="283"/>
+      <c r="HQ27" s="283"/>
+      <c r="HR27" s="283"/>
+      <c r="HS27" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="HT27" s="280"/>
-      <c r="HU27" s="280"/>
-      <c r="HV27" s="280"/>
-      <c r="HW27" s="280" t="s">
+      <c r="HT27" s="283"/>
+      <c r="HU27" s="283"/>
+      <c r="HV27" s="283"/>
+      <c r="HW27" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="HX27" s="280"/>
-      <c r="HY27" s="280"/>
-      <c r="HZ27" s="280"/>
-      <c r="IA27" s="280" t="s">
+      <c r="HX27" s="283"/>
+      <c r="HY27" s="283"/>
+      <c r="HZ27" s="283"/>
+      <c r="IA27" s="283" t="s">
         <v>142</v>
       </c>
-      <c r="IB27" s="280"/>
-      <c r="IC27" s="280"/>
-      <c r="ID27" s="281"/>
+      <c r="IB27" s="283"/>
+      <c r="IC27" s="283"/>
+      <c r="ID27" s="284"/>
     </row>
   </sheetData>
   <mergeCells count="317">
@@ -39704,7 +41280,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="9:46" x14ac:dyDescent="0.4">
-      <c r="AG2" s="336" t="s">
+      <c r="AG2" s="339" t="s">
         <v>610</v>
       </c>
       <c r="AH2" s="144"/>
@@ -39722,611 +41298,611 @@
       <c r="AT2" s="144"/>
     </row>
     <row r="4" spans="9:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="L4" s="362" t="s">
+      <c r="L4" s="365" t="s">
         <v>609</v>
       </c>
-      <c r="M4" s="362"/>
-      <c r="N4" s="362"/>
-      <c r="O4" s="362"/>
-      <c r="P4" s="362"/>
-      <c r="Q4" s="362"/>
-      <c r="R4" s="362"/>
-      <c r="S4" s="362"/>
-      <c r="AJ4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="365"/>
+      <c r="O4" s="365"/>
+      <c r="P4" s="365"/>
+      <c r="Q4" s="365"/>
+      <c r="R4" s="365"/>
+      <c r="S4" s="365"/>
+      <c r="AJ4" s="365" t="s">
         <v>609</v>
       </c>
-      <c r="AK4" s="362"/>
-      <c r="AL4" s="362"/>
-      <c r="AM4" s="362"/>
-      <c r="AN4" s="362"/>
-      <c r="AO4" s="362"/>
-      <c r="AP4" s="362"/>
-      <c r="AQ4" s="362"/>
+      <c r="AK4" s="365"/>
+      <c r="AL4" s="365"/>
+      <c r="AM4" s="365"/>
+      <c r="AN4" s="365"/>
+      <c r="AO4" s="365"/>
+      <c r="AP4" s="365"/>
+      <c r="AQ4" s="365"/>
     </row>
     <row r="5" spans="9:46" x14ac:dyDescent="0.4">
-      <c r="I5" s="343" t="s">
+      <c r="I5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="J5" s="344"/>
-      <c r="K5" s="343"/>
-      <c r="L5" s="344"/>
-      <c r="M5" s="343" t="s">
+      <c r="J5" s="347"/>
+      <c r="K5" s="346"/>
+      <c r="L5" s="347"/>
+      <c r="M5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="N5" s="344"/>
-      <c r="O5" s="343" t="s">
+      <c r="N5" s="347"/>
+      <c r="O5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="P5" s="344"/>
-      <c r="Q5" s="343" t="s">
+      <c r="P5" s="347"/>
+      <c r="Q5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="R5" s="344"/>
-      <c r="S5" s="343" t="s">
+      <c r="R5" s="347"/>
+      <c r="S5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="T5" s="344"/>
-      <c r="U5" s="343" t="s">
+      <c r="T5" s="347"/>
+      <c r="U5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="V5" s="344"/>
-      <c r="AG5" s="343" t="s">
+      <c r="V5" s="347"/>
+      <c r="AG5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH5" s="344"/>
-      <c r="AI5" s="343"/>
-      <c r="AJ5" s="344"/>
-      <c r="AK5" s="343" t="s">
+      <c r="AH5" s="347"/>
+      <c r="AI5" s="346"/>
+      <c r="AJ5" s="347"/>
+      <c r="AK5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL5" s="344"/>
-      <c r="AM5" s="343" t="s">
+      <c r="AL5" s="347"/>
+      <c r="AM5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AN5" s="344"/>
-      <c r="AO5" s="343" t="s">
+      <c r="AN5" s="347"/>
+      <c r="AO5" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AP5" s="344"/>
-      <c r="AQ5" s="337" t="s">
+      <c r="AP5" s="347"/>
+      <c r="AQ5" s="340" t="s">
         <v>606</v>
       </c>
-      <c r="AR5" s="338"/>
-      <c r="AS5" s="337" t="s">
+      <c r="AR5" s="341"/>
+      <c r="AS5" s="340" t="s">
         <v>605</v>
       </c>
-      <c r="AT5" s="338"/>
+      <c r="AT5" s="341"/>
     </row>
     <row r="6" spans="9:46" x14ac:dyDescent="0.4">
-      <c r="I6" s="345"/>
-      <c r="J6" s="346"/>
-      <c r="K6" s="345"/>
-      <c r="L6" s="346"/>
-      <c r="M6" s="345"/>
-      <c r="N6" s="346"/>
-      <c r="O6" s="345"/>
-      <c r="P6" s="346"/>
-      <c r="Q6" s="345"/>
-      <c r="R6" s="346"/>
-      <c r="S6" s="345"/>
-      <c r="T6" s="346"/>
-      <c r="U6" s="345"/>
-      <c r="V6" s="346"/>
-      <c r="AG6" s="345"/>
-      <c r="AH6" s="346"/>
-      <c r="AI6" s="345"/>
-      <c r="AJ6" s="346"/>
-      <c r="AK6" s="345"/>
-      <c r="AL6" s="346"/>
-      <c r="AM6" s="345"/>
-      <c r="AN6" s="346"/>
-      <c r="AO6" s="345"/>
-      <c r="AP6" s="346"/>
-      <c r="AQ6" s="339"/>
-      <c r="AR6" s="340"/>
-      <c r="AS6" s="339"/>
-      <c r="AT6" s="340"/>
+      <c r="I6" s="348"/>
+      <c r="J6" s="349"/>
+      <c r="K6" s="348"/>
+      <c r="L6" s="349"/>
+      <c r="M6" s="348"/>
+      <c r="N6" s="349"/>
+      <c r="O6" s="348"/>
+      <c r="P6" s="349"/>
+      <c r="Q6" s="348"/>
+      <c r="R6" s="349"/>
+      <c r="S6" s="348"/>
+      <c r="T6" s="349"/>
+      <c r="U6" s="348"/>
+      <c r="V6" s="349"/>
+      <c r="AG6" s="348"/>
+      <c r="AH6" s="349"/>
+      <c r="AI6" s="348"/>
+      <c r="AJ6" s="349"/>
+      <c r="AK6" s="348"/>
+      <c r="AL6" s="349"/>
+      <c r="AM6" s="348"/>
+      <c r="AN6" s="349"/>
+      <c r="AO6" s="348"/>
+      <c r="AP6" s="349"/>
+      <c r="AQ6" s="342"/>
+      <c r="AR6" s="343"/>
+      <c r="AS6" s="342"/>
+      <c r="AT6" s="343"/>
     </row>
     <row r="7" spans="9:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="I7" s="341" t="s">
+      <c r="I7" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="J7" s="342"/>
-      <c r="K7" s="341" t="s">
+      <c r="J7" s="345"/>
+      <c r="K7" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="342"/>
-      <c r="M7" s="341" t="s">
+      <c r="L7" s="345"/>
+      <c r="M7" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="342"/>
-      <c r="O7" s="341" t="s">
+      <c r="N7" s="345"/>
+      <c r="O7" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="P7" s="342"/>
-      <c r="Q7" s="341" t="s">
+      <c r="P7" s="345"/>
+      <c r="Q7" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="R7" s="342"/>
-      <c r="S7" s="341" t="s">
+      <c r="R7" s="345"/>
+      <c r="S7" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="342"/>
-      <c r="U7" s="341" t="s">
+      <c r="T7" s="345"/>
+      <c r="U7" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="V7" s="342"/>
-      <c r="AG7" s="341" t="s">
+      <c r="V7" s="345"/>
+      <c r="AG7" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH7" s="342"/>
-      <c r="AI7" s="341" t="s">
+      <c r="AH7" s="345"/>
+      <c r="AI7" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ7" s="342"/>
-      <c r="AK7" s="341" t="s">
+      <c r="AJ7" s="345"/>
+      <c r="AK7" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL7" s="342"/>
-      <c r="AM7" s="341" t="s">
+      <c r="AL7" s="345"/>
+      <c r="AM7" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN7" s="342"/>
-      <c r="AO7" s="341" t="s">
+      <c r="AN7" s="345"/>
+      <c r="AO7" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP7" s="342"/>
-      <c r="AQ7" s="341" t="s">
+      <c r="AP7" s="345"/>
+      <c r="AQ7" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR7" s="342"/>
-      <c r="AS7" s="341" t="s">
+      <c r="AR7" s="345"/>
+      <c r="AS7" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT7" s="342"/>
+      <c r="AT7" s="345"/>
     </row>
     <row r="11" spans="9:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="9:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="I12" s="343" t="s">
+      <c r="I12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="J12" s="344"/>
-      <c r="K12" s="343"/>
-      <c r="L12" s="344"/>
-      <c r="M12" s="343" t="s">
+      <c r="J12" s="347"/>
+      <c r="K12" s="346"/>
+      <c r="L12" s="347"/>
+      <c r="M12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="N12" s="344"/>
-      <c r="O12" s="343" t="s">
+      <c r="N12" s="347"/>
+      <c r="O12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="P12" s="344"/>
-      <c r="Q12" s="343" t="s">
+      <c r="P12" s="347"/>
+      <c r="Q12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="R12" s="344"/>
-      <c r="S12" s="337" t="s">
+      <c r="R12" s="347"/>
+      <c r="S12" s="340" t="s">
         <v>606</v>
       </c>
-      <c r="T12" s="338"/>
-      <c r="U12" s="337" t="s">
+      <c r="T12" s="341"/>
+      <c r="U12" s="340" t="s">
         <v>605</v>
       </c>
-      <c r="V12" s="338"/>
-      <c r="AG12" s="343" t="s">
+      <c r="V12" s="341"/>
+      <c r="AG12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH12" s="344"/>
-      <c r="AI12" s="343"/>
-      <c r="AJ12" s="344"/>
-      <c r="AK12" s="343" t="s">
+      <c r="AH12" s="347"/>
+      <c r="AI12" s="346"/>
+      <c r="AJ12" s="347"/>
+      <c r="AK12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL12" s="344"/>
-      <c r="AM12" s="343" t="s">
+      <c r="AL12" s="347"/>
+      <c r="AM12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AN12" s="344"/>
-      <c r="AO12" s="343" t="s">
+      <c r="AN12" s="347"/>
+      <c r="AO12" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AP12" s="344"/>
-      <c r="AQ12" s="337" t="s">
+      <c r="AP12" s="347"/>
+      <c r="AQ12" s="340" t="s">
         <v>606</v>
       </c>
-      <c r="AR12" s="347"/>
-      <c r="AS12" s="361" t="s">
+      <c r="AR12" s="350"/>
+      <c r="AS12" s="364" t="s">
         <v>605</v>
       </c>
-      <c r="AT12" s="349"/>
+      <c r="AT12" s="352"/>
     </row>
     <row r="13" spans="9:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="I13" s="345"/>
-      <c r="J13" s="346"/>
-      <c r="K13" s="345"/>
-      <c r="L13" s="346"/>
-      <c r="M13" s="345"/>
-      <c r="N13" s="346"/>
-      <c r="O13" s="345"/>
-      <c r="P13" s="346"/>
-      <c r="Q13" s="345"/>
-      <c r="R13" s="346"/>
-      <c r="S13" s="339"/>
-      <c r="T13" s="340"/>
-      <c r="U13" s="339"/>
-      <c r="V13" s="340"/>
-      <c r="AG13" s="345"/>
-      <c r="AH13" s="346"/>
-      <c r="AI13" s="345"/>
-      <c r="AJ13" s="346"/>
-      <c r="AK13" s="345"/>
-      <c r="AL13" s="346"/>
-      <c r="AM13" s="345"/>
-      <c r="AN13" s="346"/>
-      <c r="AO13" s="345"/>
-      <c r="AP13" s="346"/>
-      <c r="AQ13" s="339"/>
+      <c r="I13" s="348"/>
+      <c r="J13" s="349"/>
+      <c r="K13" s="348"/>
+      <c r="L13" s="349"/>
+      <c r="M13" s="348"/>
+      <c r="N13" s="349"/>
+      <c r="O13" s="348"/>
+      <c r="P13" s="349"/>
+      <c r="Q13" s="348"/>
+      <c r="R13" s="349"/>
+      <c r="S13" s="342"/>
+      <c r="T13" s="343"/>
+      <c r="U13" s="342"/>
+      <c r="V13" s="343"/>
+      <c r="AG13" s="348"/>
+      <c r="AH13" s="349"/>
+      <c r="AI13" s="348"/>
+      <c r="AJ13" s="349"/>
+      <c r="AK13" s="348"/>
+      <c r="AL13" s="349"/>
+      <c r="AM13" s="348"/>
+      <c r="AN13" s="349"/>
+      <c r="AO13" s="348"/>
+      <c r="AP13" s="349"/>
+      <c r="AQ13" s="342"/>
       <c r="AR13" s="154"/>
-      <c r="AS13" s="350"/>
-      <c r="AT13" s="351"/>
+      <c r="AS13" s="353"/>
+      <c r="AT13" s="354"/>
     </row>
     <row r="14" spans="9:46" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="I14" s="341" t="s">
+      <c r="I14" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="J14" s="342"/>
-      <c r="K14" s="341" t="s">
+      <c r="J14" s="345"/>
+      <c r="K14" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="342"/>
-      <c r="M14" s="341" t="s">
+      <c r="L14" s="345"/>
+      <c r="M14" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="342"/>
-      <c r="O14" s="341" t="s">
+      <c r="N14" s="345"/>
+      <c r="O14" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="P14" s="342"/>
-      <c r="Q14" s="341" t="s">
+      <c r="P14" s="345"/>
+      <c r="Q14" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="R14" s="342"/>
-      <c r="S14" s="341" t="s">
+      <c r="R14" s="345"/>
+      <c r="S14" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="T14" s="342"/>
-      <c r="U14" s="341" t="s">
+      <c r="T14" s="345"/>
+      <c r="U14" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="V14" s="342"/>
-      <c r="AG14" s="341" t="s">
+      <c r="V14" s="345"/>
+      <c r="AG14" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH14" s="342"/>
-      <c r="AI14" s="341" t="s">
+      <c r="AH14" s="345"/>
+      <c r="AI14" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ14" s="342"/>
-      <c r="AK14" s="341" t="s">
+      <c r="AJ14" s="345"/>
+      <c r="AK14" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL14" s="342"/>
-      <c r="AM14" s="341" t="s">
+      <c r="AL14" s="345"/>
+      <c r="AM14" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN14" s="342"/>
-      <c r="AO14" s="341" t="s">
+      <c r="AN14" s="345"/>
+      <c r="AO14" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP14" s="342"/>
-      <c r="AQ14" s="341" t="s">
+      <c r="AP14" s="345"/>
+      <c r="AQ14" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR14" s="342"/>
-      <c r="AS14" s="341" t="s">
+      <c r="AR14" s="345"/>
+      <c r="AS14" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT14" s="342"/>
+      <c r="AT14" s="345"/>
     </row>
     <row r="18" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="33:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="AG19" s="343" t="s">
+      <c r="AG19" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH19" s="344"/>
-      <c r="AI19" s="343"/>
-      <c r="AJ19" s="344"/>
-      <c r="AK19" s="343" t="s">
+      <c r="AH19" s="347"/>
+      <c r="AI19" s="346"/>
+      <c r="AJ19" s="347"/>
+      <c r="AK19" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL19" s="344"/>
-      <c r="AM19" s="343" t="s">
+      <c r="AL19" s="347"/>
+      <c r="AM19" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AN19" s="344"/>
-      <c r="AO19" s="343" t="s">
+      <c r="AN19" s="347"/>
+      <c r="AO19" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AP19" s="359"/>
-      <c r="AQ19" s="348" t="s">
+      <c r="AP19" s="362"/>
+      <c r="AQ19" s="351" t="s">
         <v>606</v>
       </c>
-      <c r="AR19" s="349"/>
-      <c r="AS19" s="347" t="s">
+      <c r="AR19" s="352"/>
+      <c r="AS19" s="350" t="s">
         <v>605</v>
       </c>
-      <c r="AT19" s="338"/>
+      <c r="AT19" s="341"/>
     </row>
     <row r="20" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG20" s="345"/>
-      <c r="AH20" s="346"/>
-      <c r="AI20" s="345"/>
-      <c r="AJ20" s="346"/>
-      <c r="AK20" s="345"/>
-      <c r="AL20" s="346"/>
-      <c r="AM20" s="345"/>
-      <c r="AN20" s="346"/>
-      <c r="AO20" s="345"/>
-      <c r="AP20" s="360"/>
-      <c r="AQ20" s="350"/>
-      <c r="AR20" s="351"/>
+      <c r="AG20" s="348"/>
+      <c r="AH20" s="349"/>
+      <c r="AI20" s="348"/>
+      <c r="AJ20" s="349"/>
+      <c r="AK20" s="348"/>
+      <c r="AL20" s="349"/>
+      <c r="AM20" s="348"/>
+      <c r="AN20" s="349"/>
+      <c r="AO20" s="348"/>
+      <c r="AP20" s="363"/>
+      <c r="AQ20" s="353"/>
+      <c r="AR20" s="354"/>
       <c r="AS20" s="154"/>
-      <c r="AT20" s="340"/>
+      <c r="AT20" s="343"/>
     </row>
     <row r="21" spans="33:46" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG21" s="341" t="s">
+      <c r="AG21" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH21" s="342"/>
-      <c r="AI21" s="341" t="s">
+      <c r="AH21" s="345"/>
+      <c r="AI21" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ21" s="342"/>
-      <c r="AK21" s="341" t="s">
+      <c r="AJ21" s="345"/>
+      <c r="AK21" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL21" s="342"/>
-      <c r="AM21" s="341" t="s">
+      <c r="AL21" s="345"/>
+      <c r="AM21" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN21" s="342"/>
-      <c r="AO21" s="341" t="s">
+      <c r="AN21" s="345"/>
+      <c r="AO21" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP21" s="342"/>
-      <c r="AQ21" s="341" t="s">
+      <c r="AP21" s="345"/>
+      <c r="AQ21" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR21" s="342"/>
-      <c r="AS21" s="341" t="s">
+      <c r="AR21" s="345"/>
+      <c r="AS21" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT21" s="342"/>
+      <c r="AT21" s="345"/>
     </row>
     <row r="25" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="26" spans="33:46" x14ac:dyDescent="0.4">
-      <c r="AG26" s="343" t="s">
+      <c r="AG26" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH26" s="344"/>
-      <c r="AI26" s="343"/>
-      <c r="AJ26" s="344"/>
-      <c r="AK26" s="343" t="s">
+      <c r="AH26" s="347"/>
+      <c r="AI26" s="346"/>
+      <c r="AJ26" s="347"/>
+      <c r="AK26" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL26" s="344"/>
-      <c r="AM26" s="343" t="s">
+      <c r="AL26" s="347"/>
+      <c r="AM26" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AN26" s="344"/>
-      <c r="AO26" s="343" t="s">
+      <c r="AN26" s="347"/>
+      <c r="AO26" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AP26" s="344"/>
-      <c r="AQ26" s="337" t="s">
+      <c r="AP26" s="347"/>
+      <c r="AQ26" s="340" t="s">
         <v>606</v>
       </c>
-      <c r="AR26" s="338"/>
-      <c r="AS26" s="337" t="s">
+      <c r="AR26" s="341"/>
+      <c r="AS26" s="340" t="s">
         <v>605</v>
       </c>
-      <c r="AT26" s="338"/>
+      <c r="AT26" s="341"/>
     </row>
     <row r="27" spans="33:46" x14ac:dyDescent="0.4">
-      <c r="AG27" s="345"/>
-      <c r="AH27" s="346"/>
-      <c r="AI27" s="345"/>
-      <c r="AJ27" s="346"/>
-      <c r="AK27" s="345"/>
-      <c r="AL27" s="346"/>
-      <c r="AM27" s="345"/>
-      <c r="AN27" s="346"/>
-      <c r="AO27" s="345"/>
-      <c r="AP27" s="346"/>
-      <c r="AQ27" s="339"/>
-      <c r="AR27" s="340"/>
-      <c r="AS27" s="339"/>
-      <c r="AT27" s="340"/>
+      <c r="AG27" s="348"/>
+      <c r="AH27" s="349"/>
+      <c r="AI27" s="348"/>
+      <c r="AJ27" s="349"/>
+      <c r="AK27" s="348"/>
+      <c r="AL27" s="349"/>
+      <c r="AM27" s="348"/>
+      <c r="AN27" s="349"/>
+      <c r="AO27" s="348"/>
+      <c r="AP27" s="349"/>
+      <c r="AQ27" s="342"/>
+      <c r="AR27" s="343"/>
+      <c r="AS27" s="342"/>
+      <c r="AT27" s="343"/>
     </row>
     <row r="28" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG28" s="341" t="s">
+      <c r="AG28" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH28" s="342"/>
-      <c r="AI28" s="341" t="s">
+      <c r="AH28" s="345"/>
+      <c r="AI28" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ28" s="342"/>
-      <c r="AK28" s="341" t="s">
+      <c r="AJ28" s="345"/>
+      <c r="AK28" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL28" s="342"/>
-      <c r="AM28" s="341" t="s">
+      <c r="AL28" s="345"/>
+      <c r="AM28" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN28" s="342"/>
-      <c r="AO28" s="341" t="s">
+      <c r="AN28" s="345"/>
+      <c r="AO28" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP28" s="342"/>
-      <c r="AQ28" s="341" t="s">
+      <c r="AP28" s="345"/>
+      <c r="AQ28" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR28" s="342"/>
-      <c r="AS28" s="341" t="s">
+      <c r="AR28" s="345"/>
+      <c r="AS28" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT28" s="342"/>
+      <c r="AT28" s="345"/>
     </row>
     <row r="32" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="33" spans="33:46" x14ac:dyDescent="0.4">
-      <c r="AG33" s="343" t="s">
+      <c r="AG33" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH33" s="344"/>
-      <c r="AI33" s="343"/>
-      <c r="AJ33" s="344"/>
-      <c r="AK33" s="343" t="s">
+      <c r="AH33" s="347"/>
+      <c r="AI33" s="346"/>
+      <c r="AJ33" s="347"/>
+      <c r="AK33" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL33" s="344"/>
-      <c r="AM33" s="337" t="s">
+      <c r="AL33" s="347"/>
+      <c r="AM33" s="340" t="s">
         <v>608</v>
       </c>
-      <c r="AN33" s="347"/>
-      <c r="AO33" s="354" t="s">
+      <c r="AN33" s="350"/>
+      <c r="AO33" s="357" t="s">
         <v>607</v>
       </c>
-      <c r="AP33" s="355"/>
-      <c r="AQ33" s="347" t="s">
+      <c r="AP33" s="358"/>
+      <c r="AQ33" s="350" t="s">
         <v>606</v>
       </c>
-      <c r="AR33" s="338"/>
-      <c r="AS33" s="337" t="s">
+      <c r="AR33" s="341"/>
+      <c r="AS33" s="340" t="s">
         <v>605</v>
       </c>
-      <c r="AT33" s="338"/>
+      <c r="AT33" s="341"/>
     </row>
     <row r="34" spans="33:46" x14ac:dyDescent="0.4">
-      <c r="AG34" s="345"/>
-      <c r="AH34" s="346"/>
-      <c r="AI34" s="345"/>
-      <c r="AJ34" s="346"/>
-      <c r="AK34" s="345"/>
-      <c r="AL34" s="346"/>
-      <c r="AM34" s="339"/>
+      <c r="AG34" s="348"/>
+      <c r="AH34" s="349"/>
+      <c r="AI34" s="348"/>
+      <c r="AJ34" s="349"/>
+      <c r="AK34" s="348"/>
+      <c r="AL34" s="349"/>
+      <c r="AM34" s="342"/>
       <c r="AN34" s="154"/>
-      <c r="AO34" s="356"/>
-      <c r="AP34" s="357"/>
-      <c r="AQ34" s="358"/>
-      <c r="AR34" s="353"/>
-      <c r="AS34" s="352"/>
-      <c r="AT34" s="353"/>
+      <c r="AO34" s="359"/>
+      <c r="AP34" s="360"/>
+      <c r="AQ34" s="361"/>
+      <c r="AR34" s="356"/>
+      <c r="AS34" s="355"/>
+      <c r="AT34" s="356"/>
     </row>
     <row r="35" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG35" s="341" t="s">
+      <c r="AG35" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH35" s="342"/>
-      <c r="AI35" s="341" t="s">
+      <c r="AH35" s="345"/>
+      <c r="AI35" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ35" s="342"/>
-      <c r="AK35" s="341" t="s">
+      <c r="AJ35" s="345"/>
+      <c r="AK35" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL35" s="342"/>
-      <c r="AM35" s="341" t="s">
+      <c r="AL35" s="345"/>
+      <c r="AM35" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN35" s="342"/>
-      <c r="AO35" s="341" t="s">
+      <c r="AN35" s="345"/>
+      <c r="AO35" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP35" s="342"/>
-      <c r="AQ35" s="341" t="s">
+      <c r="AP35" s="345"/>
+      <c r="AQ35" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR35" s="342"/>
-      <c r="AS35" s="341" t="s">
+      <c r="AR35" s="345"/>
+      <c r="AS35" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT35" s="342"/>
+      <c r="AT35" s="345"/>
     </row>
     <row r="39" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="40" spans="33:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="AG40" s="343" t="s">
+      <c r="AG40" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AH40" s="344"/>
-      <c r="AI40" s="343"/>
-      <c r="AJ40" s="344"/>
-      <c r="AK40" s="343" t="s">
+      <c r="AH40" s="347"/>
+      <c r="AI40" s="346"/>
+      <c r="AJ40" s="347"/>
+      <c r="AK40" s="346" t="s">
         <v>604</v>
       </c>
-      <c r="AL40" s="344"/>
-      <c r="AM40" s="337" t="s">
+      <c r="AL40" s="347"/>
+      <c r="AM40" s="340" t="s">
         <v>608</v>
       </c>
-      <c r="AN40" s="347"/>
-      <c r="AO40" s="348" t="s">
+      <c r="AN40" s="350"/>
+      <c r="AO40" s="351" t="s">
         <v>607</v>
       </c>
-      <c r="AP40" s="349"/>
-      <c r="AQ40" s="347" t="s">
+      <c r="AP40" s="352"/>
+      <c r="AQ40" s="350" t="s">
         <v>606</v>
       </c>
-      <c r="AR40" s="338"/>
-      <c r="AS40" s="337" t="s">
+      <c r="AR40" s="341"/>
+      <c r="AS40" s="340" t="s">
         <v>605</v>
       </c>
-      <c r="AT40" s="338"/>
+      <c r="AT40" s="341"/>
     </row>
     <row r="41" spans="33:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG41" s="345"/>
-      <c r="AH41" s="346"/>
-      <c r="AI41" s="345"/>
-      <c r="AJ41" s="346"/>
-      <c r="AK41" s="345"/>
-      <c r="AL41" s="346"/>
-      <c r="AM41" s="339"/>
+      <c r="AG41" s="348"/>
+      <c r="AH41" s="349"/>
+      <c r="AI41" s="348"/>
+      <c r="AJ41" s="349"/>
+      <c r="AK41" s="348"/>
+      <c r="AL41" s="349"/>
+      <c r="AM41" s="342"/>
       <c r="AN41" s="154"/>
-      <c r="AO41" s="350"/>
-      <c r="AP41" s="351"/>
+      <c r="AO41" s="353"/>
+      <c r="AP41" s="354"/>
       <c r="AQ41" s="154"/>
-      <c r="AR41" s="340"/>
-      <c r="AS41" s="339"/>
-      <c r="AT41" s="340"/>
+      <c r="AR41" s="343"/>
+      <c r="AS41" s="342"/>
+      <c r="AT41" s="343"/>
     </row>
     <row r="42" spans="33:46" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AG42" s="341" t="s">
+      <c r="AG42" s="344" t="s">
         <v>603</v>
       </c>
-      <c r="AH42" s="342"/>
-      <c r="AI42" s="341" t="s">
+      <c r="AH42" s="345"/>
+      <c r="AI42" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="AJ42" s="342"/>
-      <c r="AK42" s="341" t="s">
+      <c r="AJ42" s="345"/>
+      <c r="AK42" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="AL42" s="342"/>
-      <c r="AM42" s="341" t="s">
+      <c r="AL42" s="345"/>
+      <c r="AM42" s="344" t="s">
         <v>74</v>
       </c>
-      <c r="AN42" s="342"/>
-      <c r="AO42" s="341" t="s">
+      <c r="AN42" s="345"/>
+      <c r="AO42" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="AP42" s="342"/>
-      <c r="AQ42" s="341" t="s">
+      <c r="AP42" s="345"/>
+      <c r="AQ42" s="344" t="s">
         <v>69</v>
       </c>
-      <c r="AR42" s="342"/>
-      <c r="AS42" s="341" t="s">
+      <c r="AR42" s="345"/>
+      <c r="AS42" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="AT42" s="342"/>
+      <c r="AT42" s="345"/>
     </row>
   </sheetData>
   <mergeCells count="115">
